--- a/AAII_Financials/Quarterly/BBAR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BBAR_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="92">
   <si>
     <t>BBAR</t>
   </si>
@@ -656,194 +656,201 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43190</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1050600</v>
+        <v>692500</v>
       </c>
       <c r="E8" s="3">
-        <v>872900</v>
+        <v>1081300</v>
       </c>
       <c r="F8" s="3">
-        <v>749300</v>
+        <v>364000</v>
       </c>
       <c r="G8" s="3">
-        <v>408400</v>
+        <v>312400</v>
       </c>
       <c r="H8" s="3">
-        <v>623400</v>
+        <v>170300</v>
       </c>
       <c r="I8" s="3">
-        <v>229100</v>
+        <v>259900</v>
       </c>
       <c r="J8" s="3">
+        <v>95500</v>
+      </c>
+      <c r="K8" s="3">
         <v>437400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>410500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>727600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>254100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>377500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>248500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>494500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>386400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>501000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>401000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>728200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>327000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>240600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>166900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>139500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>130800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>121600</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -916,8 +923,11 @@
       <c r="Z9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -990,8 +1000,11 @@
       <c r="Z10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1018,8 +1031,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1092,8 +1106,11 @@
       <c r="Z12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1166,8 +1183,11 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1240,82 +1260,88 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-9900</v>
+        <v>-5200</v>
       </c>
       <c r="E15" s="3">
-        <v>-9900</v>
+        <v>-11100</v>
       </c>
       <c r="F15" s="3">
-        <v>-10700</v>
+        <v>-4100</v>
       </c>
       <c r="G15" s="3">
-        <v>-5800</v>
+        <v>-4400</v>
       </c>
       <c r="H15" s="3">
-        <v>-12600</v>
+        <v>-2400</v>
       </c>
       <c r="I15" s="3">
-        <v>-5400</v>
+        <v>-5200</v>
       </c>
       <c r="J15" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="K15" s="3">
         <v>-10900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-14600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-31700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-14100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-12800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-8000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-17500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-24600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-25900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-15300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-26900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-27600</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-3800</v>
-      </c>
-      <c r="W15" s="3">
-        <v>-3000</v>
       </c>
       <c r="X15" s="3">
         <v>-3000</v>
       </c>
       <c r="Y15" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="Z15" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1339,156 +1365,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>557000</v>
+        <v>382800</v>
       </c>
       <c r="E17" s="3">
-        <v>442000</v>
+        <v>561600</v>
       </c>
       <c r="F17" s="3">
-        <v>377600</v>
+        <v>184300</v>
       </c>
       <c r="G17" s="3">
-        <v>203300</v>
+        <v>157400</v>
       </c>
       <c r="H17" s="3">
-        <v>294700</v>
+        <v>84800</v>
       </c>
       <c r="I17" s="3">
-        <v>106400</v>
+        <v>122900</v>
       </c>
       <c r="J17" s="3">
+        <v>44400</v>
+      </c>
+      <c r="K17" s="3">
         <v>187700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>199500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>348500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>118200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>182700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>98900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>199000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>153800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>256700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>242200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>377400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>172500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>140700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>91800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>63100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>55100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>52200</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>493600</v>
+        <v>309800</v>
       </c>
       <c r="E18" s="3">
-        <v>430900</v>
+        <v>519700</v>
       </c>
       <c r="F18" s="3">
-        <v>371700</v>
+        <v>179700</v>
       </c>
       <c r="G18" s="3">
-        <v>205100</v>
+        <v>155000</v>
       </c>
       <c r="H18" s="3">
-        <v>328700</v>
+        <v>85500</v>
       </c>
       <c r="I18" s="3">
-        <v>122700</v>
+        <v>137000</v>
       </c>
       <c r="J18" s="3">
+        <v>51200</v>
+      </c>
+      <c r="K18" s="3">
         <v>249700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>211000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>379000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>135900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>194700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>149600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>295400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>232700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>244300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>158800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>350800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>154500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>99900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>75100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>76300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>75700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>69400</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1515,156 +1548,163 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-356500</v>
+        <v>-291800</v>
       </c>
       <c r="E20" s="3">
-        <v>-354200</v>
+        <v>-399500</v>
       </c>
       <c r="F20" s="3">
-        <v>-284900</v>
+        <v>-147700</v>
       </c>
       <c r="G20" s="3">
-        <v>-169300</v>
+        <v>-118800</v>
       </c>
       <c r="H20" s="3">
-        <v>-276200</v>
+        <v>-70600</v>
       </c>
       <c r="I20" s="3">
-        <v>-103500</v>
+        <v>-115200</v>
       </c>
       <c r="J20" s="3">
+        <v>-43200</v>
+      </c>
+      <c r="K20" s="3">
         <v>-199000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-172400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-317800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-118400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-161000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-104600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-193000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-177000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-255800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-63500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-122200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-56500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-41500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-18300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-32100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-38800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-33500</v>
       </c>
     </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>148900</v>
+        <v>26000</v>
       </c>
       <c r="E21" s="3">
-        <v>84700</v>
+        <v>128400</v>
       </c>
       <c r="F21" s="3">
-        <v>99400</v>
+        <v>35300</v>
       </c>
       <c r="G21" s="3">
-        <v>43900</v>
+        <v>41500</v>
       </c>
       <c r="H21" s="3">
-        <v>62800</v>
+        <v>18300</v>
       </c>
       <c r="I21" s="3">
-        <v>23800</v>
+        <v>26200</v>
       </c>
       <c r="J21" s="3">
+        <v>9900</v>
+      </c>
+      <c r="K21" s="3">
         <v>61800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>51800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>78000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>24200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>46500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>54400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>118400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>67300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>14400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>107800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>249700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>111500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>61800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>59700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>47300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>40100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>36100</v>
       </c>
     </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1737,156 +1777,165 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>137100</v>
+        <v>18000</v>
       </c>
       <c r="E23" s="3">
-        <v>76700</v>
+        <v>120200</v>
       </c>
       <c r="F23" s="3">
-        <v>86800</v>
+        <v>32000</v>
       </c>
       <c r="G23" s="3">
-        <v>35800</v>
+        <v>36200</v>
       </c>
       <c r="H23" s="3">
-        <v>52500</v>
+        <v>14900</v>
       </c>
       <c r="I23" s="3">
-        <v>19100</v>
+        <v>21900</v>
       </c>
       <c r="J23" s="3">
+        <v>8000</v>
+      </c>
+      <c r="K23" s="3">
         <v>50700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>38600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>61200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>17500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>33700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>45000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>102400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>55600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-11500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>95300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>228600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>98000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>58400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>56700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>44200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>36800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>35900</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>51200</v>
+        <v>6300</v>
       </c>
       <c r="E24" s="3">
-        <v>24100</v>
+        <v>42300</v>
       </c>
       <c r="F24" s="3">
-        <v>21300</v>
+        <v>10100</v>
       </c>
       <c r="G24" s="3">
-        <v>8500</v>
+        <v>8900</v>
       </c>
       <c r="H24" s="3">
-        <v>-18700</v>
+        <v>3500</v>
       </c>
       <c r="I24" s="3">
-        <v>5800</v>
+        <v>-7800</v>
       </c>
       <c r="J24" s="3">
+        <v>2400</v>
+      </c>
+      <c r="K24" s="3">
         <v>11100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>11900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-29400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-3000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>21700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>11100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>44400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>34000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>21500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>11100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>72200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>42000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>18500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>15400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>12700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>11000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>12400</v>
       </c>
     </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1959,156 +2008,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>85900</v>
+        <v>11700</v>
       </c>
       <c r="E26" s="3">
-        <v>52600</v>
+        <v>77900</v>
       </c>
       <c r="F26" s="3">
-        <v>65400</v>
+        <v>21900</v>
       </c>
       <c r="G26" s="3">
         <v>27300</v>
       </c>
       <c r="H26" s="3">
-        <v>71200</v>
+        <v>11400</v>
       </c>
       <c r="I26" s="3">
-        <v>13400</v>
+        <v>29700</v>
       </c>
       <c r="J26" s="3">
+        <v>5600</v>
+      </c>
+      <c r="K26" s="3">
         <v>39600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>26700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>90600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>20500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>12100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>33900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>58000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>21700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-33000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>84100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>156400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>56000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>39900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>41400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>31500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>25900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>85100</v>
+        <v>11400</v>
       </c>
       <c r="E27" s="3">
-        <v>52600</v>
+        <v>77400</v>
       </c>
       <c r="F27" s="3">
-        <v>66400</v>
+        <v>22000</v>
       </c>
       <c r="G27" s="3">
-        <v>27800</v>
+        <v>27700</v>
       </c>
       <c r="H27" s="3">
-        <v>72200</v>
+        <v>11600</v>
       </c>
       <c r="I27" s="3">
-        <v>13900</v>
+        <v>30100</v>
       </c>
       <c r="J27" s="3">
+        <v>5800</v>
+      </c>
+      <c r="K27" s="3">
         <v>39500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>26700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>91000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>20800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>13000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>33900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>57200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>21200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-28600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>79700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>156400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>56000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>39900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>40800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>31100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>25500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2181,8 +2239,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2255,8 +2316,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2329,8 +2393,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2403,156 +2470,165 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>356500</v>
+        <v>291800</v>
       </c>
       <c r="E32" s="3">
-        <v>354200</v>
+        <v>399500</v>
       </c>
       <c r="F32" s="3">
-        <v>284900</v>
+        <v>147700</v>
       </c>
       <c r="G32" s="3">
-        <v>169300</v>
+        <v>118800</v>
       </c>
       <c r="H32" s="3">
-        <v>276200</v>
+        <v>70600</v>
       </c>
       <c r="I32" s="3">
-        <v>103500</v>
+        <v>115200</v>
       </c>
       <c r="J32" s="3">
+        <v>43200</v>
+      </c>
+      <c r="K32" s="3">
         <v>199000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>172400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>317800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>118400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>161000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>104600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>193000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>177000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>255800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>63500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>122200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>56500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>41500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>18300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>32100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>38800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>33500</v>
       </c>
     </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>85100</v>
+        <v>11400</v>
       </c>
       <c r="E33" s="3">
-        <v>52600</v>
+        <v>77400</v>
       </c>
       <c r="F33" s="3">
-        <v>66400</v>
+        <v>22000</v>
       </c>
       <c r="G33" s="3">
-        <v>27800</v>
+        <v>27700</v>
       </c>
       <c r="H33" s="3">
-        <v>72200</v>
+        <v>11600</v>
       </c>
       <c r="I33" s="3">
-        <v>13900</v>
+        <v>30100</v>
       </c>
       <c r="J33" s="3">
+        <v>5800</v>
+      </c>
+      <c r="K33" s="3">
         <v>39500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>26700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>91000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>20800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>13000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>33900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>57200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>21200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-28600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>79700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>156400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>56000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>39900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>40800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>31100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>25500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2625,161 +2701,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>85100</v>
+        <v>11400</v>
       </c>
       <c r="E35" s="3">
-        <v>52600</v>
+        <v>77400</v>
       </c>
       <c r="F35" s="3">
-        <v>66400</v>
+        <v>22000</v>
       </c>
       <c r="G35" s="3">
-        <v>27800</v>
+        <v>27700</v>
       </c>
       <c r="H35" s="3">
-        <v>72200</v>
+        <v>11600</v>
       </c>
       <c r="I35" s="3">
-        <v>13900</v>
+        <v>30100</v>
       </c>
       <c r="J35" s="3">
+        <v>5800</v>
+      </c>
+      <c r="K35" s="3">
         <v>39500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>26700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>91000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>20800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>13000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>33900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>57200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>21200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-28600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>79700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>156400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>56000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>39900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>40800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>31100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>25500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43190</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2806,8 +2891,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2834,156 +2920,163 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1176200</v>
+        <v>542900</v>
       </c>
       <c r="E41" s="3">
-        <v>1031700</v>
+        <v>490400</v>
       </c>
       <c r="F41" s="3">
-        <v>789200</v>
+        <v>430200</v>
       </c>
       <c r="G41" s="3">
-        <v>541900</v>
+        <v>329100</v>
       </c>
       <c r="H41" s="3">
-        <v>489900</v>
+        <v>225900</v>
       </c>
       <c r="I41" s="3">
-        <v>539300</v>
+        <v>204300</v>
       </c>
       <c r="J41" s="3">
+        <v>224900</v>
+      </c>
+      <c r="K41" s="3">
         <v>1192000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>836700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>837900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1195800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1398000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>804800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>676300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1410000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2158700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>898700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>947900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1060300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1235900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1103600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>735900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>535600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>596800</v>
       </c>
     </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>259100</v>
+        <v>151800</v>
       </c>
       <c r="E42" s="3">
-        <v>110600</v>
+        <v>108000</v>
       </c>
       <c r="F42" s="3">
-        <v>124200</v>
+        <v>46100</v>
       </c>
       <c r="G42" s="3">
-        <v>93700</v>
+        <v>51800</v>
       </c>
       <c r="H42" s="3">
-        <v>93200</v>
+        <v>39100</v>
       </c>
       <c r="I42" s="3">
-        <v>54600</v>
+        <v>38900</v>
       </c>
       <c r="J42" s="3">
+        <v>22800</v>
+      </c>
+      <c r="K42" s="3">
         <v>31500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>51000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>45500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>70200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>67700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>74900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>98000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>151400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>115000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>141800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>107400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>118300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>212600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>96300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>104300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>96300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>279000</v>
       </c>
     </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3056,8 +3149,11 @@
       <c r="Z43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3130,8 +3226,11 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3204,8 +3303,11 @@
       <c r="Z45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3278,230 +3380,242 @@
       <c r="Z46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>15700</v>
+        <v>8800</v>
       </c>
       <c r="E47" s="3">
-        <v>13000</v>
+        <v>6500</v>
       </c>
       <c r="F47" s="3">
-        <v>9800</v>
+        <v>5400</v>
       </c>
       <c r="G47" s="3">
-        <v>8700</v>
+        <v>4100</v>
       </c>
       <c r="H47" s="3">
-        <v>7400</v>
+        <v>3600</v>
       </c>
       <c r="I47" s="3">
-        <v>6400</v>
+        <v>3100</v>
       </c>
       <c r="J47" s="3">
+        <v>2700</v>
+      </c>
+      <c r="K47" s="3">
         <v>11300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>8400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>8800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>9900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>13600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>8300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>7700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>11200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>14500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>22000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>20300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>23800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>24200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>15900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>15200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>10900</v>
       </c>
     </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>404000</v>
+        <v>227000</v>
       </c>
       <c r="E48" s="3">
-        <v>328700</v>
+        <v>168400</v>
       </c>
       <c r="F48" s="3">
-        <v>272000</v>
+        <v>137100</v>
       </c>
       <c r="G48" s="3">
-        <v>229300</v>
+        <v>113400</v>
       </c>
       <c r="H48" s="3">
-        <v>194500</v>
+        <v>95600</v>
       </c>
       <c r="I48" s="3">
-        <v>165000</v>
+        <v>81100</v>
       </c>
       <c r="J48" s="3">
+        <v>68800</v>
+      </c>
+      <c r="K48" s="3">
         <v>280700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>192100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>177700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>234900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>318100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>188100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>176400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>271100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>364900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>121500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>125900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>126800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>133200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>124500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>133800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>149200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>70200</v>
       </c>
     </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>41700</v>
+        <v>24400</v>
       </c>
       <c r="E49" s="3">
-        <v>33000</v>
+        <v>17400</v>
       </c>
       <c r="F49" s="3">
-        <v>27200</v>
+        <v>13700</v>
       </c>
       <c r="G49" s="3">
-        <v>21200</v>
+        <v>11300</v>
       </c>
       <c r="H49" s="3">
-        <v>16600</v>
+        <v>8800</v>
       </c>
       <c r="I49" s="3">
-        <v>13000</v>
+        <v>6900</v>
       </c>
       <c r="J49" s="3">
+        <v>5400</v>
+      </c>
+      <c r="K49" s="3">
         <v>20300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>12300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>10200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>11900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>14600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>8100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>6700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>9100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>10900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>6600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>6300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>5900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>6900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>8100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>7900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>7400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3574,8 +3688,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3648,82 +3765,88 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>6400</v>
+        <v>3300</v>
       </c>
       <c r="E52" s="3">
-        <v>5300</v>
+        <v>2700</v>
       </c>
       <c r="F52" s="3">
-        <v>4900</v>
+        <v>2200</v>
       </c>
       <c r="G52" s="3">
-        <v>4100</v>
+        <v>2100</v>
       </c>
       <c r="H52" s="3">
-        <v>4100</v>
+        <v>1700</v>
       </c>
       <c r="I52" s="3">
-        <v>3800</v>
+        <v>1700</v>
       </c>
       <c r="J52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K52" s="3">
         <v>6500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>27700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>52100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>37000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>34100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>75300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>40000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>35600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>9300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>4800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>7800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>13200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3796,82 +3919,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>8867200</v>
+        <v>4580700</v>
       </c>
       <c r="E54" s="3">
-        <v>6678300</v>
+        <v>3697300</v>
       </c>
       <c r="F54" s="3">
-        <v>5543500</v>
+        <v>2784600</v>
       </c>
       <c r="G54" s="3">
-        <v>4531900</v>
+        <v>2311400</v>
       </c>
       <c r="H54" s="3">
-        <v>3977100</v>
+        <v>1889600</v>
       </c>
       <c r="I54" s="3">
-        <v>3308500</v>
+        <v>1658300</v>
       </c>
       <c r="J54" s="3">
+        <v>1379500</v>
+      </c>
+      <c r="K54" s="3">
         <v>5679100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3940200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3725500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4629800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6479800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3680600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3382600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5085500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6320300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4256700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>4168600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>4234100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>4812100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>4532100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>3926900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>3707300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>3729900</v>
       </c>
     </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3898,8 +4027,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3926,82 +4056,86 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>965500</v>
+        <v>341100</v>
       </c>
       <c r="E57" s="3">
-        <v>549800</v>
+        <v>402600</v>
       </c>
       <c r="F57" s="3">
+        <v>229300</v>
+      </c>
+      <c r="G57" s="3">
+        <v>189900</v>
+      </c>
+      <c r="H57" s="3">
+        <v>143000</v>
+      </c>
+      <c r="I57" s="3">
+        <v>124000</v>
+      </c>
+      <c r="J57" s="3">
+        <v>104100</v>
+      </c>
+      <c r="K57" s="3">
+        <v>426700</v>
+      </c>
+      <c r="L57" s="3">
+        <v>286900</v>
+      </c>
+      <c r="M57" s="3">
+        <v>249200</v>
+      </c>
+      <c r="N57" s="3">
+        <v>354700</v>
+      </c>
+      <c r="O57" s="3">
+        <v>443700</v>
+      </c>
+      <c r="P57" s="3">
+        <v>274100</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>200400</v>
+      </c>
+      <c r="R57" s="3">
         <v>455500</v>
       </c>
-      <c r="G57" s="3">
-        <v>342900</v>
-      </c>
-      <c r="H57" s="3">
-        <v>297400</v>
-      </c>
-      <c r="I57" s="3">
-        <v>249800</v>
-      </c>
-      <c r="J57" s="3">
-        <v>426700</v>
-      </c>
-      <c r="K57" s="3">
-        <v>286900</v>
-      </c>
-      <c r="L57" s="3">
-        <v>249200</v>
-      </c>
-      <c r="M57" s="3">
-        <v>354700</v>
-      </c>
-      <c r="N57" s="3">
-        <v>443700</v>
-      </c>
-      <c r="O57" s="3">
-        <v>274100</v>
-      </c>
-      <c r="P57" s="3">
-        <v>200400</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>455500</v>
-      </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>435500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>346300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>251100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>320900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>398200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>316500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>284300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>301300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>275600</v>
       </c>
     </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4074,82 +4208,88 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>249100</v>
+        <v>124900</v>
       </c>
       <c r="E59" s="3">
-        <v>176500</v>
+        <v>103900</v>
       </c>
       <c r="F59" s="3">
-        <v>137300</v>
+        <v>73600</v>
       </c>
       <c r="G59" s="3">
-        <v>114400</v>
+        <v>57200</v>
       </c>
       <c r="H59" s="3">
-        <v>126200</v>
+        <v>47700</v>
       </c>
       <c r="I59" s="3">
-        <v>115600</v>
+        <v>52600</v>
       </c>
       <c r="J59" s="3">
+        <v>48200</v>
+      </c>
+      <c r="K59" s="3">
         <v>222400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>140900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>131000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>146300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>232300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>74200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>69900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>165500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>193200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>105900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>91000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>97800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>97400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>80000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>57500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>49900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>54200</v>
       </c>
     </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4222,156 +4362,165 @@
       <c r="Z60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>16300</v>
+        <v>10600</v>
       </c>
       <c r="E61" s="3">
-        <v>14200</v>
+        <v>6800</v>
       </c>
       <c r="F61" s="3">
-        <v>11700</v>
+        <v>5900</v>
       </c>
       <c r="G61" s="3">
-        <v>10600</v>
+        <v>4900</v>
       </c>
       <c r="H61" s="3">
-        <v>9400</v>
+        <v>4400</v>
       </c>
       <c r="I61" s="3">
-        <v>8300</v>
+        <v>3900</v>
       </c>
       <c r="J61" s="3">
+        <v>3500</v>
+      </c>
+      <c r="K61" s="3">
         <v>16100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>12600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>12200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>18600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>27800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>17400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>16600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>25300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>35200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>26400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>21300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>23100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>200</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
         <v>13700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>9600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>78300</v>
       </c>
     </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>73800</v>
+        <v>45100</v>
       </c>
       <c r="E62" s="3">
-        <v>44100</v>
+        <v>30800</v>
       </c>
       <c r="F62" s="3">
-        <v>43500</v>
+        <v>18400</v>
       </c>
       <c r="G62" s="3">
-        <v>40400</v>
+        <v>18100</v>
       </c>
       <c r="H62" s="3">
-        <v>19500</v>
+        <v>16800</v>
       </c>
       <c r="I62" s="3">
-        <v>49200</v>
+        <v>8100</v>
       </c>
       <c r="J62" s="3">
+        <v>20500</v>
+      </c>
+      <c r="K62" s="3">
         <v>76200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>44000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>42100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>65800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>108400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>65500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>68700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>111800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>150400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>79000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>75500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>42900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>49900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>47400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>54400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>62500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>46300</v>
       </c>
     </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4444,8 +4593,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4518,8 +4670,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4592,82 +4747,88 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>7286400</v>
+        <v>3692200</v>
       </c>
       <c r="E66" s="3">
-        <v>5395700</v>
+        <v>3038200</v>
       </c>
       <c r="F66" s="3">
-        <v>4523300</v>
+        <v>2249800</v>
       </c>
       <c r="G66" s="3">
-        <v>3690900</v>
+        <v>1886100</v>
       </c>
       <c r="H66" s="3">
-        <v>3326500</v>
+        <v>1539000</v>
       </c>
       <c r="I66" s="3">
-        <v>2769200</v>
+        <v>1387000</v>
       </c>
       <c r="J66" s="3">
+        <v>1154700</v>
+      </c>
+      <c r="K66" s="3">
         <v>4800300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3313100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3164100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3896400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5522700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3027400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2801800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4222000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5280700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3680100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3651100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3749600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4289000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4047700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3445800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3184200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3299200</v>
       </c>
     </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4694,8 +4855,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4768,8 +4930,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4842,8 +5007,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4916,8 +5084,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4990,82 +5161,88 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1008600</v>
+        <v>566900</v>
       </c>
       <c r="E72" s="3">
-        <v>820300</v>
+        <v>420500</v>
       </c>
       <c r="F72" s="3">
-        <v>640400</v>
+        <v>342000</v>
       </c>
       <c r="G72" s="3">
-        <v>517200</v>
+        <v>267000</v>
       </c>
       <c r="H72" s="3">
-        <v>385100</v>
+        <v>215600</v>
       </c>
       <c r="I72" s="3">
-        <v>313000</v>
+        <v>160600</v>
       </c>
       <c r="J72" s="3">
+        <v>130500</v>
+      </c>
+      <c r="K72" s="3">
         <v>499000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>357800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>314900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>411700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>527200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>397400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>343200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>505000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>570400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>497900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>436200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>400900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>419200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>380500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>368900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>396500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>304100</v>
       </c>
     </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5138,8 +5315,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5212,8 +5392,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5286,82 +5469,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1580800</v>
+        <v>888500</v>
       </c>
       <c r="E76" s="3">
-        <v>1282600</v>
+        <v>659100</v>
       </c>
       <c r="F76" s="3">
-        <v>1020200</v>
+        <v>534800</v>
       </c>
       <c r="G76" s="3">
-        <v>841000</v>
+        <v>425400</v>
       </c>
       <c r="H76" s="3">
-        <v>650500</v>
+        <v>350600</v>
       </c>
       <c r="I76" s="3">
-        <v>539300</v>
+        <v>271200</v>
       </c>
       <c r="J76" s="3">
+        <v>224900</v>
+      </c>
+      <c r="K76" s="3">
         <v>878700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>627200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>561400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>733400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>957100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>653200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>580800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>863500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1039600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>576700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>517500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>484600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>523100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>484400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>481100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>523100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>430700</v>
       </c>
     </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5434,161 +5623,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43190</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>85100</v>
+        <v>11400</v>
       </c>
       <c r="E81" s="3">
-        <v>52600</v>
+        <v>77400</v>
       </c>
       <c r="F81" s="3">
-        <v>66400</v>
+        <v>22000</v>
       </c>
       <c r="G81" s="3">
-        <v>27800</v>
+        <v>27700</v>
       </c>
       <c r="H81" s="3">
-        <v>72200</v>
+        <v>11600</v>
       </c>
       <c r="I81" s="3">
-        <v>13900</v>
+        <v>30100</v>
       </c>
       <c r="J81" s="3">
+        <v>5800</v>
+      </c>
+      <c r="K81" s="3">
         <v>39500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>26700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>91000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>20800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>13000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>33900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>57200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>21200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-28600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>79700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>156400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>56000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>39900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>40800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>31100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>25500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5615,82 +5813,86 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>11800</v>
+        <v>8000</v>
       </c>
       <c r="E83" s="3">
-        <v>8000</v>
+        <v>8200</v>
       </c>
       <c r="F83" s="3">
-        <v>12700</v>
+        <v>3300</v>
       </c>
       <c r="G83" s="3">
-        <v>8100</v>
+        <v>5300</v>
       </c>
       <c r="H83" s="3">
-        <v>10300</v>
+        <v>3400</v>
       </c>
       <c r="I83" s="3">
-        <v>4600</v>
+        <v>4300</v>
       </c>
       <c r="J83" s="3">
+        <v>1900</v>
+      </c>
+      <c r="K83" s="3">
         <v>11100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>13100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>16800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>6700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>12800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>9500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>16000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>11600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>25900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>12500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>21100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>13400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>3400</v>
-      </c>
-      <c r="W83" s="3">
-        <v>3000</v>
       </c>
       <c r="X83" s="3">
         <v>3000</v>
       </c>
       <c r="Y83" s="3">
+        <v>3000</v>
+      </c>
+      <c r="Z83" s="3">
         <v>3300</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5763,8 +5965,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5837,8 +6042,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5911,8 +6119,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5985,8 +6196,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6059,82 +6273,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-122500</v>
+        <v>-167900</v>
       </c>
       <c r="E89" s="3">
-        <v>35300</v>
+        <v>-36300</v>
       </c>
       <c r="F89" s="3">
-        <v>105300</v>
+        <v>14700</v>
       </c>
       <c r="G89" s="3">
-        <v>-97400</v>
+        <v>43900</v>
       </c>
       <c r="H89" s="3">
-        <v>-282800</v>
+        <v>-40600</v>
       </c>
       <c r="I89" s="3">
-        <v>-146400</v>
+        <v>-117900</v>
       </c>
       <c r="J89" s="3">
+        <v>-61000</v>
+      </c>
+      <c r="K89" s="3">
         <v>82500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-7600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>88800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>157000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-19300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>50100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-415200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-247300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>611600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-180800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-156000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-62700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>260600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>198900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>38000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-38900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>154700</v>
       </c>
     </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6161,82 +6381,86 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-6606200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3044100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1859800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-12277100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-312900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2694300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1125700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-10201100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2576100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1792900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-7800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-14400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-9200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-22400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>7300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-4800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-5200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6309,8 +6533,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6383,82 +6610,88 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="F94" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-27700</v>
+      </c>
+      <c r="H94" s="3">
+        <v>400</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="K94" s="3">
+        <v>-14500</v>
+      </c>
+      <c r="L94" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="M94" s="3">
         <v>-6000</v>
       </c>
-      <c r="E94" s="3">
-        <v>-6500</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-30000</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-3100</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-10100</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-14500</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-8300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-15100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>17800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>16100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-22300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>14500</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
       <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6485,13 +6718,14 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
@@ -6539,11 +6773,11 @@
         <v>0</v>
       </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-25500</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
         <v>0</v>
       </c>
@@ -6557,10 +6791,13 @@
         <v>0</v>
       </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6633,8 +6870,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6707,8 +6947,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6781,226 +7024,238 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>5600</v>
+        <v>-19600</v>
       </c>
       <c r="E100" s="3">
-        <v>-16900</v>
+        <v>-4700</v>
       </c>
       <c r="F100" s="3">
-        <v>1900</v>
+        <v>-7100</v>
       </c>
       <c r="G100" s="3">
-        <v>-28600</v>
+        <v>800</v>
       </c>
       <c r="H100" s="3">
-        <v>9900</v>
+        <v>-11900</v>
       </c>
       <c r="I100" s="3">
+        <v>4100</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="K100" s="3">
+        <v>-900</v>
+      </c>
+      <c r="L100" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="M100" s="3">
+        <v>-18400</v>
+      </c>
+      <c r="N100" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="O100" s="3">
         <v>-5300</v>
       </c>
-      <c r="J100" s="3">
-        <v>-900</v>
-      </c>
-      <c r="K100" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="L100" s="3">
-        <v>-18400</v>
-      </c>
-      <c r="M100" s="3">
-        <v>-9800</v>
-      </c>
-      <c r="N100" s="3">
-        <v>-5300</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-16500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-22500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-12900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>11500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-30600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-18300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>21900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-8000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>21900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>55900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>2100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>24600</v>
+        <v>75200</v>
       </c>
       <c r="E101" s="3">
-        <v>26100</v>
+        <v>21100</v>
       </c>
       <c r="F101" s="3">
-        <v>45000</v>
+        <v>10900</v>
       </c>
       <c r="G101" s="3">
-        <v>-9100</v>
+        <v>18800</v>
       </c>
       <c r="H101" s="3">
-        <v>-32400</v>
+        <v>-3800</v>
       </c>
       <c r="I101" s="3">
-        <v>1200</v>
+        <v>-13500</v>
       </c>
       <c r="J101" s="3">
+        <v>500</v>
+      </c>
+      <c r="K101" s="3">
         <v>-25700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-65700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>5500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>4800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>23400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>23700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>51500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>63500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>30300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>245700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>69900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>87800</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-81800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>221100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>161900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>22700</v>
       </c>
-      <c r="Z101" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-99900</v>
+        <v>-120000</v>
       </c>
       <c r="E102" s="3">
-        <v>38000</v>
+        <v>-25800</v>
       </c>
       <c r="F102" s="3">
-        <v>85800</v>
+        <v>15900</v>
       </c>
       <c r="G102" s="3">
-        <v>-134300</v>
+        <v>35800</v>
       </c>
       <c r="H102" s="3">
-        <v>-316700</v>
+        <v>-56000</v>
       </c>
       <c r="I102" s="3">
-        <v>-154100</v>
+        <v>-132000</v>
       </c>
       <c r="J102" s="3">
+        <v>-64300</v>
+      </c>
+      <c r="K102" s="3">
         <v>-500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-102100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>54400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>149300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-16900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>44100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-405400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-217500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>638300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>33000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-86500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>53300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>152200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>452700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>257800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-21800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>188600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BBAR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BBAR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="92">
   <si>
     <t>BBAR</t>
   </si>
@@ -656,201 +656,214 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>692500</v>
+        <v>1417000</v>
       </c>
       <c r="E8" s="3">
-        <v>1081300</v>
+        <v>1865600</v>
       </c>
       <c r="F8" s="3">
-        <v>364000</v>
+        <v>651400</v>
       </c>
       <c r="G8" s="3">
-        <v>312400</v>
+        <v>1017200</v>
       </c>
       <c r="H8" s="3">
-        <v>170300</v>
+        <v>342400</v>
       </c>
       <c r="I8" s="3">
+        <v>293900</v>
+      </c>
+      <c r="J8" s="3">
+        <v>160200</v>
+      </c>
+      <c r="K8" s="3">
         <v>259900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>95500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>437400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>410500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>727600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>254100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>377500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>248500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>494500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>386400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>501000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>401000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>728200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>327000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>240600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>166900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>139500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>130800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>121600</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -926,8 +939,14 @@
       <c r="AA9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1003,8 +1022,14 @@
       <c r="AA10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1032,8 +1057,10 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1109,8 +1136,14 @@
       <c r="AA12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1186,8 +1219,14 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1263,85 +1302,97 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-5200</v>
+        <v>-11400</v>
       </c>
       <c r="E15" s="3">
-        <v>-11100</v>
+        <v>-15600</v>
       </c>
       <c r="F15" s="3">
-        <v>-4100</v>
+        <v>-4900</v>
       </c>
       <c r="G15" s="3">
-        <v>-4400</v>
+        <v>-10500</v>
       </c>
       <c r="H15" s="3">
-        <v>-2400</v>
+        <v>-3900</v>
       </c>
       <c r="I15" s="3">
-        <v>-5200</v>
+        <v>-4200</v>
       </c>
       <c r="J15" s="3">
         <v>-2300</v>
       </c>
       <c r="K15" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="L15" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="M15" s="3">
         <v>-10900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>-14600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>-31700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>-14100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>-12800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>-17500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>-24600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>-25900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>-15300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>-26900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>-27600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>-3800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>-3000</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>-3300</v>
       </c>
       <c r="AA15" s="3">
         <v>-3000</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="AC15" s="3">
+        <v>-3000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1366,162 +1417,176 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>382800</v>
+        <v>572400</v>
       </c>
       <c r="E17" s="3">
-        <v>561600</v>
+        <v>922500</v>
       </c>
       <c r="F17" s="3">
-        <v>184300</v>
+        <v>360100</v>
       </c>
       <c r="G17" s="3">
-        <v>157400</v>
+        <v>528300</v>
       </c>
       <c r="H17" s="3">
-        <v>84800</v>
+        <v>173400</v>
       </c>
       <c r="I17" s="3">
+        <v>148100</v>
+      </c>
+      <c r="J17" s="3">
+        <v>79700</v>
+      </c>
+      <c r="K17" s="3">
         <v>122900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>44400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>187700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>199500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>348500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>118200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>182700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>98900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>199000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>153800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>256700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>242200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>377400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>172500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>140700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>91800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>63100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>55100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>52200</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>309800</v>
+        <v>844600</v>
       </c>
       <c r="E18" s="3">
-        <v>519700</v>
+        <v>943100</v>
       </c>
       <c r="F18" s="3">
-        <v>179700</v>
+        <v>291400</v>
       </c>
       <c r="G18" s="3">
-        <v>155000</v>
+        <v>488900</v>
       </c>
       <c r="H18" s="3">
-        <v>85500</v>
+        <v>169000</v>
       </c>
       <c r="I18" s="3">
+        <v>145800</v>
+      </c>
+      <c r="J18" s="3">
+        <v>80500</v>
+      </c>
+      <c r="K18" s="3">
         <v>137000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>51200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>249700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>211000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>379000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>135900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>194700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>149600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>295400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>232700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>244300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>158800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>350800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>154500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>99900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>75100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>76300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>75700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>69400</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1549,162 +1614,176 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-291800</v>
+        <v>-780100</v>
       </c>
       <c r="E20" s="3">
-        <v>-399500</v>
+        <v>-737800</v>
       </c>
       <c r="F20" s="3">
-        <v>-147700</v>
+        <v>-274500</v>
       </c>
       <c r="G20" s="3">
-        <v>-118800</v>
+        <v>-375800</v>
       </c>
       <c r="H20" s="3">
-        <v>-70600</v>
+        <v>-138900</v>
       </c>
       <c r="I20" s="3">
+        <v>-111800</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-66400</v>
+      </c>
+      <c r="K20" s="3">
         <v>-115200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-43200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-199000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-172400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-317800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-118400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-161000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-104600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-193000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-177000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-255800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-63500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-122200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-56500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-41500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-18300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-32100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-38800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-33500</v>
       </c>
     </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>26000</v>
+        <v>75900</v>
       </c>
       <c r="E21" s="3">
-        <v>128400</v>
+        <v>221800</v>
       </c>
       <c r="F21" s="3">
-        <v>35300</v>
+        <v>24500</v>
       </c>
       <c r="G21" s="3">
-        <v>41500</v>
+        <v>120800</v>
       </c>
       <c r="H21" s="3">
-        <v>18300</v>
+        <v>33200</v>
       </c>
       <c r="I21" s="3">
+        <v>39000</v>
+      </c>
+      <c r="J21" s="3">
+        <v>17200</v>
+      </c>
+      <c r="K21" s="3">
         <v>26200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>9900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>61800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>51800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>78000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>24200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>46500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>54400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>118400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>67300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>14400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>107800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>249700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>111500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>61800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>59700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>47300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>40100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>36100</v>
       </c>
     </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1780,162 +1859,180 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>18000</v>
+        <v>64500</v>
       </c>
       <c r="E23" s="3">
-        <v>120200</v>
+        <v>205200</v>
       </c>
       <c r="F23" s="3">
-        <v>32000</v>
+        <v>16900</v>
       </c>
       <c r="G23" s="3">
-        <v>36200</v>
+        <v>113100</v>
       </c>
       <c r="H23" s="3">
-        <v>14900</v>
+        <v>30100</v>
       </c>
       <c r="I23" s="3">
+        <v>34000</v>
+      </c>
+      <c r="J23" s="3">
+        <v>14100</v>
+      </c>
+      <c r="K23" s="3">
         <v>21900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>8000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>50700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>38600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>61200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>17500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>33700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>45000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>102400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>55600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-11500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>95300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>228600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>98000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>58400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>56700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>44200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>36800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>35900</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>6300</v>
+        <v>26500</v>
       </c>
       <c r="E24" s="3">
-        <v>42300</v>
+        <v>106400</v>
       </c>
       <c r="F24" s="3">
-        <v>10100</v>
+        <v>6000</v>
       </c>
       <c r="G24" s="3">
-        <v>8900</v>
+        <v>39800</v>
       </c>
       <c r="H24" s="3">
-        <v>3500</v>
+        <v>9500</v>
       </c>
       <c r="I24" s="3">
+        <v>8400</v>
+      </c>
+      <c r="J24" s="3">
+        <v>3300</v>
+      </c>
+      <c r="K24" s="3">
         <v>-7800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>2400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>11100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>11900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>-29400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>-3000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>21700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>11100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>44400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>34000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>21500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>11100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>72200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>42000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>18500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>15400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>12700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>11000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>12400</v>
       </c>
     </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2011,162 +2108,180 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>11700</v>
+        <v>37900</v>
       </c>
       <c r="E26" s="3">
-        <v>77900</v>
+        <v>98900</v>
       </c>
       <c r="F26" s="3">
-        <v>21900</v>
+        <v>11000</v>
       </c>
       <c r="G26" s="3">
-        <v>27300</v>
+        <v>73300</v>
       </c>
       <c r="H26" s="3">
-        <v>11400</v>
+        <v>20600</v>
       </c>
       <c r="I26" s="3">
+        <v>25700</v>
+      </c>
+      <c r="J26" s="3">
+        <v>10700</v>
+      </c>
+      <c r="K26" s="3">
         <v>29700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>5600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>39600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>26700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>90600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>20500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>12100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>33900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>58000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>21700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-33000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>84100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>156400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>56000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>39900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>41400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>31500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>25900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>11400</v>
+        <v>38600</v>
       </c>
       <c r="E27" s="3">
-        <v>77400</v>
+        <v>99100</v>
       </c>
       <c r="F27" s="3">
-        <v>22000</v>
+        <v>10700</v>
       </c>
       <c r="G27" s="3">
-        <v>27700</v>
+        <v>72800</v>
       </c>
       <c r="H27" s="3">
-        <v>11600</v>
+        <v>20600</v>
       </c>
       <c r="I27" s="3">
+        <v>26000</v>
+      </c>
+      <c r="J27" s="3">
+        <v>10900</v>
+      </c>
+      <c r="K27" s="3">
         <v>30100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>5800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>39500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>26700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>91000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>20800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>13000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>33900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>57200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>21200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-28600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>79700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>156400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>56000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>39900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>40800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>31100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>25500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2242,8 +2357,14 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2319,8 +2440,14 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2396,8 +2523,14 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2473,162 +2606,180 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>291800</v>
+        <v>780100</v>
       </c>
       <c r="E32" s="3">
-        <v>399500</v>
+        <v>737800</v>
       </c>
       <c r="F32" s="3">
-        <v>147700</v>
+        <v>274500</v>
       </c>
       <c r="G32" s="3">
-        <v>118800</v>
+        <v>375800</v>
       </c>
       <c r="H32" s="3">
-        <v>70600</v>
+        <v>138900</v>
       </c>
       <c r="I32" s="3">
+        <v>111800</v>
+      </c>
+      <c r="J32" s="3">
+        <v>66400</v>
+      </c>
+      <c r="K32" s="3">
         <v>115200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>43200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>199000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>172400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>317800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>118400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>161000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>104600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>193000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>177000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>255800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>63500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>122200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>56500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>41500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>18300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>32100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>38800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>33500</v>
       </c>
     </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>11400</v>
+        <v>38600</v>
       </c>
       <c r="E33" s="3">
-        <v>77400</v>
+        <v>99100</v>
       </c>
       <c r="F33" s="3">
-        <v>22000</v>
+        <v>10700</v>
       </c>
       <c r="G33" s="3">
-        <v>27700</v>
+        <v>72800</v>
       </c>
       <c r="H33" s="3">
-        <v>11600</v>
+        <v>20600</v>
       </c>
       <c r="I33" s="3">
+        <v>26000</v>
+      </c>
+      <c r="J33" s="3">
+        <v>10900</v>
+      </c>
+      <c r="K33" s="3">
         <v>30100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>5800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>39500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>26700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>91000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>20800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>13000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>33900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>57200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>21200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-28600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>79700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>156400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>56000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>39900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>40800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>31100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>25500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2704,167 +2855,185 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>11400</v>
+        <v>38600</v>
       </c>
       <c r="E35" s="3">
-        <v>77400</v>
+        <v>99100</v>
       </c>
       <c r="F35" s="3">
-        <v>22000</v>
+        <v>10700</v>
       </c>
       <c r="G35" s="3">
-        <v>27700</v>
+        <v>72800</v>
       </c>
       <c r="H35" s="3">
-        <v>11600</v>
+        <v>20600</v>
       </c>
       <c r="I35" s="3">
+        <v>26000</v>
+      </c>
+      <c r="J35" s="3">
+        <v>10900</v>
+      </c>
+      <c r="K35" s="3">
         <v>30100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>5800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>39500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>26700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>91000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>20800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>13000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>33900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>57200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>21200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-28600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>79700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>156400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>56000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>39900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>40800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>31100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>25500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2892,8 +3061,10 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2921,162 +3092,176 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>542900</v>
+        <v>1318700</v>
       </c>
       <c r="E41" s="3">
-        <v>490400</v>
+        <v>1206700</v>
       </c>
       <c r="F41" s="3">
-        <v>430200</v>
+        <v>510700</v>
       </c>
       <c r="G41" s="3">
-        <v>329100</v>
+        <v>461300</v>
       </c>
       <c r="H41" s="3">
-        <v>225900</v>
+        <v>404700</v>
       </c>
       <c r="I41" s="3">
+        <v>309600</v>
+      </c>
+      <c r="J41" s="3">
+        <v>212500</v>
+      </c>
+      <c r="K41" s="3">
         <v>204300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>224900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1192000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>836700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>837900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1195800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1398000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>804800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>676300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>1410000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>2158700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>898700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>947900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>1060300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>1235900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>1103600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>735900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>535600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>596800</v>
       </c>
     </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>151800</v>
+        <v>356600</v>
       </c>
       <c r="E42" s="3">
-        <v>108000</v>
+        <v>318700</v>
       </c>
       <c r="F42" s="3">
-        <v>46100</v>
+        <v>142800</v>
       </c>
       <c r="G42" s="3">
-        <v>51800</v>
+        <v>101600</v>
       </c>
       <c r="H42" s="3">
-        <v>39100</v>
+        <v>43400</v>
       </c>
       <c r="I42" s="3">
+        <v>48700</v>
+      </c>
+      <c r="J42" s="3">
+        <v>36800</v>
+      </c>
+      <c r="K42" s="3">
         <v>38900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>22800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>31500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>51000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>45500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>70200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>67700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>74900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>98000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>151400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>115000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>141800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>107400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>118300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>212600</v>
-      </c>
-      <c r="X42" s="3">
-        <v>96300</v>
-      </c>
-      <c r="Y42" s="3">
-        <v>104300</v>
       </c>
       <c r="Z42" s="3">
         <v>96300</v>
       </c>
       <c r="AA42" s="3">
+        <v>104300</v>
+      </c>
+      <c r="AB42" s="3">
+        <v>96300</v>
+      </c>
+      <c r="AC42" s="3">
         <v>279000</v>
       </c>
     </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3152,8 +3337,14 @@
       <c r="AA43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3229,8 +3420,14 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3306,8 +3503,14 @@
       <c r="AA45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3383,239 +3586,263 @@
       <c r="AA46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E47" s="3">
+        <v>13700</v>
+      </c>
+      <c r="F47" s="3">
+        <v>8300</v>
+      </c>
+      <c r="G47" s="3">
+        <v>6100</v>
+      </c>
+      <c r="H47" s="3">
+        <v>5100</v>
+      </c>
+      <c r="I47" s="3">
+        <v>3800</v>
+      </c>
+      <c r="J47" s="3">
+        <v>3400</v>
+      </c>
+      <c r="K47" s="3">
+        <v>3100</v>
+      </c>
+      <c r="L47" s="3">
+        <v>2700</v>
+      </c>
+      <c r="M47" s="3">
+        <v>11300</v>
+      </c>
+      <c r="N47" s="3">
+        <v>8400</v>
+      </c>
+      <c r="O47" s="3">
         <v>8800</v>
       </c>
-      <c r="E47" s="3">
-        <v>6500</v>
-      </c>
-      <c r="F47" s="3">
-        <v>5400</v>
-      </c>
-      <c r="G47" s="3">
-        <v>4100</v>
-      </c>
-      <c r="H47" s="3">
-        <v>3600</v>
-      </c>
-      <c r="I47" s="3">
-        <v>3100</v>
-      </c>
-      <c r="J47" s="3">
-        <v>2700</v>
-      </c>
-      <c r="K47" s="3">
-        <v>11300</v>
-      </c>
-      <c r="L47" s="3">
-        <v>8400</v>
-      </c>
-      <c r="M47" s="3">
-        <v>8800</v>
-      </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>9900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>13600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>8300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>7700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>11200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>14500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>2800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>22000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>20300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>23800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>24200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>15900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>15200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>10900</v>
       </c>
     </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>227000</v>
+        <v>516900</v>
       </c>
       <c r="E48" s="3">
-        <v>168400</v>
+        <v>331000</v>
       </c>
       <c r="F48" s="3">
-        <v>137100</v>
+        <v>213500</v>
       </c>
       <c r="G48" s="3">
-        <v>113400</v>
+        <v>158400</v>
       </c>
       <c r="H48" s="3">
-        <v>95600</v>
+        <v>128900</v>
       </c>
       <c r="I48" s="3">
+        <v>106700</v>
+      </c>
+      <c r="J48" s="3">
+        <v>89900</v>
+      </c>
+      <c r="K48" s="3">
         <v>81100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>68800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>280700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>192100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>177700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>234900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>318100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>188100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>176400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>271100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>364900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>121500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>125900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>126800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>133200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>124500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>133800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>149200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>70200</v>
       </c>
     </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>24400</v>
+        <v>56500</v>
       </c>
       <c r="E49" s="3">
-        <v>17400</v>
+        <v>36800</v>
       </c>
       <c r="F49" s="3">
-        <v>13700</v>
+        <v>22900</v>
       </c>
       <c r="G49" s="3">
-        <v>11300</v>
+        <v>16400</v>
       </c>
       <c r="H49" s="3">
-        <v>8800</v>
+        <v>12900</v>
       </c>
       <c r="I49" s="3">
+        <v>10700</v>
+      </c>
+      <c r="J49" s="3">
+        <v>8300</v>
+      </c>
+      <c r="K49" s="3">
         <v>6900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>5400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>20300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>12300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>10200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>11900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>14600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>8100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>6700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>9100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>10900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>6600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>6300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>5900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>6900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>8100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>7900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>7400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3691,8 +3918,14 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3768,85 +4001,97 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>3300</v>
+        <v>35200</v>
       </c>
       <c r="E52" s="3">
-        <v>2700</v>
+        <v>4100</v>
       </c>
       <c r="F52" s="3">
-        <v>2200</v>
+        <v>3100</v>
       </c>
       <c r="G52" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H52" s="3">
         <v>2100</v>
       </c>
-      <c r="H52" s="3">
-        <v>1700</v>
-      </c>
       <c r="I52" s="3">
-        <v>1700</v>
+        <v>1900</v>
       </c>
       <c r="J52" s="3">
         <v>1600</v>
       </c>
       <c r="K52" s="3">
+        <v>1700</v>
+      </c>
+      <c r="L52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="M52" s="3">
         <v>6500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>4200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>4000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>27700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>52100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>37000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>34100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>75300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>40000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>35600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>6200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>3600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>9300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>4800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>7800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>13200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3922,85 +4167,97 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>4580700</v>
+        <v>8996000</v>
       </c>
       <c r="E54" s="3">
-        <v>3697300</v>
+        <v>6798200</v>
       </c>
       <c r="F54" s="3">
-        <v>2784600</v>
+        <v>4309000</v>
       </c>
       <c r="G54" s="3">
-        <v>2311400</v>
+        <v>3478000</v>
       </c>
       <c r="H54" s="3">
-        <v>1889600</v>
+        <v>2619400</v>
       </c>
       <c r="I54" s="3">
+        <v>2174300</v>
+      </c>
+      <c r="J54" s="3">
+        <v>1777500</v>
+      </c>
+      <c r="K54" s="3">
         <v>1658300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1379500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>5679100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>3940200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>3725500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>4629800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>6479800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>3680600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>3382600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>5085500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>6320300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>4256700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>4168600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>4234100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>4812100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>4532100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>3926900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>3707300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>3729900</v>
       </c>
     </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4028,8 +4285,10 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4057,85 +4316,93 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>341100</v>
+        <v>766800</v>
       </c>
       <c r="E57" s="3">
-        <v>402600</v>
+        <v>569200</v>
       </c>
       <c r="F57" s="3">
-        <v>229300</v>
+        <v>320900</v>
       </c>
       <c r="G57" s="3">
-        <v>189900</v>
+        <v>378700</v>
       </c>
       <c r="H57" s="3">
-        <v>143000</v>
+        <v>215700</v>
       </c>
       <c r="I57" s="3">
+        <v>178700</v>
+      </c>
+      <c r="J57" s="3">
+        <v>134500</v>
+      </c>
+      <c r="K57" s="3">
         <v>124000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>104100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>426700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>286900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>249200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>354700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>443700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>274100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>200400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>455500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>435500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>346300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>251100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>320900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>398200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>316500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>284300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>301300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>275600</v>
       </c>
     </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4211,85 +4478,97 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>124900</v>
+        <v>319200</v>
       </c>
       <c r="E59" s="3">
-        <v>103900</v>
+        <v>322500</v>
       </c>
       <c r="F59" s="3">
-        <v>73600</v>
+        <v>117500</v>
       </c>
       <c r="G59" s="3">
-        <v>57200</v>
+        <v>97700</v>
       </c>
       <c r="H59" s="3">
-        <v>47700</v>
+        <v>69200</v>
       </c>
       <c r="I59" s="3">
+        <v>53800</v>
+      </c>
+      <c r="J59" s="3">
+        <v>44900</v>
+      </c>
+      <c r="K59" s="3">
         <v>52600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>48200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>222400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>140900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>131000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>146300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>232300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>74200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>69900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>165500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>193200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>105900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>91000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>97800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>97400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>80000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>57500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>49900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>54200</v>
       </c>
     </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4365,162 +4644,180 @@
       <c r="AA60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>10600</v>
+        <v>28900</v>
       </c>
       <c r="E61" s="3">
-        <v>6800</v>
+        <v>26100</v>
       </c>
       <c r="F61" s="3">
-        <v>5900</v>
+        <v>10000</v>
       </c>
       <c r="G61" s="3">
-        <v>4900</v>
+        <v>6400</v>
       </c>
       <c r="H61" s="3">
-        <v>4400</v>
+        <v>5600</v>
       </c>
       <c r="I61" s="3">
+        <v>4600</v>
+      </c>
+      <c r="J61" s="3">
+        <v>4200</v>
+      </c>
+      <c r="K61" s="3">
         <v>3900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>3500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>16100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>12600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>12200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>18600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>27800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>17400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>16600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>25300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>35200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>26400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>21300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>23100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>200</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3">
         <v>13700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>9600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>78300</v>
       </c>
     </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>45100</v>
+        <v>61300</v>
       </c>
       <c r="E62" s="3">
-        <v>30800</v>
+        <v>49000</v>
       </c>
       <c r="F62" s="3">
-        <v>18400</v>
+        <v>42500</v>
       </c>
       <c r="G62" s="3">
-        <v>18100</v>
+        <v>28900</v>
       </c>
       <c r="H62" s="3">
-        <v>16800</v>
+        <v>17300</v>
       </c>
       <c r="I62" s="3">
+        <v>17100</v>
+      </c>
+      <c r="J62" s="3">
+        <v>15800</v>
+      </c>
+      <c r="K62" s="3">
         <v>8100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>20500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>76200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>44000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>42100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>65800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>108400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>65500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>68700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>111800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>150400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>79000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>75500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>42900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>49900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>47400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>54400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>62500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>46300</v>
       </c>
     </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4596,8 +4893,14 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4673,8 +4976,14 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4750,85 +5059,97 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>3692200</v>
+        <v>6666800</v>
       </c>
       <c r="E66" s="3">
-        <v>3038200</v>
+        <v>5237400</v>
       </c>
       <c r="F66" s="3">
-        <v>2249800</v>
+        <v>3473200</v>
       </c>
       <c r="G66" s="3">
-        <v>1886100</v>
+        <v>2857900</v>
       </c>
       <c r="H66" s="3">
-        <v>1539000</v>
+        <v>2116400</v>
       </c>
       <c r="I66" s="3">
+        <v>1774200</v>
+      </c>
+      <c r="J66" s="3">
+        <v>1447700</v>
+      </c>
+      <c r="K66" s="3">
         <v>1387000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1154700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>4800300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>3313100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>3164100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>3896400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>5522700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>3027400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>2801800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>4222000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>5280700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>3680100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>3651100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>3749600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>4289000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>4047700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>3445800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>3184200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>3299200</v>
       </c>
     </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4856,8 +5177,10 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4933,8 +5256,14 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5010,8 +5339,14 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5087,8 +5422,14 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5164,85 +5505,97 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>566900</v>
+        <v>1625900</v>
       </c>
       <c r="E72" s="3">
-        <v>420500</v>
+        <v>1097000</v>
       </c>
       <c r="F72" s="3">
-        <v>342000</v>
+        <v>533200</v>
       </c>
       <c r="G72" s="3">
-        <v>267000</v>
+        <v>395600</v>
       </c>
       <c r="H72" s="3">
-        <v>215600</v>
+        <v>321700</v>
       </c>
       <c r="I72" s="3">
+        <v>251200</v>
+      </c>
+      <c r="J72" s="3">
+        <v>202900</v>
+      </c>
+      <c r="K72" s="3">
         <v>160600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>130500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>499000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>357800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>314900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>411700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>527200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>397400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>343200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>505000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>570400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>497900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>436200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>400900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>419200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>380500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>368900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>396500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>304100</v>
       </c>
     </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5318,8 +5671,14 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5395,8 +5754,14 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5472,85 +5837,97 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>888500</v>
+        <v>2329200</v>
       </c>
       <c r="E76" s="3">
-        <v>659100</v>
+        <v>1560800</v>
       </c>
       <c r="F76" s="3">
-        <v>534800</v>
+        <v>835800</v>
       </c>
       <c r="G76" s="3">
-        <v>425400</v>
+        <v>620000</v>
       </c>
       <c r="H76" s="3">
-        <v>350600</v>
+        <v>503100</v>
       </c>
       <c r="I76" s="3">
+        <v>400100</v>
+      </c>
+      <c r="J76" s="3">
+        <v>329800</v>
+      </c>
+      <c r="K76" s="3">
         <v>271200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>224900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>878700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>627200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>561400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>733400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>957100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>653200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>580800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>863500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>1039600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>576700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>517500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>484600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>523100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>484400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>481100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>523100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>430700</v>
       </c>
     </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5626,167 +6003,185 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>11400</v>
+        <v>38600</v>
       </c>
       <c r="E81" s="3">
-        <v>77400</v>
+        <v>99100</v>
       </c>
       <c r="F81" s="3">
-        <v>22000</v>
+        <v>10700</v>
       </c>
       <c r="G81" s="3">
-        <v>27700</v>
+        <v>72800</v>
       </c>
       <c r="H81" s="3">
-        <v>11600</v>
+        <v>20600</v>
       </c>
       <c r="I81" s="3">
+        <v>26000</v>
+      </c>
+      <c r="J81" s="3">
+        <v>10900</v>
+      </c>
+      <c r="K81" s="3">
         <v>30100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>5800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>39500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>26700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>91000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>20800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>13000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>33900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>57200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>21200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-28600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>79700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>156400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>56000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>39900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>40800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>31100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>25500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5814,85 +6209,93 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>8000</v>
+        <v>11400</v>
       </c>
       <c r="E83" s="3">
-        <v>8200</v>
+        <v>16500</v>
       </c>
       <c r="F83" s="3">
+        <v>7600</v>
+      </c>
+      <c r="G83" s="3">
+        <v>7800</v>
+      </c>
+      <c r="H83" s="3">
+        <v>3100</v>
+      </c>
+      <c r="I83" s="3">
+        <v>5000</v>
+      </c>
+      <c r="J83" s="3">
+        <v>3200</v>
+      </c>
+      <c r="K83" s="3">
+        <v>4300</v>
+      </c>
+      <c r="L83" s="3">
+        <v>1900</v>
+      </c>
+      <c r="M83" s="3">
+        <v>11100</v>
+      </c>
+      <c r="N83" s="3">
+        <v>13100</v>
+      </c>
+      <c r="O83" s="3">
+        <v>16800</v>
+      </c>
+      <c r="P83" s="3">
+        <v>6700</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>12800</v>
+      </c>
+      <c r="R83" s="3">
+        <v>9500</v>
+      </c>
+      <c r="S83" s="3">
+        <v>16000</v>
+      </c>
+      <c r="T83" s="3">
+        <v>11600</v>
+      </c>
+      <c r="U83" s="3">
+        <v>25900</v>
+      </c>
+      <c r="V83" s="3">
+        <v>12500</v>
+      </c>
+      <c r="W83" s="3">
+        <v>21100</v>
+      </c>
+      <c r="X83" s="3">
+        <v>13400</v>
+      </c>
+      <c r="Y83" s="3">
+        <v>3400</v>
+      </c>
+      <c r="Z83" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AA83" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AB83" s="3">
         <v>3300</v>
       </c>
-      <c r="G83" s="3">
-        <v>5300</v>
-      </c>
-      <c r="H83" s="3">
-        <v>3400</v>
-      </c>
-      <c r="I83" s="3">
-        <v>4300</v>
-      </c>
-      <c r="J83" s="3">
-        <v>1900</v>
-      </c>
-      <c r="K83" s="3">
-        <v>11100</v>
-      </c>
-      <c r="L83" s="3">
-        <v>13100</v>
-      </c>
-      <c r="M83" s="3">
-        <v>16800</v>
-      </c>
-      <c r="N83" s="3">
-        <v>6700</v>
-      </c>
-      <c r="O83" s="3">
-        <v>12800</v>
-      </c>
-      <c r="P83" s="3">
-        <v>9500</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>16000</v>
-      </c>
-      <c r="R83" s="3">
-        <v>11600</v>
-      </c>
-      <c r="S83" s="3">
-        <v>25900</v>
-      </c>
-      <c r="T83" s="3">
-        <v>12500</v>
-      </c>
-      <c r="U83" s="3">
-        <v>21100</v>
-      </c>
-      <c r="V83" s="3">
-        <v>13400</v>
-      </c>
-      <c r="W83" s="3">
-        <v>3400</v>
-      </c>
-      <c r="X83" s="3">
-        <v>3000</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>3000</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>3300</v>
-      </c>
-      <c r="AA83" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5968,8 +6371,14 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6045,8 +6454,14 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6122,8 +6537,14 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6199,8 +6620,14 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6276,85 +6703,97 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-167900</v>
+        <v>-232100</v>
       </c>
       <c r="E89" s="3">
-        <v>-36300</v>
+        <v>-122100</v>
       </c>
       <c r="F89" s="3">
-        <v>14700</v>
+        <v>-157900</v>
       </c>
       <c r="G89" s="3">
-        <v>43900</v>
+        <v>-34200</v>
       </c>
       <c r="H89" s="3">
-        <v>-40600</v>
+        <v>13900</v>
       </c>
       <c r="I89" s="3">
+        <v>41300</v>
+      </c>
+      <c r="J89" s="3">
+        <v>-38200</v>
+      </c>
+      <c r="K89" s="3">
         <v>-117900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-61000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>82500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-7600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>88800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>157000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-19300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>50100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-415200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-247300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>611600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-180800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-156000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-62700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>260600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>198900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>38000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-38900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>154700</v>
       </c>
     </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6382,85 +6821,93 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-24199800</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-30567700</v>
+      </c>
+      <c r="F91" s="3">
         <v>-6606200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-3044100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-1859800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-12277100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-312900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-2694300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-1125700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-10201100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-2576100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-1792900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-4400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-7800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-5000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-3700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-14400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-4000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-9200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-4500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-22400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>7300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-5200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6536,8 +6983,14 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6613,85 +7066,97 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-7800</v>
+        <v>-26900</v>
       </c>
       <c r="E94" s="3">
-        <v>-5800</v>
+        <v>-34800</v>
       </c>
       <c r="F94" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="J94" s="3">
+        <v>300</v>
+      </c>
+      <c r="K94" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="L94" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="M94" s="3">
+        <v>-14500</v>
+      </c>
+      <c r="N94" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="O94" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="P94" s="3">
         <v>-2700</v>
       </c>
-      <c r="G94" s="3">
-        <v>-27700</v>
-      </c>
-      <c r="H94" s="3">
-        <v>400</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-4700</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-14500</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="M94" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="N94" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-8300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-2000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-1900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-15100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-1200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>17800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>16100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-22300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>14500</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-5100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6719,20 +7184,22 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F96" s="3">
         <v>-100</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
       <c r="G96" s="3">
         <v>0</v>
       </c>
@@ -6776,14 +7243,14 @@
         <v>0</v>
       </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-25500</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
         <v>0</v>
       </c>
@@ -6794,10 +7261,16 @@
         <v>0</v>
       </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6873,8 +7346,14 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6950,8 +7429,14 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7027,235 +7512,259 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-19600</v>
+        <v>-30900</v>
       </c>
       <c r="E100" s="3">
-        <v>-4700</v>
+        <v>-6700</v>
       </c>
       <c r="F100" s="3">
-        <v>-7100</v>
+        <v>-18400</v>
       </c>
       <c r="G100" s="3">
-        <v>800</v>
+        <v>-4500</v>
       </c>
       <c r="H100" s="3">
-        <v>-11900</v>
+        <v>-6600</v>
       </c>
       <c r="I100" s="3">
+        <v>700</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="K100" s="3">
         <v>4100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-2200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-3400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-18400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-9800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-5300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-16500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-22500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-12900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>11500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-30600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-18300</v>
-      </c>
-      <c r="V100" s="3">
-        <v>21900</v>
-      </c>
-      <c r="W100" s="3">
-        <v>-8000</v>
       </c>
       <c r="X100" s="3">
         <v>21900</v>
       </c>
       <c r="Y100" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="Z100" s="3">
+        <v>21900</v>
+      </c>
+      <c r="AA100" s="3">
         <v>55900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>2100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>75200</v>
+        <v>-220700</v>
       </c>
       <c r="E101" s="3">
-        <v>21100</v>
+        <v>545200</v>
       </c>
       <c r="F101" s="3">
-        <v>10900</v>
+        <v>70800</v>
       </c>
       <c r="G101" s="3">
-        <v>18800</v>
+        <v>19900</v>
       </c>
       <c r="H101" s="3">
-        <v>-3800</v>
+        <v>10200</v>
       </c>
       <c r="I101" s="3">
+        <v>17600</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="K101" s="3">
         <v>-13500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-25700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-65700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>5500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>4800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>23400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>23700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>51500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>63500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>30300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>245700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>69900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>87800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-81800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>221100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>161900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>22700</v>
       </c>
-      <c r="AA101" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-120000</v>
+        <v>-510600</v>
       </c>
       <c r="E102" s="3">
-        <v>-25800</v>
+        <v>381700</v>
       </c>
       <c r="F102" s="3">
-        <v>15900</v>
+        <v>-112900</v>
       </c>
       <c r="G102" s="3">
-        <v>35800</v>
+        <v>-24300</v>
       </c>
       <c r="H102" s="3">
-        <v>-56000</v>
+        <v>14900</v>
       </c>
       <c r="I102" s="3">
+        <v>33700</v>
+      </c>
+      <c r="J102" s="3">
+        <v>-52700</v>
+      </c>
+      <c r="K102" s="3">
         <v>-132000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-64300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-102100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>54400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>149300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-16900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>44100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-405400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-217500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>638300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>33000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-86500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>53300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>152200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>452700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>257800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-21800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>188600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BBAR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BBAR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="92">
   <si>
     <t>BBAR</t>
   </si>
@@ -656,214 +656,220 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1417000</v>
+        <v>1012200</v>
       </c>
       <c r="E8" s="3">
-        <v>1865600</v>
+        <v>1574100</v>
       </c>
       <c r="F8" s="3">
-        <v>651400</v>
+        <v>1747900</v>
       </c>
       <c r="G8" s="3">
-        <v>1017200</v>
+        <v>610400</v>
       </c>
       <c r="H8" s="3">
-        <v>342400</v>
+        <v>953000</v>
       </c>
       <c r="I8" s="3">
-        <v>293900</v>
+        <v>320800</v>
       </c>
       <c r="J8" s="3">
+        <v>275400</v>
+      </c>
+      <c r="K8" s="3">
         <v>160200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>259900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>95500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>437400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>410500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>727600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>254100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>377500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>248500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>494500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>386400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>501000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>401000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>728200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>327000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>240600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>166900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>139500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>130800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>121600</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -945,8 +951,11 @@
       <c r="AC9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1028,8 +1037,11 @@
       <c r="AC10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1059,8 +1071,9 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1142,8 +1155,11 @@
       <c r="AC12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1225,8 +1241,11 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1308,91 +1327,97 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-11400</v>
+        <v>-18700</v>
       </c>
       <c r="E15" s="3">
-        <v>-15600</v>
+        <v>-12700</v>
       </c>
       <c r="F15" s="3">
-        <v>-4900</v>
+        <v>-14700</v>
       </c>
       <c r="G15" s="3">
-        <v>-10500</v>
+        <v>-4500</v>
       </c>
       <c r="H15" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="I15" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="J15" s="3">
         <v>-3900</v>
       </c>
-      <c r="I15" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>-2300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-5200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-2300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-10900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-14600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-31700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-14100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-12800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-8000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-17500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-24600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-25900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-15300</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>-26900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-27600</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-3800</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>-3000</v>
       </c>
       <c r="AA15" s="3">
         <v>-3000</v>
       </c>
       <c r="AB15" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="AC15" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1419,174 +1444,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>572400</v>
+        <v>349800</v>
       </c>
       <c r="E17" s="3">
-        <v>922500</v>
+        <v>635800</v>
       </c>
       <c r="F17" s="3">
-        <v>360100</v>
+        <v>864300</v>
       </c>
       <c r="G17" s="3">
-        <v>528300</v>
+        <v>337300</v>
       </c>
       <c r="H17" s="3">
-        <v>173400</v>
+        <v>495000</v>
       </c>
       <c r="I17" s="3">
-        <v>148100</v>
+        <v>162400</v>
       </c>
       <c r="J17" s="3">
+        <v>138800</v>
+      </c>
+      <c r="K17" s="3">
         <v>79700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>122900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>44400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>187700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>199500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>348500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>118200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>182700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>98900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>199000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>153800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>256700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>242200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>377400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>172500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>140700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>91800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>63100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>55100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>52200</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>844600</v>
+        <v>662500</v>
       </c>
       <c r="E18" s="3">
-        <v>943100</v>
+        <v>938200</v>
       </c>
       <c r="F18" s="3">
-        <v>291400</v>
+        <v>883600</v>
       </c>
       <c r="G18" s="3">
-        <v>488900</v>
+        <v>273000</v>
       </c>
       <c r="H18" s="3">
-        <v>169000</v>
+        <v>458000</v>
       </c>
       <c r="I18" s="3">
-        <v>145800</v>
+        <v>158400</v>
       </c>
       <c r="J18" s="3">
+        <v>136600</v>
+      </c>
+      <c r="K18" s="3">
         <v>80500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>137000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>51200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>249700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>211000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>379000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>135900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>194700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>149600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>295400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>232700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>244300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>158800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>350800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>154500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>99900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>75100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>76300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>75700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>69400</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1616,174 +1648,181 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-780100</v>
+        <v>-477000</v>
       </c>
       <c r="E20" s="3">
-        <v>-737800</v>
+        <v>-866600</v>
       </c>
       <c r="F20" s="3">
-        <v>-274500</v>
+        <v>-691300</v>
       </c>
       <c r="G20" s="3">
-        <v>-375800</v>
+        <v>-257200</v>
       </c>
       <c r="H20" s="3">
-        <v>-138900</v>
+        <v>-352100</v>
       </c>
       <c r="I20" s="3">
-        <v>-111800</v>
+        <v>-130200</v>
       </c>
       <c r="J20" s="3">
+        <v>-104700</v>
+      </c>
+      <c r="K20" s="3">
         <v>-66400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-115200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-43200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-199000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-172400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-317800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-118400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-161000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-104600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-193000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-177000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-255800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-63500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-122200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-56500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-41500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-18300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-32100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-38800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-33500</v>
       </c>
     </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>75900</v>
+        <v>206100</v>
       </c>
       <c r="E21" s="3">
-        <v>221800</v>
+        <v>82300</v>
       </c>
       <c r="F21" s="3">
-        <v>24500</v>
+        <v>207800</v>
       </c>
       <c r="G21" s="3">
-        <v>120800</v>
+        <v>22900</v>
       </c>
       <c r="H21" s="3">
-        <v>33200</v>
+        <v>113200</v>
       </c>
       <c r="I21" s="3">
-        <v>39000</v>
+        <v>31100</v>
       </c>
       <c r="J21" s="3">
+        <v>36500</v>
+      </c>
+      <c r="K21" s="3">
         <v>17200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>26200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>9900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>61800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>51800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>78000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>24200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>46500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>54400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>118400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>67300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>14400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>107800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>249700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>111500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>61800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>59700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>47300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>40100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>36100</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1865,174 +1904,183 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>64500</v>
+        <v>185500</v>
       </c>
       <c r="E23" s="3">
-        <v>205200</v>
+        <v>71600</v>
       </c>
       <c r="F23" s="3">
-        <v>16900</v>
+        <v>192300</v>
       </c>
       <c r="G23" s="3">
-        <v>113100</v>
+        <v>15900</v>
       </c>
       <c r="H23" s="3">
-        <v>30100</v>
+        <v>105900</v>
       </c>
       <c r="I23" s="3">
-        <v>34000</v>
+        <v>28200</v>
       </c>
       <c r="J23" s="3">
+        <v>31900</v>
+      </c>
+      <c r="K23" s="3">
         <v>14100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>21900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>8000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>50700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>38600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>61200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>17500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>33700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>45000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>102400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>55600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-11500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>95300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>228600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>98000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>58400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>56700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>44200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>36800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>35900</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>26500</v>
+        <v>68100</v>
       </c>
       <c r="E24" s="3">
-        <v>106400</v>
+        <v>29500</v>
       </c>
       <c r="F24" s="3">
-        <v>6000</v>
+        <v>99700</v>
       </c>
       <c r="G24" s="3">
-        <v>39800</v>
+        <v>5600</v>
       </c>
       <c r="H24" s="3">
-        <v>9500</v>
+        <v>37300</v>
       </c>
       <c r="I24" s="3">
-        <v>8400</v>
+        <v>8900</v>
       </c>
       <c r="J24" s="3">
+        <v>7800</v>
+      </c>
+      <c r="K24" s="3">
         <v>3300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-7800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>11100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>11900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-29400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>21700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>11100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>44400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>34000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>21500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>11100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>72200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>42000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>18500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>15400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>12700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>11000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>12400</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2114,174 +2162,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>37900</v>
+        <v>117400</v>
       </c>
       <c r="E26" s="3">
-        <v>98900</v>
+        <v>42100</v>
       </c>
       <c r="F26" s="3">
-        <v>11000</v>
+        <v>92600</v>
       </c>
       <c r="G26" s="3">
-        <v>73300</v>
+        <v>10300</v>
       </c>
       <c r="H26" s="3">
-        <v>20600</v>
+        <v>68600</v>
       </c>
       <c r="I26" s="3">
-        <v>25700</v>
+        <v>19300</v>
       </c>
       <c r="J26" s="3">
+        <v>24000</v>
+      </c>
+      <c r="K26" s="3">
         <v>10700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>29700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>5600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>39600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>26700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>90600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>20500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>12100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>33900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>58000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>21700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-33000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>84100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>156400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>56000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>39900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>41400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>31500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>25900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>38600</v>
+        <v>115400</v>
       </c>
       <c r="E27" s="3">
-        <v>99100</v>
+        <v>42900</v>
       </c>
       <c r="F27" s="3">
-        <v>10700</v>
+        <v>92900</v>
       </c>
       <c r="G27" s="3">
-        <v>72800</v>
+        <v>10000</v>
       </c>
       <c r="H27" s="3">
-        <v>20600</v>
+        <v>68200</v>
       </c>
       <c r="I27" s="3">
-        <v>26000</v>
+        <v>19300</v>
       </c>
       <c r="J27" s="3">
+        <v>24400</v>
+      </c>
+      <c r="K27" s="3">
         <v>10900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>30100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>5800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>39500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>26700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>91000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>20800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>13000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>33900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>57200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>21200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-28600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>79700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>156400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>56000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>39900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>40800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>31100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>25500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2363,8 +2420,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2446,8 +2506,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2529,8 +2592,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2612,174 +2678,183 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>780100</v>
+        <v>477000</v>
       </c>
       <c r="E32" s="3">
-        <v>737800</v>
+        <v>866600</v>
       </c>
       <c r="F32" s="3">
-        <v>274500</v>
+        <v>691300</v>
       </c>
       <c r="G32" s="3">
-        <v>375800</v>
+        <v>257200</v>
       </c>
       <c r="H32" s="3">
-        <v>138900</v>
+        <v>352100</v>
       </c>
       <c r="I32" s="3">
-        <v>111800</v>
+        <v>130200</v>
       </c>
       <c r="J32" s="3">
+        <v>104700</v>
+      </c>
+      <c r="K32" s="3">
         <v>66400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>115200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>43200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>199000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>172400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>317800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>118400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>161000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>104600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>193000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>177000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>255800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>63500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>122200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>56500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>41500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>18300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>32100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>38800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>33500</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>38600</v>
+        <v>115400</v>
       </c>
       <c r="E33" s="3">
-        <v>99100</v>
+        <v>42900</v>
       </c>
       <c r="F33" s="3">
-        <v>10700</v>
+        <v>92900</v>
       </c>
       <c r="G33" s="3">
-        <v>72800</v>
+        <v>10000</v>
       </c>
       <c r="H33" s="3">
-        <v>20600</v>
+        <v>68200</v>
       </c>
       <c r="I33" s="3">
-        <v>26000</v>
+        <v>19300</v>
       </c>
       <c r="J33" s="3">
+        <v>24400</v>
+      </c>
+      <c r="K33" s="3">
         <v>10900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>30100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>5800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>39500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>26700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>91000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>20800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>13000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>33900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>57200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>21200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-28600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>79700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>156400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>56000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>39900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>40800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>31100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>25500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2861,179 +2936,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>38600</v>
+        <v>115400</v>
       </c>
       <c r="E35" s="3">
-        <v>99100</v>
+        <v>42900</v>
       </c>
       <c r="F35" s="3">
-        <v>10700</v>
+        <v>92900</v>
       </c>
       <c r="G35" s="3">
-        <v>72800</v>
+        <v>10000</v>
       </c>
       <c r="H35" s="3">
-        <v>20600</v>
+        <v>68200</v>
       </c>
       <c r="I35" s="3">
-        <v>26000</v>
+        <v>19300</v>
       </c>
       <c r="J35" s="3">
+        <v>24400</v>
+      </c>
+      <c r="K35" s="3">
         <v>10900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>30100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>5800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>39500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>26700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>91000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>20800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>13000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>33900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>57200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>21200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-28600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>79700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>156400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>56000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>39900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>40800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>31100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>25500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3063,8 +3147,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3094,174 +3179,181 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1318700</v>
+        <v>1434300</v>
       </c>
       <c r="E41" s="3">
-        <v>1206700</v>
+        <v>1235500</v>
       </c>
       <c r="F41" s="3">
-        <v>510700</v>
+        <v>1130600</v>
       </c>
       <c r="G41" s="3">
-        <v>461300</v>
+        <v>478500</v>
       </c>
       <c r="H41" s="3">
-        <v>404700</v>
+        <v>432200</v>
       </c>
       <c r="I41" s="3">
-        <v>309600</v>
+        <v>379100</v>
       </c>
       <c r="J41" s="3">
+        <v>290000</v>
+      </c>
+      <c r="K41" s="3">
         <v>212500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>204300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>224900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1192000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>836700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>837900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1195800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1398000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>804800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>676300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1410000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2158700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>898700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>947900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1060300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1235900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1103600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>735900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>535600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>596800</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>356600</v>
+        <v>346500</v>
       </c>
       <c r="E42" s="3">
-        <v>318700</v>
+        <v>334200</v>
       </c>
       <c r="F42" s="3">
-        <v>142800</v>
+        <v>298600</v>
       </c>
       <c r="G42" s="3">
-        <v>101600</v>
+        <v>133800</v>
       </c>
       <c r="H42" s="3">
-        <v>43400</v>
+        <v>95200</v>
       </c>
       <c r="I42" s="3">
-        <v>48700</v>
+        <v>40600</v>
       </c>
       <c r="J42" s="3">
+        <v>45600</v>
+      </c>
+      <c r="K42" s="3">
         <v>36800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>38900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>22800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>31500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>51000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>45500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>70200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>67700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>74900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>98000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>151400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>115000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>141800</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>107400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>118300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>212600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>96300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>104300</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>96300</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>279000</v>
       </c>
     </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3343,8 +3435,11 @@
       <c r="AC43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3426,8 +3521,11 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3509,8 +3607,11 @@
       <c r="AC45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3592,257 +3693,269 @@
       <c r="AC46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>17600</v>
+        <v>18900</v>
       </c>
       <c r="E47" s="3">
-        <v>13700</v>
+        <v>16500</v>
       </c>
       <c r="F47" s="3">
+        <v>12900</v>
+      </c>
+      <c r="G47" s="3">
+        <v>7800</v>
+      </c>
+      <c r="H47" s="3">
+        <v>5800</v>
+      </c>
+      <c r="I47" s="3">
+        <v>4800</v>
+      </c>
+      <c r="J47" s="3">
+        <v>3600</v>
+      </c>
+      <c r="K47" s="3">
+        <v>3400</v>
+      </c>
+      <c r="L47" s="3">
+        <v>3100</v>
+      </c>
+      <c r="M47" s="3">
+        <v>2700</v>
+      </c>
+      <c r="N47" s="3">
+        <v>11300</v>
+      </c>
+      <c r="O47" s="3">
+        <v>8400</v>
+      </c>
+      <c r="P47" s="3">
+        <v>8800</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>9900</v>
+      </c>
+      <c r="R47" s="3">
+        <v>13600</v>
+      </c>
+      <c r="S47" s="3">
         <v>8300</v>
       </c>
-      <c r="G47" s="3">
-        <v>6100</v>
-      </c>
-      <c r="H47" s="3">
-        <v>5100</v>
-      </c>
-      <c r="I47" s="3">
-        <v>3800</v>
-      </c>
-      <c r="J47" s="3">
-        <v>3400</v>
-      </c>
-      <c r="K47" s="3">
-        <v>3100</v>
-      </c>
-      <c r="L47" s="3">
-        <v>2700</v>
-      </c>
-      <c r="M47" s="3">
-        <v>11300</v>
-      </c>
-      <c r="N47" s="3">
-        <v>8400</v>
-      </c>
-      <c r="O47" s="3">
-        <v>8800</v>
-      </c>
-      <c r="P47" s="3">
-        <v>9900</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>13600</v>
-      </c>
-      <c r="R47" s="3">
-        <v>8300</v>
-      </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>7700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>11200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>14500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>2800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>22000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>20300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>23800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>24200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>15900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>15200</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>10900</v>
       </c>
     </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>516900</v>
+        <v>577100</v>
       </c>
       <c r="E48" s="3">
-        <v>331000</v>
+        <v>484300</v>
       </c>
       <c r="F48" s="3">
-        <v>213500</v>
+        <v>310100</v>
       </c>
       <c r="G48" s="3">
-        <v>158400</v>
+        <v>200100</v>
       </c>
       <c r="H48" s="3">
-        <v>128900</v>
+        <v>148500</v>
       </c>
       <c r="I48" s="3">
-        <v>106700</v>
+        <v>120800</v>
       </c>
       <c r="J48" s="3">
+        <v>99900</v>
+      </c>
+      <c r="K48" s="3">
         <v>89900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>81100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>68800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>280700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>192100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>177700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>234900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>318100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>188100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>176400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>271100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>364900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>121500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>125900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>126800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>133200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>124500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>133800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>149200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>70200</v>
       </c>
     </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>56500</v>
+        <v>60100</v>
       </c>
       <c r="E49" s="3">
-        <v>36800</v>
+        <v>52900</v>
       </c>
       <c r="F49" s="3">
-        <v>22900</v>
+        <v>34500</v>
       </c>
       <c r="G49" s="3">
-        <v>16400</v>
+        <v>21500</v>
       </c>
       <c r="H49" s="3">
-        <v>12900</v>
+        <v>15300</v>
       </c>
       <c r="I49" s="3">
-        <v>10700</v>
+        <v>12100</v>
       </c>
       <c r="J49" s="3">
+        <v>10000</v>
+      </c>
+      <c r="K49" s="3">
         <v>8300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>20300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>12300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>10200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>11900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>14600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>8100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>6700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>9100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>10900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>6600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>6300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>5900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>6900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>8100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>7900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>7400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3924,8 +4037,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4007,91 +4123,97 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>35200</v>
+        <v>27800</v>
       </c>
       <c r="E52" s="3">
-        <v>4100</v>
+        <v>33000</v>
       </c>
       <c r="F52" s="3">
-        <v>3100</v>
+        <v>3800</v>
       </c>
       <c r="G52" s="3">
-        <v>2500</v>
+        <v>2900</v>
       </c>
       <c r="H52" s="3">
-        <v>2100</v>
+        <v>2400</v>
       </c>
       <c r="I52" s="3">
         <v>1900</v>
       </c>
       <c r="J52" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K52" s="3">
         <v>1600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>27700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>52100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>37000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>34100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>75300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>40000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>35600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>6200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>9300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>4800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>7800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>13200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4173,91 +4295,97 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>8996000</v>
+        <v>9923000</v>
       </c>
       <c r="E54" s="3">
-        <v>6798200</v>
+        <v>8428700</v>
       </c>
       <c r="F54" s="3">
-        <v>4309000</v>
+        <v>6369500</v>
       </c>
       <c r="G54" s="3">
-        <v>3478000</v>
+        <v>4037300</v>
       </c>
       <c r="H54" s="3">
-        <v>2619400</v>
+        <v>3258600</v>
       </c>
       <c r="I54" s="3">
-        <v>2174300</v>
+        <v>2454200</v>
       </c>
       <c r="J54" s="3">
+        <v>2037200</v>
+      </c>
+      <c r="K54" s="3">
         <v>1777500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1658300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1379500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5679100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3940200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3725500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4629800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6479800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3680600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3382600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5085500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6320300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>4256700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>4168600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>4234100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>4812100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>4532100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>3926900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>3707300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>3729900</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4287,8 +4415,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4318,91 +4447,95 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>766800</v>
+        <v>1103600</v>
       </c>
       <c r="E57" s="3">
-        <v>569200</v>
+        <v>718500</v>
       </c>
       <c r="F57" s="3">
+        <v>533300</v>
+      </c>
+      <c r="G57" s="3">
+        <v>300700</v>
+      </c>
+      <c r="H57" s="3">
+        <v>354800</v>
+      </c>
+      <c r="I57" s="3">
+        <v>202100</v>
+      </c>
+      <c r="J57" s="3">
+        <v>167400</v>
+      </c>
+      <c r="K57" s="3">
+        <v>134500</v>
+      </c>
+      <c r="L57" s="3">
+        <v>124000</v>
+      </c>
+      <c r="M57" s="3">
+        <v>104100</v>
+      </c>
+      <c r="N57" s="3">
+        <v>426700</v>
+      </c>
+      <c r="O57" s="3">
+        <v>286900</v>
+      </c>
+      <c r="P57" s="3">
+        <v>249200</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>354700</v>
+      </c>
+      <c r="R57" s="3">
+        <v>443700</v>
+      </c>
+      <c r="S57" s="3">
+        <v>274100</v>
+      </c>
+      <c r="T57" s="3">
+        <v>200400</v>
+      </c>
+      <c r="U57" s="3">
+        <v>455500</v>
+      </c>
+      <c r="V57" s="3">
+        <v>435500</v>
+      </c>
+      <c r="W57" s="3">
+        <v>346300</v>
+      </c>
+      <c r="X57" s="3">
+        <v>251100</v>
+      </c>
+      <c r="Y57" s="3">
         <v>320900</v>
       </c>
-      <c r="G57" s="3">
-        <v>378700</v>
-      </c>
-      <c r="H57" s="3">
-        <v>215700</v>
-      </c>
-      <c r="I57" s="3">
-        <v>178700</v>
-      </c>
-      <c r="J57" s="3">
-        <v>134500</v>
-      </c>
-      <c r="K57" s="3">
-        <v>124000</v>
-      </c>
-      <c r="L57" s="3">
-        <v>104100</v>
-      </c>
-      <c r="M57" s="3">
-        <v>426700</v>
-      </c>
-      <c r="N57" s="3">
-        <v>286900</v>
-      </c>
-      <c r="O57" s="3">
-        <v>249200</v>
-      </c>
-      <c r="P57" s="3">
-        <v>354700</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>443700</v>
-      </c>
-      <c r="R57" s="3">
-        <v>274100</v>
-      </c>
-      <c r="S57" s="3">
-        <v>200400</v>
-      </c>
-      <c r="T57" s="3">
-        <v>455500</v>
-      </c>
-      <c r="U57" s="3">
-        <v>435500</v>
-      </c>
-      <c r="V57" s="3">
-        <v>346300</v>
-      </c>
-      <c r="W57" s="3">
-        <v>251100</v>
-      </c>
-      <c r="X57" s="3">
-        <v>320900</v>
-      </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>398200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>316500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>284300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>301300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>275600</v>
       </c>
     </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4484,91 +4617,97 @@
       <c r="AC58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>319200</v>
+        <v>172400</v>
       </c>
       <c r="E59" s="3">
-        <v>322500</v>
+        <v>299100</v>
       </c>
       <c r="F59" s="3">
-        <v>117500</v>
+        <v>302100</v>
       </c>
       <c r="G59" s="3">
-        <v>97700</v>
+        <v>110000</v>
       </c>
       <c r="H59" s="3">
-        <v>69200</v>
+        <v>91500</v>
       </c>
       <c r="I59" s="3">
-        <v>53800</v>
+        <v>64900</v>
       </c>
       <c r="J59" s="3">
+        <v>50400</v>
+      </c>
+      <c r="K59" s="3">
         <v>44900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>52600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>48200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>222400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>140900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>131000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>146300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>232300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>74200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>69900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>165500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>193200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>105900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>91000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>97800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>97400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>80000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>57500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>49900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>54200</v>
       </c>
     </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4650,174 +4789,183 @@
       <c r="AC60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>28900</v>
+        <v>214700</v>
       </c>
       <c r="E61" s="3">
-        <v>26100</v>
+        <v>27100</v>
       </c>
       <c r="F61" s="3">
-        <v>10000</v>
+        <v>24400</v>
       </c>
       <c r="G61" s="3">
-        <v>6400</v>
+        <v>9300</v>
       </c>
       <c r="H61" s="3">
-        <v>5600</v>
+        <v>6000</v>
       </c>
       <c r="I61" s="3">
-        <v>4600</v>
+        <v>5200</v>
       </c>
       <c r="J61" s="3">
+        <v>4300</v>
+      </c>
+      <c r="K61" s="3">
         <v>4200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>16100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>12600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>12200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>18600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>27800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>17400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>16600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>25300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>35200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>26400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>21300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>23100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>200</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="3">
         <v>13700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>9600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>78300</v>
       </c>
     </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>61300</v>
+        <v>39900</v>
       </c>
       <c r="E62" s="3">
-        <v>49000</v>
+        <v>57500</v>
       </c>
       <c r="F62" s="3">
-        <v>42500</v>
+        <v>45900</v>
       </c>
       <c r="G62" s="3">
-        <v>28900</v>
+        <v>39800</v>
       </c>
       <c r="H62" s="3">
-        <v>17300</v>
+        <v>27100</v>
       </c>
       <c r="I62" s="3">
-        <v>17100</v>
+        <v>16200</v>
       </c>
       <c r="J62" s="3">
+        <v>16000</v>
+      </c>
+      <c r="K62" s="3">
         <v>15800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>8100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>20500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>76200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>44000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>42100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>65800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>108400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>65500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>68700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>111800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>150400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>79000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>75500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>42900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>49900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>47400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>54400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>62500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>46300</v>
       </c>
     </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4899,8 +5047,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4982,8 +5133,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5065,91 +5219,97 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>6666800</v>
+        <v>7764400</v>
       </c>
       <c r="E66" s="3">
-        <v>5237400</v>
+        <v>6246300</v>
       </c>
       <c r="F66" s="3">
-        <v>3473200</v>
+        <v>4907100</v>
       </c>
       <c r="G66" s="3">
-        <v>2857900</v>
+        <v>3254100</v>
       </c>
       <c r="H66" s="3">
-        <v>2116400</v>
+        <v>2677700</v>
       </c>
       <c r="I66" s="3">
-        <v>1774200</v>
+        <v>1982900</v>
       </c>
       <c r="J66" s="3">
+        <v>1662300</v>
+      </c>
+      <c r="K66" s="3">
         <v>1447700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1387000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1154700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4800300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3313100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3164100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3896400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5522700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3027400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2801800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4222000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5280700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3680100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3651100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3749600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4289000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4047700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3445800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3184200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3299200</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5179,8 +5339,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5262,8 +5423,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5345,8 +5509,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5428,8 +5595,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5511,91 +5681,97 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1625900</v>
+        <v>1377300</v>
       </c>
       <c r="E72" s="3">
-        <v>1097000</v>
+        <v>1523400</v>
       </c>
       <c r="F72" s="3">
-        <v>533200</v>
+        <v>1027800</v>
       </c>
       <c r="G72" s="3">
-        <v>395600</v>
+        <v>499600</v>
       </c>
       <c r="H72" s="3">
-        <v>321700</v>
+        <v>370600</v>
       </c>
       <c r="I72" s="3">
-        <v>251200</v>
+        <v>301400</v>
       </c>
       <c r="J72" s="3">
+        <v>235300</v>
+      </c>
+      <c r="K72" s="3">
         <v>202900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>160600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>130500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>499000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>357800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>314900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>411700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>527200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>397400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>343200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>505000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>570400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>497900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>436200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>400900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>419200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>380500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>368900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>396500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>304100</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5677,8 +5853,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5760,8 +5939,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5843,91 +6025,97 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2329200</v>
+        <v>2158600</v>
       </c>
       <c r="E76" s="3">
-        <v>1560800</v>
+        <v>2182300</v>
       </c>
       <c r="F76" s="3">
-        <v>835800</v>
+        <v>1462400</v>
       </c>
       <c r="G76" s="3">
-        <v>620000</v>
+        <v>783100</v>
       </c>
       <c r="H76" s="3">
-        <v>503100</v>
+        <v>580900</v>
       </c>
       <c r="I76" s="3">
-        <v>400100</v>
+        <v>471300</v>
       </c>
       <c r="J76" s="3">
+        <v>374900</v>
+      </c>
+      <c r="K76" s="3">
         <v>329800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>271200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>224900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>878700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>627200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>561400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>733400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>957100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>653200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>580800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>863500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1039600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>576700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>517500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>484600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>523100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>484400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>481100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>523100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>430700</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6009,179 +6197,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>38600</v>
+        <v>115400</v>
       </c>
       <c r="E81" s="3">
-        <v>99100</v>
+        <v>42900</v>
       </c>
       <c r="F81" s="3">
-        <v>10700</v>
+        <v>92900</v>
       </c>
       <c r="G81" s="3">
-        <v>72800</v>
+        <v>10000</v>
       </c>
       <c r="H81" s="3">
-        <v>20600</v>
+        <v>68200</v>
       </c>
       <c r="I81" s="3">
-        <v>26000</v>
+        <v>19300</v>
       </c>
       <c r="J81" s="3">
+        <v>24400</v>
+      </c>
+      <c r="K81" s="3">
         <v>10900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>30100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>5800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>39500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>26700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>91000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>20800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>13000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>33900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>57200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>21200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-28600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>79700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>156400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>56000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>39900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>40800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>31100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>25500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6211,91 +6408,95 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>11400</v>
+        <v>20600</v>
       </c>
       <c r="E83" s="3">
-        <v>16500</v>
+        <v>10700</v>
       </c>
       <c r="F83" s="3">
-        <v>7600</v>
+        <v>15500</v>
       </c>
       <c r="G83" s="3">
-        <v>7800</v>
+        <v>7100</v>
       </c>
       <c r="H83" s="3">
-        <v>3100</v>
+        <v>7300</v>
       </c>
       <c r="I83" s="3">
-        <v>5000</v>
+        <v>2900</v>
       </c>
       <c r="J83" s="3">
+        <v>4700</v>
+      </c>
+      <c r="K83" s="3">
         <v>3200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>11100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>13100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>16800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>6700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>12800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>9500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>16000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>11600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>25900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>12500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>21100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>13400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>3400</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>3000</v>
       </c>
       <c r="AA83" s="3">
         <v>3000</v>
       </c>
       <c r="AB83" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AC83" s="3">
         <v>3300</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6377,8 +6578,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6460,8 +6664,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6543,8 +6750,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6626,8 +6836,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6709,91 +6922,97 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-232100</v>
+        <v>118500</v>
       </c>
       <c r="E89" s="3">
-        <v>-122100</v>
+        <v>-217500</v>
       </c>
       <c r="F89" s="3">
-        <v>-157900</v>
+        <v>-114400</v>
       </c>
       <c r="G89" s="3">
-        <v>-34200</v>
+        <v>-148000</v>
       </c>
       <c r="H89" s="3">
-        <v>13900</v>
+        <v>-32000</v>
       </c>
       <c r="I89" s="3">
-        <v>41300</v>
+        <v>13000</v>
       </c>
       <c r="J89" s="3">
+        <v>38700</v>
+      </c>
+      <c r="K89" s="3">
         <v>-38200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-117900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-61000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>82500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-7600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>88800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>157000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-19300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>50100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-415200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-247300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>611600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-180800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-156000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-62700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>260600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>198900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>38000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-38900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>154700</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6823,91 +7042,95 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-21954000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-24199800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-30567700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6606200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3044100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1859800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-12277100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-312900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2694300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1125700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-10201100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2576100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1792900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-7800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-5000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-14400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-4000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-9200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-22400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>7300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-4800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-5200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6989,8 +7212,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7072,91 +7298,97 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-26900</v>
+        <v>-22800</v>
       </c>
       <c r="E94" s="3">
-        <v>-34800</v>
+        <v>-25200</v>
       </c>
       <c r="F94" s="3">
-        <v>-7400</v>
+        <v>-29800</v>
       </c>
       <c r="G94" s="3">
-        <v>-5500</v>
+        <v>-8100</v>
       </c>
       <c r="H94" s="3">
-        <v>-2500</v>
+        <v>-4600</v>
       </c>
       <c r="I94" s="3">
-        <v>-26000</v>
+        <v>-2400</v>
       </c>
       <c r="J94" s="3">
+        <v>-26100</v>
+      </c>
+      <c r="K94" s="3">
         <v>300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-14500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-6000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-8300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-4500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-15100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>17800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>16100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-22300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>14500</v>
       </c>
-      <c r="AA94" s="3">
-        <v>0</v>
-      </c>
       <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-5100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7186,8 +7418,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7195,14 +7428,14 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
         <v>-200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-100</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
       <c r="H96" s="3">
         <v>0</v>
       </c>
@@ -7249,11 +7482,11 @@
         <v>0</v>
       </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-25500</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
         <v>0</v>
       </c>
@@ -7267,10 +7500,13 @@
         <v>0</v>
       </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7352,8 +7588,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7435,8 +7674,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7518,253 +7760,265 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-30900</v>
+        <v>-39400</v>
       </c>
       <c r="E100" s="3">
-        <v>-6700</v>
+        <v>-29000</v>
       </c>
       <c r="F100" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="G100" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="H100" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="J100" s="3">
+        <v>700</v>
+      </c>
+      <c r="K100" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="L100" s="3">
+        <v>4100</v>
+      </c>
+      <c r="M100" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="N100" s="3">
+        <v>-900</v>
+      </c>
+      <c r="O100" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="P100" s="3">
         <v>-18400</v>
       </c>
-      <c r="G100" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="H100" s="3">
-        <v>-6600</v>
-      </c>
-      <c r="I100" s="3">
-        <v>700</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-11200</v>
-      </c>
-      <c r="K100" s="3">
-        <v>4100</v>
-      </c>
-      <c r="L100" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="M100" s="3">
-        <v>-900</v>
-      </c>
-      <c r="N100" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="O100" s="3">
-        <v>-18400</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-5300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-16500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-22500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-12900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>11500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-30600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-18300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>21900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>21900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>55900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>2100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-220700</v>
+        <v>-209200</v>
       </c>
       <c r="E101" s="3">
-        <v>545200</v>
+        <v>-206800</v>
       </c>
       <c r="F101" s="3">
-        <v>70800</v>
+        <v>510800</v>
       </c>
       <c r="G101" s="3">
-        <v>19900</v>
+        <v>66300</v>
       </c>
       <c r="H101" s="3">
-        <v>10200</v>
+        <v>18600</v>
       </c>
       <c r="I101" s="3">
-        <v>17600</v>
+        <v>9600</v>
       </c>
       <c r="J101" s="3">
+        <v>16500</v>
+      </c>
+      <c r="K101" s="3">
         <v>-3600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-13500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-25700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-65700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>5500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>4800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>23400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>23700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>51500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>63500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>30300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>245700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>69900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>87800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-81800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>221100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>161900</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>22700</v>
       </c>
-      <c r="AC101" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-510600</v>
+        <v>-149800</v>
       </c>
       <c r="E102" s="3">
-        <v>381700</v>
+        <v>-478400</v>
       </c>
       <c r="F102" s="3">
-        <v>-112900</v>
+        <v>357600</v>
       </c>
       <c r="G102" s="3">
-        <v>-24300</v>
+        <v>-105800</v>
       </c>
       <c r="H102" s="3">
-        <v>14900</v>
+        <v>-22700</v>
       </c>
       <c r="I102" s="3">
-        <v>33700</v>
+        <v>14000</v>
       </c>
       <c r="J102" s="3">
+        <v>31500</v>
+      </c>
+      <c r="K102" s="3">
         <v>-52700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-132000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-64300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-102100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>54400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>149300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-16900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>44100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-405400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-217500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>638300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>33000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-86500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>53300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>152200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>452700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>257800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-21800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>188600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BBAR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BBAR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="92">
   <si>
     <t>BBAR</t>
   </si>
@@ -656,243 +656,251 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1012200</v>
+        <v>629700</v>
       </c>
       <c r="E8" s="3">
-        <v>1574100</v>
+        <v>865700</v>
       </c>
       <c r="F8" s="3">
-        <v>1747900</v>
+        <v>1300900</v>
       </c>
       <c r="G8" s="3">
-        <v>610400</v>
+        <v>1410200</v>
       </c>
       <c r="H8" s="3">
-        <v>953000</v>
+        <v>870000</v>
       </c>
       <c r="I8" s="3">
-        <v>320800</v>
+        <v>3157000</v>
       </c>
       <c r="J8" s="3">
+        <v>3254600</v>
+      </c>
+      <c r="K8" s="3">
         <v>275400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>160200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>259900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>95500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>437400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>410500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>727600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>254100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>377500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>248500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>494500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>386400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>501000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>401000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>728200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>327000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>240600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>166900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>139500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>130800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>121600</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>5</v>
+      <c r="D9" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E9" s="3">
+        <v>10200</v>
+      </c>
+      <c r="F9" s="3">
+        <v>11400</v>
+      </c>
+      <c r="G9" s="3">
+        <v>13700</v>
+      </c>
+      <c r="H9" s="3">
+        <v>10100</v>
+      </c>
+      <c r="I9" s="3">
+        <v>33800</v>
+      </c>
+      <c r="J9" s="3">
+        <v>46500</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>5</v>
@@ -954,31 +962,34 @@
       <c r="AD9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>618600</v>
+      </c>
+      <c r="E10" s="3">
+        <v>855500</v>
+      </c>
+      <c r="F10" s="3">
+        <v>1289500</v>
+      </c>
+      <c r="G10" s="3">
+        <v>1396500</v>
+      </c>
+      <c r="H10" s="3">
+        <v>859900</v>
+      </c>
+      <c r="I10" s="3">
+        <v>3123200</v>
+      </c>
+      <c r="J10" s="3">
+        <v>3208100</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -1040,8 +1051,11 @@
       <c r="AD10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1072,8 +1086,9 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1158,8 +1173,11 @@
       <c r="AD12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1244,31 +1262,34 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>1200</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1330,94 +1351,100 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-18700</v>
+        <v>20600</v>
       </c>
       <c r="E15" s="3">
-        <v>-12700</v>
+        <v>21900</v>
       </c>
       <c r="F15" s="3">
-        <v>-14700</v>
+        <v>10300</v>
       </c>
       <c r="G15" s="3">
-        <v>-4500</v>
+        <v>13600</v>
       </c>
       <c r="H15" s="3">
-        <v>-9800</v>
+        <v>12800</v>
       </c>
       <c r="I15" s="3">
-        <v>-3600</v>
+        <v>58000</v>
       </c>
       <c r="J15" s="3">
+        <v>41000</v>
+      </c>
+      <c r="K15" s="3">
         <v>-3900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-2300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-5200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-2300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-10900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-14600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-31700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-14100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-12800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-8000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-17500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-24600</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-25900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>-15300</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-26900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-27600</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-3800</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>-3000</v>
       </c>
       <c r="AB15" s="3">
         <v>-3000</v>
       </c>
       <c r="AC15" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="AD15" s="3">
         <v>-3300</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1445,180 +1472,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>349800</v>
+        <v>502300</v>
       </c>
       <c r="E17" s="3">
-        <v>635800</v>
+        <v>672800</v>
       </c>
       <c r="F17" s="3">
-        <v>864300</v>
+        <v>1216700</v>
       </c>
       <c r="G17" s="3">
-        <v>337300</v>
+        <v>1180400</v>
       </c>
       <c r="H17" s="3">
-        <v>495000</v>
+        <v>825200</v>
       </c>
       <c r="I17" s="3">
-        <v>162400</v>
+        <v>2464300</v>
       </c>
       <c r="J17" s="3">
+        <v>2771300</v>
+      </c>
+      <c r="K17" s="3">
         <v>138800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>79700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>122900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>44400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>187700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>199500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>348500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>118200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>182700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>98900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>199000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>153800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>256700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>242200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>377400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>172500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>140700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>91800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>63100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>55100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>52200</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>662500</v>
+        <v>127400</v>
       </c>
       <c r="E18" s="3">
-        <v>938200</v>
+        <v>192800</v>
       </c>
       <c r="F18" s="3">
-        <v>883600</v>
+        <v>84300</v>
       </c>
       <c r="G18" s="3">
-        <v>273000</v>
+        <v>229800</v>
       </c>
       <c r="H18" s="3">
-        <v>458000</v>
+        <v>44700</v>
       </c>
       <c r="I18" s="3">
-        <v>158400</v>
+        <v>692700</v>
       </c>
       <c r="J18" s="3">
+        <v>483300</v>
+      </c>
+      <c r="K18" s="3">
         <v>136600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>80500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>137000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>51200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>249700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>211000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>379000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>135900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>194700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>149600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>295400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>232700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>244300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>158800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>350800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>154500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>99900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>75100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>76300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>75700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>69400</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1649,203 +1683,210 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-477000</v>
+        <v>-400</v>
       </c>
       <c r="E20" s="3">
-        <v>-866600</v>
+        <v>-2700</v>
       </c>
       <c r="F20" s="3">
-        <v>-691300</v>
+        <v>4000</v>
       </c>
       <c r="G20" s="3">
-        <v>-257200</v>
+        <v>-500</v>
       </c>
       <c r="H20" s="3">
-        <v>-352100</v>
+        <v>-100</v>
       </c>
       <c r="I20" s="3">
-        <v>-130200</v>
+        <v>-8600</v>
       </c>
       <c r="J20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K20" s="3">
         <v>-104700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-66400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-115200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-43200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-199000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-172400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-317800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-118400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-161000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-104600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-193000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-177000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-255800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-63500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-122200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-56500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-41500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-18300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-32100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-38800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-33500</v>
       </c>
     </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>206100</v>
+        <v>148400</v>
       </c>
       <c r="E21" s="3">
-        <v>82300</v>
+        <v>217500</v>
       </c>
       <c r="F21" s="3">
-        <v>207800</v>
+        <v>90500</v>
       </c>
       <c r="G21" s="3">
-        <v>22900</v>
+        <v>243900</v>
       </c>
       <c r="H21" s="3">
-        <v>113200</v>
+        <v>57500</v>
       </c>
       <c r="I21" s="3">
-        <v>31100</v>
+        <v>759300</v>
       </c>
       <c r="J21" s="3">
+        <v>522900</v>
+      </c>
+      <c r="K21" s="3">
         <v>36500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>17200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>26200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>9900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>61800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>51800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>78000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>24200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>46500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>54400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>118400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>67300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>14400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>107800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>249700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>111500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>61800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>59700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>47300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>40100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>36100</v>
       </c>
     </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1907,180 +1948,189 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>185500</v>
+        <v>127700</v>
       </c>
       <c r="E23" s="3">
-        <v>71600</v>
+        <v>195600</v>
       </c>
       <c r="F23" s="3">
-        <v>192300</v>
+        <v>80300</v>
       </c>
       <c r="G23" s="3">
-        <v>15900</v>
+        <v>228700</v>
       </c>
       <c r="H23" s="3">
-        <v>105900</v>
+        <v>43600</v>
       </c>
       <c r="I23" s="3">
-        <v>28200</v>
+        <v>701300</v>
       </c>
       <c r="J23" s="3">
+        <v>481900</v>
+      </c>
+      <c r="K23" s="3">
         <v>31900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>14100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>21900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>8000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>50700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>38600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>61200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>17500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>33700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>45000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>102400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>55600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-11500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>95300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>228600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>98000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>58400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>56700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>44200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>36800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>35900</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>68100</v>
+        <v>25400</v>
       </c>
       <c r="E24" s="3">
-        <v>29500</v>
+        <v>71800</v>
       </c>
       <c r="F24" s="3">
-        <v>99700</v>
+        <v>33100</v>
       </c>
       <c r="G24" s="3">
-        <v>5600</v>
+        <v>118600</v>
       </c>
       <c r="H24" s="3">
-        <v>37300</v>
+        <v>15300</v>
       </c>
       <c r="I24" s="3">
-        <v>8900</v>
+        <v>261800</v>
       </c>
       <c r="J24" s="3">
+        <v>151400</v>
+      </c>
+      <c r="K24" s="3">
         <v>7800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-7800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>11100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>11900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-29400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-3000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>21700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>11100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>44400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>34000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>21500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>11100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>72200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>42000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>18500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>15400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>12700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>11000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>12400</v>
       </c>
     </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2165,180 +2215,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>117400</v>
+        <v>102300</v>
       </c>
       <c r="E26" s="3">
-        <v>42100</v>
+        <v>123800</v>
       </c>
       <c r="F26" s="3">
-        <v>92600</v>
+        <v>47200</v>
       </c>
       <c r="G26" s="3">
-        <v>10300</v>
+        <v>110200</v>
       </c>
       <c r="H26" s="3">
-        <v>68600</v>
+        <v>28200</v>
       </c>
       <c r="I26" s="3">
-        <v>19300</v>
+        <v>439500</v>
       </c>
       <c r="J26" s="3">
+        <v>330500</v>
+      </c>
+      <c r="K26" s="3">
         <v>24000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>10700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>29700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>39600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>26700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>90600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>20500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>12100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>33900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>58000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>21700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-33000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>84100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>156400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>56000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>39900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>41400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>31500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>25900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>115400</v>
+        <v>102800</v>
       </c>
       <c r="E27" s="3">
-        <v>42900</v>
+        <v>121700</v>
       </c>
       <c r="F27" s="3">
-        <v>92900</v>
+        <v>48100</v>
       </c>
       <c r="G27" s="3">
-        <v>10000</v>
+        <v>110500</v>
       </c>
       <c r="H27" s="3">
-        <v>68200</v>
+        <v>27500</v>
       </c>
       <c r="I27" s="3">
-        <v>19300</v>
+        <v>435100</v>
       </c>
       <c r="J27" s="3">
+        <v>330700</v>
+      </c>
+      <c r="K27" s="3">
         <v>24400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>10900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>30100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>39500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>26700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>91000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>20800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>13000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>33900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>57200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>21200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-28600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>79700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>156400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>56000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>39900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>40800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>31100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>25500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2423,8 +2482,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2509,8 +2571,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2595,8 +2660,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2681,180 +2749,189 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>477000</v>
+        <v>400</v>
       </c>
       <c r="E32" s="3">
-        <v>866600</v>
+        <v>2700</v>
       </c>
       <c r="F32" s="3">
-        <v>691300</v>
+        <v>-4000</v>
       </c>
       <c r="G32" s="3">
-        <v>257200</v>
+        <v>500</v>
       </c>
       <c r="H32" s="3">
-        <v>352100</v>
+        <v>100</v>
       </c>
       <c r="I32" s="3">
-        <v>130200</v>
+        <v>8600</v>
       </c>
       <c r="J32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="K32" s="3">
         <v>104700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>66400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>115200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>43200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>199000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>172400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>317800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>118400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>161000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>104600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>193000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>177000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>255800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>63500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>122200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>56500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>41500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>18300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>32100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>38800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>33500</v>
       </c>
     </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>115400</v>
+        <v>102800</v>
       </c>
       <c r="E33" s="3">
-        <v>42900</v>
+        <v>121700</v>
       </c>
       <c r="F33" s="3">
-        <v>92900</v>
+        <v>48100</v>
       </c>
       <c r="G33" s="3">
-        <v>10000</v>
+        <v>110500</v>
       </c>
       <c r="H33" s="3">
-        <v>68200</v>
+        <v>27500</v>
       </c>
       <c r="I33" s="3">
-        <v>19300</v>
+        <v>435100</v>
       </c>
       <c r="J33" s="3">
+        <v>330700</v>
+      </c>
+      <c r="K33" s="3">
         <v>24400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>10900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>30100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>39500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>26700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>91000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>20800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>13000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>33900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>57200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>21200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-28600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>79700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>156400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>56000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>39900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>40800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>31100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>25500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2939,185 +3016,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>115400</v>
+        <v>102800</v>
       </c>
       <c r="E35" s="3">
-        <v>42900</v>
+        <v>121700</v>
       </c>
       <c r="F35" s="3">
-        <v>92900</v>
+        <v>48100</v>
       </c>
       <c r="G35" s="3">
-        <v>10000</v>
+        <v>110500</v>
       </c>
       <c r="H35" s="3">
-        <v>68200</v>
+        <v>27500</v>
       </c>
       <c r="I35" s="3">
-        <v>19300</v>
+        <v>435100</v>
       </c>
       <c r="J35" s="3">
+        <v>330700</v>
+      </c>
+      <c r="K35" s="3">
         <v>24400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>10900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>30100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>39500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>26700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>91000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>20800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>13000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>33900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>57200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>21200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-28600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>79700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>156400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>56000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>39900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>40800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>31100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>25500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3148,8 +3234,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3180,203 +3267,210 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1434300</v>
+        <v>2070200</v>
       </c>
       <c r="E41" s="3">
-        <v>1235500</v>
+        <v>868600</v>
       </c>
       <c r="F41" s="3">
-        <v>1130600</v>
+        <v>941600</v>
       </c>
       <c r="G41" s="3">
-        <v>478500</v>
+        <v>968600</v>
       </c>
       <c r="H41" s="3">
-        <v>432200</v>
+        <v>773300</v>
       </c>
       <c r="I41" s="3">
-        <v>379100</v>
+        <v>776600</v>
       </c>
       <c r="J41" s="3">
+        <v>620200</v>
+      </c>
+      <c r="K41" s="3">
         <v>290000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>212500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>204300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>224900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1192000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>836700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>837900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1195800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1398000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>804800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>676300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1410000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2158700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>898700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>947900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1060300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1235900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1103600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>735900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>535600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>596800</v>
       </c>
     </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>346500</v>
+        <v>1142900</v>
       </c>
       <c r="E42" s="3">
-        <v>334200</v>
+        <v>627100</v>
       </c>
       <c r="F42" s="3">
-        <v>298600</v>
+        <v>2659000</v>
       </c>
       <c r="G42" s="3">
-        <v>133800</v>
+        <v>1786400</v>
       </c>
       <c r="H42" s="3">
-        <v>95200</v>
+        <v>1234500</v>
       </c>
       <c r="I42" s="3">
-        <v>40600</v>
+        <v>1224200</v>
       </c>
       <c r="J42" s="3">
+        <v>864700</v>
+      </c>
+      <c r="K42" s="3">
         <v>45600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>36800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>38900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>22800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>31500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>51000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>45500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>70200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>67700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>74900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>98000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>151400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>115000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>141800</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>107400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>118300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>212600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>96300</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>104300</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>96300</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>279000</v>
       </c>
     </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
+        <v>132600</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
+        <v>112100</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
+        <v>109400</v>
       </c>
       <c r="H43" s="3">
-        <v>0</v>
+        <v>226900</v>
       </c>
       <c r="I43" s="3">
-        <v>0</v>
+        <v>138900</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>137400</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -3438,31 +3532,34 @@
       <c r="AD43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E44" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I44" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J44" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3524,31 +3621,34 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>48300</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>328300</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>56400</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>56700</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>63500</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>55700</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>71200</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -3610,31 +3710,34 @@
       <c r="AD45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>3261400</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>2700300</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>4328800</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>3381600</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>2912800</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>3095200</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>2884000</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -3696,266 +3799,278 @@
       <c r="AD46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>18900</v>
+        <v>2674700</v>
       </c>
       <c r="E47" s="3">
-        <v>16500</v>
+        <v>2502600</v>
       </c>
       <c r="F47" s="3">
-        <v>12900</v>
+        <v>1049000</v>
       </c>
       <c r="G47" s="3">
-        <v>7800</v>
+        <v>955200</v>
       </c>
       <c r="H47" s="3">
-        <v>5800</v>
+        <v>3184700</v>
       </c>
       <c r="I47" s="3">
-        <v>4800</v>
+        <v>3991400</v>
       </c>
       <c r="J47" s="3">
+        <v>3368600</v>
+      </c>
+      <c r="K47" s="3">
         <v>3600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>11300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>8400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>8800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>9900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>13600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>8300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>7700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>11200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>14500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>2800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>22000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>20300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>23800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>24200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>15900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>15200</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>10900</v>
       </c>
     </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>577100</v>
+        <v>604600</v>
       </c>
       <c r="E48" s="3">
-        <v>484300</v>
+        <v>608400</v>
       </c>
       <c r="F48" s="3">
-        <v>310100</v>
+        <v>543100</v>
       </c>
       <c r="G48" s="3">
-        <v>200100</v>
+        <v>368900</v>
       </c>
       <c r="H48" s="3">
-        <v>148500</v>
+        <v>549600</v>
       </c>
       <c r="I48" s="3">
-        <v>120800</v>
+        <v>556100</v>
       </c>
       <c r="J48" s="3">
+        <v>555800</v>
+      </c>
+      <c r="K48" s="3">
         <v>99900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>89900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>81100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>68800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>280700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>192100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>177700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>234900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>318100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>188100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>176400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>271100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>364900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>121500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>125900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>126800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>133200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>124500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>133800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>149200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>70200</v>
       </c>
     </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>60100</v>
+        <v>0</v>
       </c>
       <c r="E49" s="3">
-        <v>52900</v>
+        <v>0</v>
       </c>
       <c r="F49" s="3">
-        <v>34500</v>
+        <v>0</v>
       </c>
       <c r="G49" s="3">
-        <v>21500</v>
+        <v>0</v>
       </c>
       <c r="H49" s="3">
-        <v>15300</v>
+        <v>59000</v>
       </c>
       <c r="I49" s="3">
-        <v>12100</v>
+        <v>57400</v>
       </c>
       <c r="J49" s="3">
+        <v>55700</v>
+      </c>
+      <c r="K49" s="3">
         <v>10000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>6900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>20300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>12300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>10200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>11900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>14600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>8100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>6700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>9100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>10900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>6600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>6300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>5900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>6900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>8100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>7900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>7400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4040,8 +4155,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4126,94 +4244,100 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>27800</v>
+        <v>704000</v>
       </c>
       <c r="E52" s="3">
-        <v>33000</v>
+        <v>378500</v>
       </c>
       <c r="F52" s="3">
-        <v>3800</v>
+        <v>392200</v>
       </c>
       <c r="G52" s="3">
-        <v>2900</v>
+        <v>382800</v>
       </c>
       <c r="H52" s="3">
-        <v>2400</v>
+        <v>515200</v>
       </c>
       <c r="I52" s="3">
-        <v>1900</v>
+        <v>403000</v>
       </c>
       <c r="J52" s="3">
+        <v>335400</v>
+      </c>
+      <c r="K52" s="3">
         <v>1800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>27700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>52100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>37000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>34100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>75300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>40000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>35600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>6200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>9300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>4800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>7800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>13200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4298,94 +4422,100 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>9923000</v>
+        <v>12943400</v>
       </c>
       <c r="E54" s="3">
-        <v>8428700</v>
+        <v>10462000</v>
       </c>
       <c r="F54" s="3">
-        <v>6369500</v>
+        <v>9452000</v>
       </c>
       <c r="G54" s="3">
-        <v>4037300</v>
+        <v>7575300</v>
       </c>
       <c r="H54" s="3">
-        <v>3258600</v>
+        <v>11090500</v>
       </c>
       <c r="I54" s="3">
-        <v>2454200</v>
+        <v>12207700</v>
       </c>
       <c r="J54" s="3">
+        <v>11291800</v>
+      </c>
+      <c r="K54" s="3">
         <v>2037200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1777500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1658300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1379500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5679100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3940200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3725500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4629800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6479800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3680600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3382600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5085500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6320300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>4256700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>4168600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>4234100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>4812100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>4532100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>3926900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>3707300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>3729900</v>
       </c>
     </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4416,8 +4546,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4448,117 +4579,121 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1103600</v>
+        <v>8795300</v>
       </c>
       <c r="E57" s="3">
-        <v>718500</v>
+        <v>6371200</v>
       </c>
       <c r="F57" s="3">
-        <v>533300</v>
+        <v>5569500</v>
       </c>
       <c r="G57" s="3">
-        <v>300700</v>
+        <v>4501400</v>
       </c>
       <c r="H57" s="3">
-        <v>354800</v>
+        <v>7410500</v>
       </c>
       <c r="I57" s="3">
-        <v>202100</v>
+        <v>7830100</v>
       </c>
       <c r="J57" s="3">
+        <v>7521300</v>
+      </c>
+      <c r="K57" s="3">
         <v>167400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>134500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>124000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>104100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>426700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>286900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>249200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>354700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>443700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>274100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>200400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>455500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>435500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>346300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>251100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>320900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>398200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>316500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>284300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>301300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>275600</v>
       </c>
     </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>43100</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>197200</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>5500</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -4620,117 +4755,123 @@
       <c r="AD58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>172400</v>
+        <v>9500</v>
       </c>
       <c r="E59" s="3">
-        <v>299100</v>
+        <v>271800</v>
       </c>
       <c r="F59" s="3">
-        <v>302100</v>
+        <v>281700</v>
       </c>
       <c r="G59" s="3">
-        <v>110000</v>
+        <v>431500</v>
       </c>
       <c r="H59" s="3">
-        <v>91500</v>
+        <v>207500</v>
       </c>
       <c r="I59" s="3">
-        <v>64900</v>
+        <v>376300</v>
       </c>
       <c r="J59" s="3">
+        <v>239300</v>
+      </c>
+      <c r="K59" s="3">
         <v>50400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>44900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>52600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>48200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>222400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>140900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>131000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>146300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>232300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>74200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>69900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>165500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>193200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>105900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>91000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>97800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>97400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>80000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>57500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>49900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>54200</v>
       </c>
     </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>8848000</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>6962000</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>5968400</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>5070600</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>7805000</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>8365400</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>7907800</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -4792,180 +4933,189 @@
       <c r="AD60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>214700</v>
+        <v>190800</v>
       </c>
       <c r="E61" s="3">
-        <v>27100</v>
+        <v>750300</v>
       </c>
       <c r="F61" s="3">
-        <v>24400</v>
+        <v>494900</v>
       </c>
       <c r="G61" s="3">
-        <v>9300</v>
+        <v>410300</v>
       </c>
       <c r="H61" s="3">
-        <v>6000</v>
+        <v>533900</v>
       </c>
       <c r="I61" s="3">
-        <v>5200</v>
+        <v>663000</v>
       </c>
       <c r="J61" s="3">
+        <v>575600</v>
+      </c>
+      <c r="K61" s="3">
         <v>4300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>16100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>12600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>12200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>18600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>27800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>17400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>16600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>25300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>35200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>26400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>21300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>23100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>200</v>
       </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
       <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
         <v>13700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>9600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>78300</v>
       </c>
     </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>39900</v>
+        <v>1439800</v>
       </c>
       <c r="E62" s="3">
-        <v>57500</v>
+        <v>426800</v>
       </c>
       <c r="F62" s="3">
-        <v>45900</v>
+        <v>503700</v>
       </c>
       <c r="G62" s="3">
-        <v>39800</v>
+        <v>298000</v>
       </c>
       <c r="H62" s="3">
-        <v>27100</v>
+        <v>481400</v>
       </c>
       <c r="I62" s="3">
-        <v>16200</v>
+        <v>905400</v>
       </c>
       <c r="J62" s="3">
+        <v>574600</v>
+      </c>
+      <c r="K62" s="3">
         <v>16000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>15800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>8100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>20500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>76200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>44000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>42100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>65800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>108400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>65500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>68700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>111800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>150400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>79000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>75500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>42900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>49900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>47400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>54400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>62500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>46300</v>
       </c>
     </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5050,8 +5200,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5136,8 +5289,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5222,94 +5378,100 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>7764400</v>
+        <v>10478600</v>
       </c>
       <c r="E66" s="3">
-        <v>6246300</v>
+        <v>8150000</v>
       </c>
       <c r="F66" s="3">
-        <v>4907100</v>
+        <v>6973900</v>
       </c>
       <c r="G66" s="3">
-        <v>3254100</v>
+        <v>5813800</v>
       </c>
       <c r="H66" s="3">
-        <v>2677700</v>
+        <v>8906100</v>
       </c>
       <c r="I66" s="3">
-        <v>1982900</v>
+        <v>9998600</v>
       </c>
       <c r="J66" s="3">
+        <v>9091700</v>
+      </c>
+      <c r="K66" s="3">
         <v>1662300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1447700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1387000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1154700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4800300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3313100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3164100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3896400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5522700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3027400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2801800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4222000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5280700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3680100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3651100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3749600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4289000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4047700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3445800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3184200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3299200</v>
       </c>
     </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5340,8 +5502,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5426,8 +5589,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5512,8 +5678,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5598,8 +5767,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5684,94 +5856,100 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1377300</v>
+        <v>278800</v>
       </c>
       <c r="E72" s="3">
-        <v>1523400</v>
+        <v>1313500</v>
       </c>
       <c r="F72" s="3">
-        <v>1027800</v>
+        <v>1481200</v>
       </c>
       <c r="G72" s="3">
-        <v>499600</v>
+        <v>1007700</v>
       </c>
       <c r="H72" s="3">
-        <v>370600</v>
+        <v>1426700</v>
       </c>
       <c r="I72" s="3">
-        <v>301400</v>
+        <v>1415300</v>
       </c>
       <c r="J72" s="3">
+        <v>1433700</v>
+      </c>
+      <c r="K72" s="3">
         <v>235300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>202900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>160600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>130500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>499000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>357800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>314900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>411700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>527200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>397400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>343200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>505000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>570400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>497900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>436200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>400900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>419200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>380500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>368900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>396500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>304100</v>
       </c>
     </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5856,8 +6034,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5942,8 +6123,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6028,94 +6212,100 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2158600</v>
+        <v>2427300</v>
       </c>
       <c r="E76" s="3">
-        <v>2182300</v>
+        <v>2275900</v>
       </c>
       <c r="F76" s="3">
-        <v>1462400</v>
+        <v>2447300</v>
       </c>
       <c r="G76" s="3">
-        <v>783100</v>
+        <v>1739300</v>
       </c>
       <c r="H76" s="3">
-        <v>580900</v>
+        <v>2151300</v>
       </c>
       <c r="I76" s="3">
-        <v>471300</v>
+        <v>2176300</v>
       </c>
       <c r="J76" s="3">
+        <v>2168600</v>
+      </c>
+      <c r="K76" s="3">
         <v>374900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>329800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>271200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>224900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>878700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>627200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>561400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>733400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>957100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>653200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>580800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>863500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1039600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>576700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>517500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>484600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>523100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>484400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>481100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>523100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>430700</v>
       </c>
     </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6200,185 +6390,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>115400</v>
+        <v>102800</v>
       </c>
       <c r="E81" s="3">
-        <v>42900</v>
+        <v>121700</v>
       </c>
       <c r="F81" s="3">
-        <v>92900</v>
+        <v>48100</v>
       </c>
       <c r="G81" s="3">
-        <v>10000</v>
+        <v>110500</v>
       </c>
       <c r="H81" s="3">
-        <v>68200</v>
+        <v>27500</v>
       </c>
       <c r="I81" s="3">
-        <v>19300</v>
+        <v>435100</v>
       </c>
       <c r="J81" s="3">
+        <v>330700</v>
+      </c>
+      <c r="K81" s="3">
         <v>24400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>10900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>30100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>39500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>26700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>91000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>20800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>13000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>33900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>57200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>21200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-28600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>79700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>156400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>56000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>39900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>40800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>31100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>25500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6409,94 +6608,98 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>20600</v>
+        <v>14700</v>
       </c>
       <c r="E83" s="3">
-        <v>10700</v>
+        <v>51600</v>
       </c>
       <c r="F83" s="3">
-        <v>15500</v>
+        <v>46200</v>
       </c>
       <c r="G83" s="3">
-        <v>7100</v>
+        <v>86300</v>
       </c>
       <c r="H83" s="3">
-        <v>7300</v>
+        <v>46200</v>
       </c>
       <c r="I83" s="3">
-        <v>2900</v>
+        <v>34200</v>
       </c>
       <c r="J83" s="3">
+        <v>28700</v>
+      </c>
+      <c r="K83" s="3">
         <v>4700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>11100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>13100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>16800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>6700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>12800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>9500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>16000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>11600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>25900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>12500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>21100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>13400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>3400</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>3000</v>
       </c>
       <c r="AB83" s="3">
         <v>3000</v>
       </c>
       <c r="AC83" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AD83" s="3">
         <v>3300</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6581,8 +6784,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6667,8 +6873,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6753,8 +6962,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6839,8 +7051,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6925,94 +7140,100 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>118500</v>
+      <c r="D89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E89" s="3">
-        <v>-217500</v>
+        <v>-920700</v>
       </c>
       <c r="F89" s="3">
-        <v>-114400</v>
+        <v>-1147600</v>
       </c>
       <c r="G89" s="3">
-        <v>-148000</v>
+        <v>-1902300</v>
       </c>
       <c r="H89" s="3">
-        <v>-32000</v>
+        <v>-2471000</v>
       </c>
       <c r="I89" s="3">
-        <v>13000</v>
+        <v>-6616800</v>
       </c>
       <c r="J89" s="3">
+        <v>-3450000</v>
+      </c>
+      <c r="K89" s="3">
         <v>38700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-38200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-117900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-61000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>82500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-7600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>88800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>157000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-19300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>50100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-415200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-247300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>611600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-180800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-156000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-62700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>260600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>198900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>38000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-38900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>154700</v>
       </c>
     </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7043,94 +7264,98 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>-21954000</v>
+      <c r="D91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E91" s="3">
-        <v>-24199800</v>
+        <v>-24100</v>
       </c>
       <c r="F91" s="3">
-        <v>-30567700</v>
+        <v>-28200</v>
       </c>
       <c r="G91" s="3">
-        <v>-6606200</v>
+        <v>-37800</v>
       </c>
       <c r="H91" s="3">
-        <v>-3044100</v>
+        <v>-18900</v>
       </c>
       <c r="I91" s="3">
-        <v>-1859800</v>
+        <v>-42900</v>
       </c>
       <c r="J91" s="3">
+        <v>-34500</v>
+      </c>
+      <c r="K91" s="3">
         <v>-12277100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-312900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2694300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1125700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-10201100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2576100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1792900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-7800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-5000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-14400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-4000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-9200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-4500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-22400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>7300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-4800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-5200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7215,8 +7440,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7301,94 +7529,100 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>-22800</v>
+      <c r="D94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E94" s="3">
-        <v>-25200</v>
+        <v>-20800</v>
       </c>
       <c r="F94" s="3">
-        <v>-29800</v>
+        <v>-28200</v>
       </c>
       <c r="G94" s="3">
-        <v>-8100</v>
+        <v>-38800</v>
       </c>
       <c r="H94" s="3">
-        <v>-4600</v>
+        <v>-18900</v>
       </c>
       <c r="I94" s="3">
-        <v>-2400</v>
+        <v>-37100</v>
       </c>
       <c r="J94" s="3">
+        <v>-42400</v>
+      </c>
+      <c r="K94" s="3">
         <v>-26100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-14500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-8300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-4500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-15100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>17800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>16100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-22300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>14500</v>
       </c>
-      <c r="AB94" s="3">
-        <v>0</v>
-      </c>
       <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-5100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7419,31 +7653,32 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>-200</v>
+        <v>53600</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G96" s="3">
-        <v>-100</v>
+        <v>200</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+        <v>300</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -7485,11 +7720,11 @@
         <v>0</v>
       </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-25500</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
         <v>0</v>
       </c>
@@ -7503,10 +7738,13 @@
         <v>0</v>
       </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7591,8 +7829,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7677,8 +7918,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7763,262 +8007,274 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>-39400</v>
+      <c r="D100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E100" s="3">
-        <v>-29000</v>
+        <v>1408400</v>
       </c>
       <c r="F100" s="3">
-        <v>-6300</v>
+        <v>1608700</v>
       </c>
       <c r="G100" s="3">
-        <v>-17200</v>
+        <v>2339300</v>
       </c>
       <c r="H100" s="3">
-        <v>-4200</v>
+        <v>2673900</v>
       </c>
       <c r="I100" s="3">
-        <v>-6200</v>
+        <v>7590600</v>
       </c>
       <c r="J100" s="3">
+        <v>4933100</v>
+      </c>
+      <c r="K100" s="3">
         <v>700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-11200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>4100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-3400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-18400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-9800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-5300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-16500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-22500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-12900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>11500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-30600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-18300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>21900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-8000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>21900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>55900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>2100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-209200</v>
+        <v>182200</v>
       </c>
       <c r="E101" s="3">
-        <v>-206800</v>
+        <v>120000</v>
       </c>
       <c r="F101" s="3">
-        <v>510800</v>
+        <v>171000</v>
       </c>
       <c r="G101" s="3">
-        <v>66300</v>
+        <v>218900</v>
       </c>
       <c r="H101" s="3">
-        <v>18600</v>
+        <v>-69800</v>
       </c>
       <c r="I101" s="3">
-        <v>9600</v>
+        <v>-204200</v>
       </c>
       <c r="J101" s="3">
+        <v>7700</v>
+      </c>
+      <c r="K101" s="3">
         <v>16500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-3600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-13500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-25700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-65700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>5500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>4800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>23400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>23700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>51500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>63500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>30300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>245700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>69900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>87800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-81800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>221100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>161900</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>22700</v>
       </c>
-      <c r="AD101" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-149800</v>
+        <v>0</v>
       </c>
       <c r="E102" s="3">
-        <v>-478400</v>
+        <v>246300</v>
       </c>
       <c r="F102" s="3">
-        <v>357600</v>
+        <v>201000</v>
       </c>
       <c r="G102" s="3">
-        <v>-105800</v>
+        <v>1005700</v>
       </c>
       <c r="H102" s="3">
-        <v>-22700</v>
+        <v>366100</v>
       </c>
       <c r="I102" s="3">
-        <v>14000</v>
+        <v>1056700</v>
       </c>
       <c r="J102" s="3">
+        <v>1611600</v>
+      </c>
+      <c r="K102" s="3">
         <v>31500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-52700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-132000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-64300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-102100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>54400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>149300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-16900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>44100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-405400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-217500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>638300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>33000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-86500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>53300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>152200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>452700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>257800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-21800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>188600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BBAR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BBAR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="92">
   <si>
     <t>BBAR</t>
   </si>
@@ -656,255 +656,261 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>776400</v>
+      </c>
+      <c r="E8" s="3">
         <v>629700</v>
       </c>
-      <c r="E8" s="3">
-        <v>865700</v>
-      </c>
       <c r="F8" s="3">
+        <v>1119000</v>
+      </c>
+      <c r="G8" s="3">
         <v>1300900</v>
       </c>
-      <c r="G8" s="3">
-        <v>1410200</v>
-      </c>
       <c r="H8" s="3">
-        <v>870000</v>
+        <v>2116200</v>
       </c>
       <c r="I8" s="3">
-        <v>3157000</v>
+        <v>2688200</v>
       </c>
       <c r="J8" s="3">
+        <v>3861400</v>
+      </c>
+      <c r="K8" s="3">
         <v>3254600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>275400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>160200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>259900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>95500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>437400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>410500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>727600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>254100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>377500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>248500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>494500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>386400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>501000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>401000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>728200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>327000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>240600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>166900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>139500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>130800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>121600</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E9" s="3">
         <v>11100</v>
       </c>
-      <c r="E9" s="3">
-        <v>10200</v>
-      </c>
       <c r="F9" s="3">
+        <v>12700</v>
+      </c>
+      <c r="G9" s="3">
         <v>11400</v>
       </c>
-      <c r="G9" s="3">
-        <v>13700</v>
-      </c>
       <c r="H9" s="3">
-        <v>10100</v>
+        <v>18200</v>
       </c>
       <c r="I9" s="3">
-        <v>33800</v>
+        <v>31200</v>
       </c>
       <c r="J9" s="3">
+        <v>42500</v>
+      </c>
+      <c r="K9" s="3">
         <v>46500</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>5</v>
       </c>
@@ -965,35 +971,38 @@
       <c r="AE9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>760800</v>
+      </c>
+      <c r="E10" s="3">
         <v>618600</v>
       </c>
-      <c r="E10" s="3">
-        <v>855500</v>
-      </c>
       <c r="F10" s="3">
+        <v>1106300</v>
+      </c>
+      <c r="G10" s="3">
         <v>1289500</v>
       </c>
-      <c r="G10" s="3">
-        <v>1396500</v>
-      </c>
       <c r="H10" s="3">
-        <v>859900</v>
+        <v>2097900</v>
       </c>
       <c r="I10" s="3">
-        <v>3123200</v>
+        <v>2657000</v>
       </c>
       <c r="J10" s="3">
+        <v>3819000</v>
+      </c>
+      <c r="K10" s="3">
         <v>3208100</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1054,8 +1063,11 @@
       <c r="AE10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1087,8 +1099,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1176,8 +1189,11 @@
       <c r="AE12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1265,13 +1281,16 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
+      <c r="D14" s="3">
+        <v>4000</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>5</v>
@@ -1279,11 +1298,11 @@
       <c r="F14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="3">
-        <v>1600</v>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H14" s="3">
-        <v>1200</v>
+        <v>6900</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>5</v>
@@ -1291,8 +1310,8 @@
       <c r="J14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1354,97 +1373,103 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>20600</v>
+        <v>17800</v>
       </c>
       <c r="E15" s="3">
+        <v>9800</v>
+      </c>
+      <c r="F15" s="3">
         <v>21900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>10300</v>
       </c>
-      <c r="G15" s="3">
-        <v>13600</v>
-      </c>
       <c r="H15" s="3">
-        <v>12800</v>
+        <v>17400</v>
       </c>
       <c r="I15" s="3">
+        <v>28200</v>
+      </c>
+      <c r="J15" s="3">
         <v>58000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>41000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-3900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-2300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-5200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-2300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-10900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-14600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-31700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-14100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-12800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-8000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-17500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-24600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>-25900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-15300</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-26900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-27600</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>-3800</v>
-      </c>
-      <c r="AB15" s="3">
-        <v>-3000</v>
       </c>
       <c r="AC15" s="3">
         <v>-3000</v>
       </c>
       <c r="AD15" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="AE15" s="3">
         <v>-3300</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1473,186 +1498,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>731000</v>
+      </c>
+      <c r="E17" s="3">
         <v>502300</v>
       </c>
-      <c r="E17" s="3">
-        <v>672800</v>
-      </c>
       <c r="F17" s="3">
+        <v>893200</v>
+      </c>
+      <c r="G17" s="3">
         <v>1216700</v>
       </c>
-      <c r="G17" s="3">
-        <v>1180400</v>
-      </c>
       <c r="H17" s="3">
-        <v>825200</v>
+        <v>1743800</v>
       </c>
       <c r="I17" s="3">
-        <v>2464300</v>
+        <v>2553700</v>
       </c>
       <c r="J17" s="3">
+        <v>3037000</v>
+      </c>
+      <c r="K17" s="3">
         <v>2771300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>138800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>79700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>122900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>44400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>187700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>199500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>348500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>118200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>182700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>98900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>199000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>153800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>256700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>242200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>377400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>172500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>140700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>91800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>63100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>55100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>52200</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>45400</v>
+      </c>
+      <c r="E18" s="3">
         <v>127400</v>
       </c>
-      <c r="E18" s="3">
-        <v>192800</v>
-      </c>
       <c r="F18" s="3">
+        <v>225800</v>
+      </c>
+      <c r="G18" s="3">
         <v>84300</v>
       </c>
-      <c r="G18" s="3">
-        <v>229800</v>
-      </c>
       <c r="H18" s="3">
-        <v>44700</v>
+        <v>372400</v>
       </c>
       <c r="I18" s="3">
-        <v>692700</v>
+        <v>134500</v>
       </c>
       <c r="J18" s="3">
+        <v>824500</v>
+      </c>
+      <c r="K18" s="3">
         <v>483300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>136600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>80500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>137000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>51200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>249700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>211000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>379000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>135900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>194700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>149600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>295400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>232700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>244300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>158800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>350800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>154500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>99900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>75100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>76300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>75700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>69400</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1684,186 +1716,193 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E20" s="3">
         <v>-400</v>
       </c>
-      <c r="E20" s="3">
-        <v>-2700</v>
-      </c>
       <c r="F20" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="G20" s="3">
         <v>4000</v>
       </c>
-      <c r="G20" s="3">
-        <v>-500</v>
-      </c>
       <c r="H20" s="3">
-        <v>-100</v>
+        <v>-400</v>
       </c>
       <c r="I20" s="3">
-        <v>-8600</v>
+        <v>-200</v>
       </c>
       <c r="J20" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="K20" s="3">
         <v>1300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-104700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-66400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-115200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-43200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-199000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-172400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-317800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-118400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-161000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-104600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-193000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-177000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-255800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-63500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-122200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-56500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-41500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-18300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-32100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-38800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-33500</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>148400</v>
+        <v>64000</v>
       </c>
       <c r="E21" s="3">
-        <v>217500</v>
+        <v>137500</v>
       </c>
       <c r="F21" s="3">
+        <v>250400</v>
+      </c>
+      <c r="G21" s="3">
         <v>90500</v>
       </c>
-      <c r="G21" s="3">
-        <v>243900</v>
-      </c>
       <c r="H21" s="3">
-        <v>57500</v>
+        <v>390100</v>
       </c>
       <c r="I21" s="3">
-        <v>759300</v>
+        <v>162800</v>
       </c>
       <c r="J21" s="3">
+        <v>892000</v>
+      </c>
+      <c r="K21" s="3">
         <v>522900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>36500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>17200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>26200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>9900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>61800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>51800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>78000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>24200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>46500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>54400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>118400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>67300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>14400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>107800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>249700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>111500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>61800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>59700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>47300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>40100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>36100</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1888,8 +1927,8 @@
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1951,186 +1990,195 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>42100</v>
+      </c>
+      <c r="E23" s="3">
         <v>127700</v>
       </c>
-      <c r="E23" s="3">
-        <v>195600</v>
-      </c>
       <c r="F23" s="3">
+        <v>228400</v>
+      </c>
+      <c r="G23" s="3">
         <v>80300</v>
       </c>
-      <c r="G23" s="3">
-        <v>228700</v>
-      </c>
       <c r="H23" s="3">
-        <v>43600</v>
+        <v>365900</v>
       </c>
       <c r="I23" s="3">
-        <v>701300</v>
+        <v>134600</v>
       </c>
       <c r="J23" s="3">
+        <v>834000</v>
+      </c>
+      <c r="K23" s="3">
         <v>481900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>31900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>14100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>21900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>8000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>50700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>38600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>61200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>17500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>33700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>45000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>102400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>55600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-11500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>95300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>228600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>98000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>58400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>56700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>44200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>36800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>35900</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-41800</v>
+      </c>
+      <c r="E24" s="3">
         <v>25400</v>
       </c>
-      <c r="E24" s="3">
-        <v>71800</v>
-      </c>
       <c r="F24" s="3">
+        <v>84300</v>
+      </c>
+      <c r="G24" s="3">
         <v>33100</v>
       </c>
-      <c r="G24" s="3">
-        <v>118600</v>
-      </c>
       <c r="H24" s="3">
-        <v>15300</v>
+        <v>211700</v>
       </c>
       <c r="I24" s="3">
-        <v>261800</v>
+        <v>47400</v>
       </c>
       <c r="J24" s="3">
+        <v>308500</v>
+      </c>
+      <c r="K24" s="3">
         <v>151400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>7800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-7800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>11100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>11900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-29400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-3000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>21700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>11100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>44400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>34000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>21500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>11100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>72200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>42000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>18500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>15400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>12700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>11000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>12400</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2218,186 +2266,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>83900</v>
+      </c>
+      <c r="E26" s="3">
         <v>102300</v>
       </c>
-      <c r="E26" s="3">
-        <v>123800</v>
-      </c>
       <c r="F26" s="3">
+        <v>144200</v>
+      </c>
+      <c r="G26" s="3">
         <v>47200</v>
       </c>
-      <c r="G26" s="3">
-        <v>110200</v>
-      </c>
       <c r="H26" s="3">
-        <v>28200</v>
+        <v>154200</v>
       </c>
       <c r="I26" s="3">
-        <v>439500</v>
+        <v>87300</v>
       </c>
       <c r="J26" s="3">
+        <v>525500</v>
+      </c>
+      <c r="K26" s="3">
         <v>330500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>24000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>10700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>29700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>39600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>26700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>90600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>20500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>12100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>33900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>58000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>21700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-33000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>84100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>156400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>56000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>39900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>41400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>31500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>25900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>80400</v>
+      </c>
+      <c r="E27" s="3">
         <v>102800</v>
       </c>
-      <c r="E27" s="3">
-        <v>121700</v>
-      </c>
       <c r="F27" s="3">
+        <v>142000</v>
+      </c>
+      <c r="G27" s="3">
         <v>48100</v>
       </c>
-      <c r="G27" s="3">
-        <v>110500</v>
-      </c>
       <c r="H27" s="3">
-        <v>27500</v>
+        <v>155600</v>
       </c>
       <c r="I27" s="3">
-        <v>435100</v>
+        <v>85000</v>
       </c>
       <c r="J27" s="3">
+        <v>520500</v>
+      </c>
+      <c r="K27" s="3">
         <v>330700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>24400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>10900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>30100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>39500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>26700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>91000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>20800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>13000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>33900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>57200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>21200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-28600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>79700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>156400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>56000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>39900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>40800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>31100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>25500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2485,8 +2542,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2574,8 +2634,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2663,8 +2726,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2752,186 +2818,195 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>700</v>
+      </c>
+      <c r="E32" s="3">
         <v>400</v>
       </c>
-      <c r="E32" s="3">
-        <v>2700</v>
-      </c>
       <c r="F32" s="3">
+        <v>2600</v>
+      </c>
+      <c r="G32" s="3">
         <v>-4000</v>
       </c>
-      <c r="G32" s="3">
-        <v>500</v>
-      </c>
       <c r="H32" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="I32" s="3">
-        <v>8600</v>
+        <v>200</v>
       </c>
       <c r="J32" s="3">
+        <v>9500</v>
+      </c>
+      <c r="K32" s="3">
         <v>-1300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>104700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>66400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>115200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>43200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>199000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>172400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>317800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>118400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>161000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>104600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>193000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>177000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>255800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>63500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>122200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>56500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>41500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>18300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>32100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>38800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>33500</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>80400</v>
+      </c>
+      <c r="E33" s="3">
         <v>102800</v>
       </c>
-      <c r="E33" s="3">
-        <v>121700</v>
-      </c>
       <c r="F33" s="3">
+        <v>142000</v>
+      </c>
+      <c r="G33" s="3">
         <v>48100</v>
       </c>
-      <c r="G33" s="3">
-        <v>110500</v>
-      </c>
       <c r="H33" s="3">
-        <v>27500</v>
+        <v>155600</v>
       </c>
       <c r="I33" s="3">
-        <v>435100</v>
+        <v>85000</v>
       </c>
       <c r="J33" s="3">
+        <v>520500</v>
+      </c>
+      <c r="K33" s="3">
         <v>330700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>24400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>10900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>30100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>39500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>26700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>91000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>20800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>13000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>33900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>57200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>21200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-28600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>79700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>156400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>56000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>39900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>40800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>31100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>25500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3019,191 +3094,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>80400</v>
+      </c>
+      <c r="E35" s="3">
         <v>102800</v>
       </c>
-      <c r="E35" s="3">
-        <v>121700</v>
-      </c>
       <c r="F35" s="3">
+        <v>142000</v>
+      </c>
+      <c r="G35" s="3">
         <v>48100</v>
       </c>
-      <c r="G35" s="3">
-        <v>110500</v>
-      </c>
       <c r="H35" s="3">
-        <v>27500</v>
+        <v>155600</v>
       </c>
       <c r="I35" s="3">
-        <v>435100</v>
+        <v>85000</v>
       </c>
       <c r="J35" s="3">
+        <v>520500</v>
+      </c>
+      <c r="K35" s="3">
         <v>330700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>24400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>10900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>30100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>39500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>26700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>91000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>20800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>13000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>33900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>57200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>21200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-28600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>79700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>156400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>56000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>39900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>40800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>31100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>25500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3235,8 +3319,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3268,213 +3353,220 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2070200</v>
+        <v>2003000</v>
       </c>
       <c r="E41" s="3">
+        <v>2192100</v>
+      </c>
+      <c r="F41" s="3">
         <v>868600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>941600</v>
       </c>
-      <c r="G41" s="3">
-        <v>968600</v>
-      </c>
       <c r="H41" s="3">
+        <v>2109300</v>
+      </c>
+      <c r="I41" s="3">
         <v>773300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>776600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>620200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>290000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>212500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>204300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>224900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1192000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>836700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>837900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1195800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1398000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>804800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>676300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1410000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2158700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>898700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>947900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1060300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1235900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1103600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>735900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>535600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>596800</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1142900</v>
+        <v>171400</v>
       </c>
       <c r="E42" s="3">
+        <v>135600</v>
+      </c>
+      <c r="F42" s="3">
         <v>627100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2659000</v>
       </c>
-      <c r="G42" s="3">
-        <v>1786400</v>
-      </c>
       <c r="H42" s="3">
+        <v>3881400</v>
+      </c>
+      <c r="I42" s="3">
         <v>1234500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1224200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>864700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>45600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>36800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>38900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>22800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>31500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>51000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>45500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>70200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>67700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>74900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>98000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>151400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>115000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>141800</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>107400</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>118300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>212600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>96300</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>104300</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>96300</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>279000</v>
       </c>
     </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>5</v>
+      <c r="D43" s="3">
+        <v>172100</v>
       </c>
       <c r="E43" s="3">
+        <v>184300</v>
+      </c>
+      <c r="F43" s="3">
         <v>132600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>112100</v>
       </c>
-      <c r="G43" s="3">
-        <v>109400</v>
-      </c>
       <c r="H43" s="3">
+        <v>238200</v>
+      </c>
+      <c r="I43" s="3">
         <v>226900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>138900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>137400</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
       <c r="L43" s="3">
         <v>0</v>
       </c>
@@ -3535,34 +3627,37 @@
       <c r="AE43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>5</v>
+      <c r="D44" s="3">
+        <v>200</v>
       </c>
       <c r="E44" s="3">
         <v>200</v>
       </c>
       <c r="F44" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G44" s="3">
         <v>100</v>
       </c>
       <c r="H44" s="3">
+        <v>200</v>
+      </c>
+      <c r="I44" s="3">
         <v>100</v>
-      </c>
-      <c r="I44" s="3">
-        <v>200</v>
       </c>
       <c r="J44" s="3">
         <v>200</v>
       </c>
       <c r="K44" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3624,35 +3719,38 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>48300</v>
+        <v>198200</v>
       </c>
       <c r="E45" s="3">
+        <v>150500</v>
+      </c>
+      <c r="F45" s="3">
         <v>328300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>56400</v>
       </c>
-      <c r="G45" s="3">
-        <v>56700</v>
-      </c>
       <c r="H45" s="3">
+        <v>123500</v>
+      </c>
+      <c r="I45" s="3">
         <v>63500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>55700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>71200</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -3713,35 +3811,38 @@
       <c r="AE45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>3261400</v>
+        <v>3280800</v>
       </c>
       <c r="E46" s="3">
+        <v>3617700</v>
+      </c>
+      <c r="F46" s="3">
         <v>2700300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4328800</v>
       </c>
-      <c r="G46" s="3">
-        <v>3381600</v>
-      </c>
       <c r="H46" s="3">
+        <v>7321900</v>
+      </c>
+      <c r="I46" s="3">
         <v>2912800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3095200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2884000</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -3802,186 +3903,195 @@
       <c r="AE46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>2674700</v>
+        <v>2457500</v>
       </c>
       <c r="E47" s="3">
+        <v>2669800</v>
+      </c>
+      <c r="F47" s="3">
         <v>2502600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1049000</v>
       </c>
-      <c r="G47" s="3">
-        <v>955200</v>
-      </c>
       <c r="H47" s="3">
+        <v>2088700</v>
+      </c>
+      <c r="I47" s="3">
         <v>3184700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>3991400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>3368600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>11300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>8400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>8800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>9900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>13600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>8300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>7700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>11200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>14500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>2800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>22000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>20300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>23800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>24200</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>15900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>15200</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>10900</v>
       </c>
     </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>627100</v>
+      </c>
+      <c r="E48" s="3">
         <v>604600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>608400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>543100</v>
       </c>
-      <c r="G48" s="3">
-        <v>368900</v>
-      </c>
       <c r="H48" s="3">
+        <v>803200</v>
+      </c>
+      <c r="I48" s="3">
         <v>549600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>556100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>555800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>99900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>89900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>81100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>68800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>280700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>192100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>177700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>234900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>318100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>188100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>176400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>271100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>364900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>121500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>125900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>126800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>133200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>124500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>133800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>149200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>70200</v>
       </c>
     </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3998,79 +4108,82 @@
         <v>0</v>
       </c>
       <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
         <v>59000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>57400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>55700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>6900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>20300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>12300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>10200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>11900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>14600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>8100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>6700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>9100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>10900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>6600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>6300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>5900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>6900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>8100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>7900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>7400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4158,8 +4271,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4247,97 +4363,103 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>704000</v>
+        <v>515900</v>
       </c>
       <c r="E52" s="3">
+        <v>355300</v>
+      </c>
+      <c r="F52" s="3">
         <v>378500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>392200</v>
       </c>
-      <c r="G52" s="3">
-        <v>382800</v>
-      </c>
       <c r="H52" s="3">
+        <v>866700</v>
+      </c>
+      <c r="I52" s="3">
         <v>515200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>403000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>335400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>27700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>52100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>37000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>34100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>75300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>40000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>35600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>6200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>9300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>4800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>7800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>13200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4425,97 +4547,103 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>14282200</v>
+      </c>
+      <c r="E54" s="3">
         <v>12943400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10462000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>9452000</v>
       </c>
-      <c r="G54" s="3">
-        <v>7575300</v>
-      </c>
       <c r="H54" s="3">
+        <v>16496200</v>
+      </c>
+      <c r="I54" s="3">
         <v>11090500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>12207700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>11291800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2037200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1777500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1658300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1379500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5679100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3940200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3725500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4629800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6479800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3680600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3382600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5085500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6320300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>4256700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>4168600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>4234100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>4812100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>4532100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>3926900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>3707300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>3729900</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4547,8 +4675,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4580,124 +4709,128 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>9631100</v>
+      </c>
+      <c r="E57" s="3">
         <v>8795300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6371200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5569500</v>
       </c>
-      <c r="G57" s="3">
-        <v>4501400</v>
-      </c>
       <c r="H57" s="3">
+        <v>9802400</v>
+      </c>
+      <c r="I57" s="3">
         <v>7410500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7830100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7521300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>167400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>134500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>124000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>104100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>426700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>286900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>249200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>354700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>443700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>274100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>200400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>455500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>435500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>346300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>251100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>320900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>398200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>316500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>284300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>301300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>275600</v>
       </c>
     </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>43100</v>
+        <v>117200</v>
       </c>
       <c r="E58" s="3">
+        <v>7400</v>
+      </c>
+      <c r="F58" s="3">
         <v>197200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5500</v>
       </c>
-      <c r="G58" s="3">
-        <v>20000</v>
-      </c>
       <c r="H58" s="3">
+        <v>43600</v>
+      </c>
+      <c r="I58" s="3">
         <v>8000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4200</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -4758,124 +4891,130 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>9500</v>
+        <v>251700</v>
       </c>
       <c r="E59" s="3">
+        <v>264300</v>
+      </c>
+      <c r="F59" s="3">
         <v>271800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>281700</v>
       </c>
-      <c r="G59" s="3">
-        <v>431500</v>
-      </c>
       <c r="H59" s="3">
+        <v>940500</v>
+      </c>
+      <c r="I59" s="3">
         <v>207500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>376300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>239300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>50400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>44900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>52600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>48200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>222400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>140900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>131000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>146300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>232300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>74200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>69900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>165500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>193200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>105900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>91000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>97800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>97400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>80000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>57500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>49900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>54200</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>8848000</v>
+        <v>10149400</v>
       </c>
       <c r="E60" s="3">
+        <v>9201200</v>
+      </c>
+      <c r="F60" s="3">
         <v>6962000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5968400</v>
       </c>
-      <c r="G60" s="3">
-        <v>5070600</v>
-      </c>
       <c r="H60" s="3">
+        <v>11042700</v>
+      </c>
+      <c r="I60" s="3">
         <v>7805000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8365400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7907800</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -4936,186 +5075,195 @@
       <c r="AE60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>190800</v>
+        <v>1105400</v>
       </c>
       <c r="E61" s="3">
+        <v>947900</v>
+      </c>
+      <c r="F61" s="3">
         <v>750300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>494900</v>
       </c>
-      <c r="G61" s="3">
-        <v>410300</v>
-      </c>
       <c r="H61" s="3">
+        <v>893400</v>
+      </c>
+      <c r="I61" s="3">
         <v>533900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>663000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>575600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>16100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>12600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>12200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>18600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>27800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>17400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>16600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>25300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>35200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>26400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>21300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>23100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>200</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
       <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="3">
         <v>13700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>9600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>78300</v>
       </c>
     </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1439800</v>
+        <v>474400</v>
       </c>
       <c r="E62" s="3">
+        <v>317500</v>
+      </c>
+      <c r="F62" s="3">
         <v>426800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>503700</v>
       </c>
-      <c r="G62" s="3">
-        <v>298000</v>
-      </c>
       <c r="H62" s="3">
+        <v>648000</v>
+      </c>
+      <c r="I62" s="3">
         <v>481400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>905400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>574600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>16000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>15800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>8100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>20500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>76200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>44000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>42100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>65800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>108400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>65500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>68700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>111800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>150400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>79000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>75500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>42900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>49900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>47400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>54400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>62500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>46300</v>
       </c>
     </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5203,8 +5351,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5292,8 +5443,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5381,97 +5535,103 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>11740100</v>
+      </c>
+      <c r="E66" s="3">
         <v>10478600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>8150000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6973900</v>
       </c>
-      <c r="G66" s="3">
-        <v>5813800</v>
-      </c>
       <c r="H66" s="3">
+        <v>12660300</v>
+      </c>
+      <c r="I66" s="3">
         <v>8906100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9998600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9091700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1662300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1447700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1387000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1154700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4800300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3313100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3164100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3896400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5522700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3027400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2801800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4222000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5280700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3680100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3651100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3749600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4289000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4047700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3445800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3184200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3299200</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5503,8 +5663,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5592,8 +5753,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5681,8 +5845,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5770,8 +5937,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5859,97 +6029,103 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1571100</v>
+      </c>
+      <c r="E72" s="3">
         <v>278800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1313500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1481200</v>
       </c>
-      <c r="G72" s="3">
-        <v>1007700</v>
-      </c>
       <c r="H72" s="3">
+        <v>2194400</v>
+      </c>
+      <c r="I72" s="3">
         <v>1426700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1415300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1433700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>235300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>202900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>160600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>130500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>499000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>357800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>314900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>411700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>527200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>397400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>343200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>505000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>570400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>497900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>436200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>400900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>419200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>380500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>368900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>396500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>304100</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6037,8 +6213,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6126,8 +6305,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6215,97 +6397,103 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2501300</v>
+      </c>
+      <c r="E76" s="3">
         <v>2427300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2275900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2447300</v>
       </c>
-      <c r="G76" s="3">
-        <v>1739300</v>
-      </c>
       <c r="H76" s="3">
+        <v>3787500</v>
+      </c>
+      <c r="I76" s="3">
         <v>2151300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2176300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2168600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>374900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>329800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>271200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>224900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>878700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>627200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>561400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>733400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>957100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>653200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>580800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>863500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1039600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>576700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>517500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>484600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>523100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>484400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>481100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>523100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>430700</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6393,191 +6581,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>80400</v>
+      </c>
+      <c r="E81" s="3">
         <v>102800</v>
       </c>
-      <c r="E81" s="3">
-        <v>121700</v>
-      </c>
       <c r="F81" s="3">
+        <v>142000</v>
+      </c>
+      <c r="G81" s="3">
         <v>48100</v>
       </c>
-      <c r="G81" s="3">
-        <v>110500</v>
-      </c>
       <c r="H81" s="3">
-        <v>27500</v>
+        <v>155600</v>
       </c>
       <c r="I81" s="3">
-        <v>435100</v>
+        <v>85000</v>
       </c>
       <c r="J81" s="3">
+        <v>520500</v>
+      </c>
+      <c r="K81" s="3">
         <v>330700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>24400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>10900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>30100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>39500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>26700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>91000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>20800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>13000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>33900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>57200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>21200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-28600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>79700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>156400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>56000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>39900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>40800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>31100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>25500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6609,97 +6806,101 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>14700</v>
+        <v>18700</v>
       </c>
       <c r="E83" s="3">
+        <v>33000</v>
+      </c>
+      <c r="F83" s="3">
         <v>51600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>46200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>86300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>46200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>34200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>28700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>11100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>13100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>16800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>6700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>12800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>9500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>16000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>11600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>25900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>12500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>21100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>13400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>3400</v>
-      </c>
-      <c r="AB83" s="3">
-        <v>3000</v>
       </c>
       <c r="AC83" s="3">
         <v>3000</v>
       </c>
       <c r="AD83" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AE83" s="3">
         <v>3300</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6787,8 +6988,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6876,8 +7080,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6965,8 +7172,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7054,8 +7264,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7143,97 +7356,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>5</v>
+      <c r="D89" s="3">
+        <v>-1798600</v>
       </c>
       <c r="E89" s="3">
+        <v>-1541300</v>
+      </c>
+      <c r="F89" s="3">
         <v>-920700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1147600</v>
       </c>
-      <c r="G89" s="3">
-        <v>-1902300</v>
-      </c>
       <c r="H89" s="3">
-        <v>-2471000</v>
+        <v>-2431600</v>
       </c>
       <c r="I89" s="3">
+        <v>-6472600</v>
+      </c>
+      <c r="J89" s="3">
         <v>-6616800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-3450000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>38700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-38200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-117900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-61000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>82500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-7600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>88800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>157000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-19300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>50100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-415200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-247300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>611600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-180800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-156000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-62700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>260600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>198900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>38000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-38900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>154700</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7265,97 +7484,101 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>5</v>
+      <c r="D91" s="3">
+        <v>-126800</v>
       </c>
       <c r="E91" s="3">
+        <v>12700</v>
+      </c>
+      <c r="F91" s="3">
         <v>-24100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-28200</v>
       </c>
-      <c r="G91" s="3">
-        <v>-37800</v>
-      </c>
       <c r="H91" s="3">
-        <v>-18900</v>
+        <v>-69500</v>
       </c>
       <c r="I91" s="3">
+        <v>-49600</v>
+      </c>
+      <c r="J91" s="3">
         <v>-42900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-34500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-12277100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-312900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2694300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1125700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-10201100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2576100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1792900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-7800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-5000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-3700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-14400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-9200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-22400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>7300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-4800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-5200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7443,8 +7666,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7532,97 +7758,103 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>5</v>
+      <c r="D94" s="3">
+        <v>-127300</v>
       </c>
       <c r="E94" s="3">
+        <v>12400</v>
+      </c>
+      <c r="F94" s="3">
         <v>-20800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-28200</v>
       </c>
-      <c r="G94" s="3">
-        <v>-38800</v>
-      </c>
       <c r="H94" s="3">
-        <v>-18900</v>
+        <v>-71600</v>
       </c>
       <c r="I94" s="3">
+        <v>-49600</v>
+      </c>
+      <c r="J94" s="3">
         <v>-37100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-42400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-26100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-14500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-6000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-8300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-4500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-15100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>17800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>16100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-22300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>14500</v>
       </c>
-      <c r="AC94" s="3">
-        <v>0</v>
-      </c>
       <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="3">
         <v>-5100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7654,34 +7886,35 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>5</v>
+      <c r="D96" s="3">
+        <v>6500</v>
       </c>
       <c r="E96" s="3">
+        <v>36100</v>
+      </c>
+      <c r="F96" s="3">
         <v>53600</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G96" s="3">
-        <v>200</v>
+      <c r="G96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H96" s="3">
         <v>300</v>
       </c>
       <c r="I96" s="3">
+        <v>700</v>
+      </c>
+      <c r="J96" s="3">
         <v>300</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -7723,11 +7956,11 @@
         <v>0</v>
       </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-25500</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
         <v>0</v>
       </c>
@@ -7741,10 +7974,13 @@
         <v>0</v>
       </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7832,8 +8068,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7921,8 +8160,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8010,271 +8252,283 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>5</v>
+      <c r="D100" s="3">
+        <v>1937100</v>
       </c>
       <c r="E100" s="3">
+        <v>3326400</v>
+      </c>
+      <c r="F100" s="3">
         <v>1408400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1608700</v>
       </c>
-      <c r="G100" s="3">
-        <v>2339300</v>
-      </c>
       <c r="H100" s="3">
-        <v>2673900</v>
+        <v>3133100</v>
       </c>
       <c r="I100" s="3">
+        <v>6830200</v>
+      </c>
+      <c r="J100" s="3">
         <v>7590600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>4933100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-11200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>4100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-18400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-9800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-5300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-16500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-22500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-12900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>11500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-30600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-18300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>21900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-8000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>21900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>55900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>2100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>182200</v>
+        <v>1230900</v>
       </c>
       <c r="E101" s="3">
+        <v>530900</v>
+      </c>
+      <c r="F101" s="3">
         <v>120000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>171000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>218900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-69800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-204200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>7700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>16500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-3600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-13500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-25700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-65700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>5500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>4800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>23400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>23700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>51500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>63500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>30300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>245700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>69900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>87800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-81800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>221100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>161900</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>22700</v>
       </c>
-      <c r="AE101" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-37700</v>
       </c>
       <c r="E102" s="3">
+        <v>1703100</v>
+      </c>
+      <c r="F102" s="3">
         <v>246300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>201000</v>
       </c>
-      <c r="G102" s="3">
-        <v>1005700</v>
-      </c>
       <c r="H102" s="3">
-        <v>366100</v>
+        <v>1860800</v>
       </c>
       <c r="I102" s="3">
+        <v>838800</v>
+      </c>
+      <c r="J102" s="3">
         <v>1056700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1611600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>31500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-52700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-132000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-64300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-102100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>54400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>149300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-16900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>44100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-405400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-217500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>638300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>33000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-86500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>53300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>152200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>452700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>257800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-21800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>188600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BBAR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BBAR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="92">
   <si>
     <t>BBAR</t>
   </si>
@@ -656,264 +656,271 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>656600</v>
+      </c>
+      <c r="E8" s="3">
         <v>776400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>629700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1119000</v>
       </c>
-      <c r="G8" s="3">
-        <v>1300900</v>
-      </c>
       <c r="H8" s="3">
+        <v>1710900</v>
+      </c>
+      <c r="I8" s="3">
         <v>2116200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2688200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3861400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3254600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>275400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>160200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>259900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>95500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>437400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>410500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>727600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>254100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>377500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>248500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>494500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>386400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>501000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>401000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>728200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>327000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>240600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>166900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>139500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>130800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>121600</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E9" s="3">
         <v>15600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>11100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>12700</v>
       </c>
-      <c r="G9" s="3">
-        <v>11400</v>
-      </c>
       <c r="H9" s="3">
+        <v>15000</v>
+      </c>
+      <c r="I9" s="3">
         <v>18200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>31200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>42500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>46500</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>5</v>
       </c>
@@ -974,38 +981,41 @@
       <c r="AF9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>645400</v>
+      </c>
+      <c r="E10" s="3">
         <v>760800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>618600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1106300</v>
       </c>
-      <c r="G10" s="3">
-        <v>1289500</v>
-      </c>
       <c r="H10" s="3">
+        <v>1695900</v>
+      </c>
+      <c r="I10" s="3">
         <v>2097900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2657000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3819000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3208100</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1066,8 +1076,11 @@
       <c r="AF10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1100,8 +1113,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1192,8 +1206,11 @@
       <c r="AF12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1284,37 +1301,40 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3">
         <v>4000</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3">
         <v>6900</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1376,100 +1396,106 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E15" s="3">
         <v>17800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>9800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>21900</v>
       </c>
-      <c r="G15" s="3">
-        <v>10300</v>
-      </c>
       <c r="H15" s="3">
+        <v>16000</v>
+      </c>
+      <c r="I15" s="3">
         <v>17400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>28200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>58000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>41000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-3900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-2300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-5200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-2300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-10900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-14600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-31700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-14100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-12800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-8000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-17500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>-24600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-25900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-15300</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-26900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>-27600</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>-3800</v>
-      </c>
-      <c r="AC15" s="3">
-        <v>-3000</v>
       </c>
       <c r="AD15" s="3">
         <v>-3000</v>
       </c>
       <c r="AE15" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="AF15" s="3">
         <v>-3300</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1499,192 +1525,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>534400</v>
+      </c>
+      <c r="E17" s="3">
         <v>731000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>502300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>893200</v>
       </c>
-      <c r="G17" s="3">
-        <v>1216700</v>
-      </c>
       <c r="H17" s="3">
+        <v>1600000</v>
+      </c>
+      <c r="I17" s="3">
         <v>1743800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2553700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3037000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2771300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>138800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>79700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>122900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>44400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>187700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>199500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>348500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>118200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>182700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>98900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>199000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>153800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>256700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>242200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>377400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>172500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>140700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>91800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>63100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>55100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>52200</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>122200</v>
+      </c>
+      <c r="E18" s="3">
         <v>45400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>127400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>225800</v>
       </c>
-      <c r="G18" s="3">
-        <v>84300</v>
-      </c>
       <c r="H18" s="3">
+        <v>110800</v>
+      </c>
+      <c r="I18" s="3">
         <v>372400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>134500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>824500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>483300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>136600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>80500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>137000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>51200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>249700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>211000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>379000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>135900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>194700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>149600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>295400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>232700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>244300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>158800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>350800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>154500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>99900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>75100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>76300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>75700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>69400</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1717,8 +1750,9 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1726,183 +1760,189 @@
         <v>-700</v>
       </c>
       <c r="E20" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F20" s="3">
         <v>-400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2600</v>
       </c>
-      <c r="G20" s="3">
-        <v>4000</v>
-      </c>
       <c r="H20" s="3">
+        <v>5200</v>
+      </c>
+      <c r="I20" s="3">
         <v>-400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-9500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-104700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-66400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-115200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-43200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-199000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-172400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-317800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-118400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-161000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-104600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-193000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-177000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-255800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-63500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-122200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-56500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-41500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-18300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-32100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-38800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-33500</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>138100</v>
+      </c>
+      <c r="E21" s="3">
         <v>64000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>137500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>250400</v>
       </c>
-      <c r="G21" s="3">
-        <v>90500</v>
-      </c>
       <c r="H21" s="3">
+        <v>121600</v>
+      </c>
+      <c r="I21" s="3">
         <v>390100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>162800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>892000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>522900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>36500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>17200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>26200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>9900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>61800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>51800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>78000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>24200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>46500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>54400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>118400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>67300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>14400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>107800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>249700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>111500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>61800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>59700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>47300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>40100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>36100</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1930,8 +1970,8 @@
       <c r="K22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1993,192 +2033,201 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>122900</v>
+      </c>
+      <c r="E23" s="3">
         <v>42100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>127700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>228400</v>
       </c>
-      <c r="G23" s="3">
-        <v>80300</v>
-      </c>
       <c r="H23" s="3">
+        <v>105600</v>
+      </c>
+      <c r="I23" s="3">
         <v>365900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>134600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>834000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>481900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>31900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>14100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>21900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>8000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>50700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>38600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>61200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>17500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>33700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>45000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>102400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>55600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-11500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>95300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>228600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>98000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>58400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>56700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>44200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>36800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>35900</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>46800</v>
+      </c>
+      <c r="E24" s="3">
         <v>-41800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>25400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>84300</v>
       </c>
-      <c r="G24" s="3">
-        <v>33100</v>
-      </c>
       <c r="H24" s="3">
+        <v>43500</v>
+      </c>
+      <c r="I24" s="3">
         <v>211700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>47400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>308500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>151400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>7800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>3300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-7800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>11100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>11900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-29400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-3000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>21700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>11100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>44400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>34000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>21500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>11100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>72200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>42000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>18500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>15400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>12700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>11000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>12400</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2269,192 +2318,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>76000</v>
+      </c>
+      <c r="E26" s="3">
         <v>83900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>102300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>144200</v>
       </c>
-      <c r="G26" s="3">
-        <v>47200</v>
-      </c>
       <c r="H26" s="3">
+        <v>62100</v>
+      </c>
+      <c r="I26" s="3">
         <v>154200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>87300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>525500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>330500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>24000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>10700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>29700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>39600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>26700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>90600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>20500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>12100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>33900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>58000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>21700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-33000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>84100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>156400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>56000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>39900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>41400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>31500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>25900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>73100</v>
+      </c>
+      <c r="E27" s="3">
         <v>80400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>102800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>142000</v>
       </c>
-      <c r="G27" s="3">
-        <v>48100</v>
-      </c>
       <c r="H27" s="3">
+        <v>63200</v>
+      </c>
+      <c r="I27" s="3">
         <v>155600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>85000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>520500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>330700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>24400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>10900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>30100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>39500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>26700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>91000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>20800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>13000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>33900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>57200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>21200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-28600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>79700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>156400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>56000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>39900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>40800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>31100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>25500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2545,8 +2603,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2637,8 +2698,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2729,8 +2793,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2821,8 +2888,11 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2830,183 +2900,189 @@
         <v>700</v>
       </c>
       <c r="E32" s="3">
+        <v>700</v>
+      </c>
+      <c r="F32" s="3">
         <v>400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2600</v>
       </c>
-      <c r="G32" s="3">
-        <v>-4000</v>
-      </c>
       <c r="H32" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="I32" s="3">
         <v>400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>9500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>104700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>66400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>115200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>43200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>199000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>172400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>317800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>118400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>161000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>104600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>193000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>177000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>255800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>63500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>122200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>56500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>41500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>18300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>32100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>38800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>33500</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>73100</v>
+      </c>
+      <c r="E33" s="3">
         <v>80400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>102800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>142000</v>
       </c>
-      <c r="G33" s="3">
-        <v>48100</v>
-      </c>
       <c r="H33" s="3">
+        <v>63200</v>
+      </c>
+      <c r="I33" s="3">
         <v>155600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>85000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>520500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>330700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>24400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>10900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>30100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>5800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>39500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>26700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>91000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>20800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>13000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>33900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>57200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>21200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-28600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>79700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>156400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>56000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>39900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>40800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>31100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>25500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3097,197 +3173,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>73100</v>
+      </c>
+      <c r="E35" s="3">
         <v>80400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>102800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>142000</v>
       </c>
-      <c r="G35" s="3">
-        <v>48100</v>
-      </c>
       <c r="H35" s="3">
+        <v>63200</v>
+      </c>
+      <c r="I35" s="3">
         <v>155600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>85000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>520500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>330700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>24400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>10900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>30100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>5800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>39500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>26700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>91000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>20800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>13000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>33900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>57200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>21200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-28600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>79700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>156400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>56000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>39900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>40800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>31100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>25500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3320,8 +3405,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3354,222 +3440,229 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1475800</v>
+      </c>
+      <c r="E41" s="3">
         <v>2003000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2192100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>868600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>941600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2109300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>773300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>776600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>620200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>290000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>212500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>204300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>224900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1192000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>836700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>837900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1195800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1398000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>804800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>676300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1410000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2158700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>898700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>947900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1060300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1235900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1103600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>735900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>535600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>596800</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>658000</v>
+      </c>
+      <c r="E42" s="3">
         <v>171400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>135600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>627100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2659000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>3881400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1234500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1224200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>864700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>45600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>36800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>38900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>22800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>31500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>51000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>45500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>70200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>67700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>74900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>98000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>151400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>115000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>141800</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>107400</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>118300</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>212600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>96300</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>104300</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>96300</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>279000</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>201100</v>
+      </c>
+      <c r="E43" s="3">
         <v>172100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>184300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>132600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>112100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>238200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>226900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>138900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>137400</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
       <c r="M43" s="3">
         <v>0</v>
       </c>
@@ -3630,8 +3723,11 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3645,22 +3741,22 @@
         <v>200</v>
       </c>
       <c r="G44" s="3">
+        <v>200</v>
+      </c>
+      <c r="H44" s="3">
         <v>100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>100</v>
-      </c>
-      <c r="J44" s="3">
-        <v>200</v>
       </c>
       <c r="K44" s="3">
         <v>200</v>
       </c>
       <c r="L44" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3722,38 +3818,41 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>188100</v>
+      </c>
+      <c r="E45" s="3">
         <v>198200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>150500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>328300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>56400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>123500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>63500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>55700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>71200</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -3814,38 +3913,41 @@
       <c r="AF45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3331200</v>
+      </c>
+      <c r="E46" s="3">
         <v>3280800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3617700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2700300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4328800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7321900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2912800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3095200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2884000</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -3906,192 +4008,201 @@
       <c r="AF46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2243600</v>
+      </c>
+      <c r="E47" s="3">
         <v>2457500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2669800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2502600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1049000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2088700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>3184700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>3991400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3368600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>3100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>11300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>8400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>8800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>9900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>13600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>8300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>7700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>11200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>14500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>2800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>22000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>20300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>23800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>24200</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>15900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>15200</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>10900</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>650500</v>
+      </c>
+      <c r="E48" s="3">
         <v>627100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>604600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>608400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>543100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>803200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>549600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>556100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>555800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>99900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>89900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>81100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>68800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>280700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>192100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>177700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>234900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>318100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>188100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>176400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>271100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>364900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>121500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>125900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>126800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>133200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>124500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>133800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>149200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>70200</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4111,79 +4222,82 @@
         <v>0</v>
       </c>
       <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>59000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>57400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>55700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>10000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>6900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>20300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>12300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>10200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>11900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>14600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>8100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>6700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>9100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>10900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>6600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>6300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>5900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>6900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>8100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>7900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>7400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4274,8 +4388,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4366,100 +4483,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>379600</v>
+      </c>
+      <c r="E52" s="3">
         <v>515900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>355300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>378500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>392200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>866700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>515200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>403000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>335400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>27700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>52100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>37000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>34100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>75300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>40000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>35600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>6200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>9300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>4800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>7800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>13200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4550,100 +4673,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>15178900</v>
+      </c>
+      <c r="E54" s="3">
         <v>14282200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>12943400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10462000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>9452000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>16496200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>11090500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>12207700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>11291800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2037200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1777500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1658300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1379500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5679100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3940200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3725500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4629800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6479800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3680600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3382600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5085500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6320300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>4256700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>4168600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>4234100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>4812100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>4532100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>3926900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>3707300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>3729900</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4676,8 +4805,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4710,130 +4840,134 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10227100</v>
+      </c>
+      <c r="E57" s="3">
         <v>9631100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8795300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6371200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5569500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>9802400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7410500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7830100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7521300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>167400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>134500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>124000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>104100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>426700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>286900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>249200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>354700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>443700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>274100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>200400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>455500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>435500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>346300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>251100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>320900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>398200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>316500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>284300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>301300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>275600</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E58" s="3">
         <v>117200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>7400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>197200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>43600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>8000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4200</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -4894,130 +5028,136 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>164200</v>
+      </c>
+      <c r="E59" s="3">
         <v>251700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>264300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>271800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>281700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>940500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>207500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>376300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>239300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>50400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>44900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>52600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>48200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>222400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>140900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>131000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>146300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>232300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>74200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>69900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>165500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>193200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>105900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>91000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>97800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>97400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>80000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>57500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>49900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>54200</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>10543800</v>
+      </c>
+      <c r="E60" s="3">
         <v>10149400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9201200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6962000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5968400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>11042700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7805000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8365400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7907800</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -5078,192 +5218,201 @@
       <c r="AF60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1445500</v>
+      </c>
+      <c r="E61" s="3">
         <v>1105400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>947900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>750300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>494900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>893400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>533900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>663000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>575600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>16100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>12600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>12200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>18600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>27800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>17400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>16600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>25300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>35200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>26400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>21300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>23100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>200</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
       <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="3">
         <v>13700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>9600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>78300</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>554700</v>
+      </c>
+      <c r="E62" s="3">
         <v>474400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>317500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>426800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>503700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>648000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>481400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>905400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>574600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>16000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>15800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>8100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>20500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>76200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>44000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>42100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>65800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>108400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>65500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>68700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>111800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>150400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>79000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>75500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>42900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>49900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>47400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>54400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>62500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>46300</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5354,8 +5503,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5446,8 +5598,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5538,100 +5693,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>12553500</v>
+      </c>
+      <c r="E66" s="3">
         <v>11740100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>10478600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>8150000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6973900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>12660300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>8906100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9998600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9091700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1662300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1447700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1387000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1154700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4800300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3313100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3164100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3896400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5522700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3027400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2801800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4222000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5280700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3680100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3651100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3749600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4289000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>4047700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3445800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3184200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3299200</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5664,8 +5825,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5756,8 +5918,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5848,8 +6013,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5940,8 +6108,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6032,100 +6203,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1711900</v>
+      </c>
+      <c r="E72" s="3">
         <v>1571100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>278800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1313500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1481200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2194400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1426700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1415300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1433700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>235300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>202900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>160600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>130500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>499000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>357800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>314900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>411700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>527200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>397400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>343200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>505000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>570400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>497900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>436200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>400900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>419200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>380500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>368900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>396500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>304100</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6216,8 +6393,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6308,8 +6488,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6400,100 +6583,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2579800</v>
+      </c>
+      <c r="E76" s="3">
         <v>2501300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2427300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2275900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2447300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3787500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2151300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2176300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2168600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>374900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>329800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>271200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>224900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>878700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>627200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>561400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>733400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>957100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>653200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>580800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>863500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1039600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>576700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>517500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>484600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>523100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>484400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>481100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>523100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>430700</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6584,197 +6773,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>73100</v>
+      </c>
+      <c r="E81" s="3">
         <v>80400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>102800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>142000</v>
       </c>
-      <c r="G81" s="3">
-        <v>48100</v>
-      </c>
       <c r="H81" s="3">
+        <v>63200</v>
+      </c>
+      <c r="I81" s="3">
         <v>155600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>85000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>520500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>330700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>24400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>10900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>30100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>5800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>39500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>26700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>91000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>20800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>13000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>33900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>57200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>21200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-28600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>79700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>156400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>56000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>39900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>40800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>31100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>25500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6807,100 +7005,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E83" s="3">
         <v>18700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>33000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>51600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>46200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>86300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>46200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>34200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>28700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>11100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>13100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>16800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>6700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>12800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>9500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>16000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>11600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>25900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>12500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>21100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>13400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>3400</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>3000</v>
       </c>
       <c r="AD83" s="3">
         <v>3000</v>
       </c>
       <c r="AE83" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AF83" s="3">
         <v>3300</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6991,8 +7193,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7083,8 +7288,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7175,8 +7383,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7267,8 +7478,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7359,100 +7573,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1507700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1798600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1541300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-920700</v>
       </c>
-      <c r="G89" s="3">
-        <v>-1147600</v>
-      </c>
       <c r="H89" s="3">
+        <v>-1789400</v>
+      </c>
+      <c r="I89" s="3">
         <v>-2431600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-6472600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-6616800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3450000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>38700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-38200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-117900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-61000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>82500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-7600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>88800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>157000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-19300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>50100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-415200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-247300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>611600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-180800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-156000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-62700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>260600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>198900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>38000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-38900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>154700</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7485,100 +7705,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-16900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-126800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>12700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-24100</v>
       </c>
-      <c r="G91" s="3">
-        <v>-28200</v>
-      </c>
       <c r="H91" s="3">
+        <v>-44000</v>
+      </c>
+      <c r="I91" s="3">
         <v>-69500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-49600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-42900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-34500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-12277100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-312900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2694300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1125700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-10201100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2576100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1792900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-7800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-5000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-3700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-14400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-9200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-22400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>7300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-4800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-5200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7669,8 +7893,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7761,100 +7988,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-16800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-127300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>12400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-20800</v>
       </c>
-      <c r="G94" s="3">
-        <v>-28200</v>
-      </c>
       <c r="H94" s="3">
+        <v>-44000</v>
+      </c>
+      <c r="I94" s="3">
         <v>-71600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-49600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-37100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-42400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-26100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-14500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-6000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-8300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-4500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-15100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>17800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>16100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-22300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>14500</v>
       </c>
-      <c r="AD94" s="3">
-        <v>0</v>
-      </c>
       <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-5100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7887,37 +8120,38 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E96" s="3">
         <v>6500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>36100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>53600</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I96" s="3">
         <v>300</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>300</v>
       </c>
-      <c r="K96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7959,11 +8193,11 @@
         <v>0</v>
       </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-25500</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
         <v>0</v>
       </c>
@@ -7977,10 +8211,13 @@
         <v>0</v>
       </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8071,8 +8308,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8163,8 +8403,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8255,280 +8498,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1203800</v>
+      </c>
+      <c r="E100" s="3">
         <v>1937100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3326400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1408400</v>
       </c>
-      <c r="G100" s="3">
-        <v>1608700</v>
-      </c>
       <c r="H100" s="3">
+        <v>2508500</v>
+      </c>
+      <c r="I100" s="3">
         <v>3133100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>6830200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>7590600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>4933100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-11200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>4100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-3400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-18400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-9800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-5300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-16500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-22500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-12900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>11500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-30600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-18300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>21900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-8000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>21900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>55900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>2100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-361600</v>
+      </c>
+      <c r="E101" s="3">
         <v>1230900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>530900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>120000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>171000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>218900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-69800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-204200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>7700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>16500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-3600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-13500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-25700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-65700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>5500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>4800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>23400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>23700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>51500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>63500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>30300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>245700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>69900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>87800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-81800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>221100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>161900</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>22700</v>
       </c>
-      <c r="AF101" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-365300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-37700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1703100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>246300</v>
       </c>
-      <c r="G102" s="3">
-        <v>201000</v>
-      </c>
       <c r="H102" s="3">
+        <v>313400</v>
+      </c>
+      <c r="I102" s="3">
         <v>1860800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>838800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1056700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1611600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>31500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-52700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-132000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-64300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-102100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>54400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>149300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-16900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>44100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-405400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-217500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>638300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>33000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-86500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>53300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>152200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>452700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>257800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-21800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>188600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BBAR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BBAR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="92">
   <si>
     <t>BBAR</t>
   </si>
@@ -656,287 +656,300 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>570500</v>
+        <v>663700</v>
       </c>
       <c r="E8" s="3">
+        <v>484300</v>
+      </c>
+      <c r="F8" s="3">
+        <v>642000</v>
+      </c>
+      <c r="G8" s="3">
         <v>696100</v>
       </c>
-      <c r="F8" s="3">
-        <v>776400</v>
-      </c>
-      <c r="G8" s="3">
-        <v>629700</v>
-      </c>
       <c r="H8" s="3">
-        <v>1206900</v>
+        <v>1015800</v>
       </c>
       <c r="I8" s="3">
+        <v>829600</v>
+      </c>
+      <c r="J8" s="3">
+        <v>1380700</v>
+      </c>
+      <c r="K8" s="3">
         <v>1813800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>2116200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>2688200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>3861400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>3254600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>275400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>160200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>259900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>95500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>437400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>410500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>727600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>254100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>377500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>248500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>494500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>386400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>501000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>401000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>728200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>327000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>240600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>166900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>139500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>130800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>121600</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E9" s="3">
         <v>11300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
+        <v>12600</v>
+      </c>
+      <c r="G9" s="3">
         <v>11900</v>
       </c>
-      <c r="F9" s="3">
-        <v>15600</v>
-      </c>
-      <c r="G9" s="3">
-        <v>11100</v>
-      </c>
       <c r="H9" s="3">
-        <v>14200</v>
+        <v>20500</v>
       </c>
       <c r="I9" s="3">
+        <v>14600</v>
+      </c>
+      <c r="J9" s="3">
         <v>15900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
+        <v>15900</v>
+      </c>
+      <c r="L9" s="3">
         <v>18200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>31200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>42500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>46500</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>5</v>
       </c>
@@ -994,47 +1007,53 @@
       <c r="AH9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AI9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>559200</v>
+        <v>650300</v>
       </c>
       <c r="E10" s="3">
+        <v>473000</v>
+      </c>
+      <c r="F10" s="3">
+        <v>629400</v>
+      </c>
+      <c r="G10" s="3">
         <v>684200</v>
       </c>
-      <c r="F10" s="3">
-        <v>760800</v>
-      </c>
-      <c r="G10" s="3">
-        <v>618600</v>
-      </c>
       <c r="H10" s="3">
-        <v>1192700</v>
+        <v>995300</v>
       </c>
       <c r="I10" s="3">
+        <v>815000</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1364800</v>
+      </c>
+      <c r="K10" s="3">
         <v>1797800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>2097900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>2657000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>3819000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>3208100</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1092,8 +1111,14 @@
       <c r="AH10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AI10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1128,8 +1153,10 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1226,8 +1253,14 @@
       <c r="AH12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AI12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1324,46 +1357,52 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
+      <c r="D14" s="3">
+        <v>9700</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F14" s="3">
-        <v>4000</v>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>5</v>
+      <c r="H14" s="3">
+        <v>5300</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L14" s="3">
         <v>6900</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1422,106 +1461,118 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>18800</v>
+      </c>
+      <c r="E15" s="3">
+        <v>15600</v>
+      </c>
+      <c r="F15" s="3">
         <v>15400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>15300</v>
       </c>
-      <c r="F15" s="3">
-        <v>17800</v>
-      </c>
-      <c r="G15" s="3">
-        <v>9800</v>
-      </c>
       <c r="H15" s="3">
+        <v>23400</v>
+      </c>
+      <c r="I15" s="3">
+        <v>20600</v>
+      </c>
+      <c r="J15" s="3">
         <v>18400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>16000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>17400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>28200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>58000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>41000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>-3900</v>
-      </c>
-      <c r="O15" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="P15" s="3">
-        <v>-5200</v>
       </c>
       <c r="Q15" s="3">
         <v>-2300</v>
       </c>
       <c r="R15" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="S15" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="T15" s="3">
         <v>-10900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>-14600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>-31700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>-14100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>-12800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>-8000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>-17500</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>-24600</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>-25900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>-15300</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>-26900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>-27600</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AF15" s="3">
         <v>-3800</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AG15" s="3">
         <v>-3000</v>
-      </c>
-      <c r="AF15" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="AG15" s="3">
-        <v>-3300</v>
       </c>
       <c r="AH15" s="3">
         <v>-3000</v>
       </c>
+      <c r="AI15" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="AJ15" s="3">
+        <v>-3000</v>
+      </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1553,204 +1604,218 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
+      <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>498500</v>
+        <v>570500</v>
       </c>
       <c r="E17" s="3">
+        <v>441900</v>
+      </c>
+      <c r="F17" s="3">
+        <v>558700</v>
+      </c>
+      <c r="G17" s="3">
         <v>566500</v>
       </c>
-      <c r="F17" s="3">
-        <v>731000</v>
-      </c>
-      <c r="G17" s="3">
-        <v>502300</v>
-      </c>
       <c r="H17" s="3">
-        <v>938100</v>
+        <v>956900</v>
       </c>
       <c r="I17" s="3">
+        <v>661800</v>
+      </c>
+      <c r="J17" s="3">
+        <v>1089200</v>
+      </c>
+      <c r="K17" s="3">
         <v>1696300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1743800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>2553700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>3037000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>2771300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>138800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>79700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>122900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>44400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>187700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>199500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>348500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>118200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>182700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>98900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>199000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>153800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>256700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>242200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>377400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>172500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>140700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>91800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>63100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>55100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>52200</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>72000</v>
+        <v>93200</v>
       </c>
       <c r="E18" s="3">
+        <v>42400</v>
+      </c>
+      <c r="F18" s="3">
+        <v>83300</v>
+      </c>
+      <c r="G18" s="3">
         <v>129500</v>
       </c>
-      <c r="F18" s="3">
-        <v>45400</v>
-      </c>
-      <c r="G18" s="3">
-        <v>127400</v>
-      </c>
       <c r="H18" s="3">
-        <v>268800</v>
+        <v>58900</v>
       </c>
       <c r="I18" s="3">
+        <v>167800</v>
+      </c>
+      <c r="J18" s="3">
+        <v>291500</v>
+      </c>
+      <c r="K18" s="3">
         <v>117500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>372400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>134500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>824500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>483300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>136600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>80500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>137000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>51200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>249700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>211000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>379000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>135900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>194700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>149600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>295400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>232700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>244300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>158800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>350800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>154500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>99900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>75100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>76300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>75700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>69400</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1785,204 +1850,218 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
+      <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-3400</v>
+        <v>-2500</v>
       </c>
       <c r="E20" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="G20" s="3">
         <v>-700</v>
       </c>
-      <c r="F20" s="3">
-        <v>-700</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="K20" s="3">
+        <v>5600</v>
+      </c>
+      <c r="L20" s="3">
         <v>-400</v>
       </c>
-      <c r="H20" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="I20" s="3">
-        <v>5600</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-400</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-9500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>1300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-104700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-66400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-115200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-43200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-199000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-172400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-317800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-118400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-161000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-104600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-193000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-177000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-255800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-63500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-122200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-56500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>-41500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>-18300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>-32100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>-38800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>-33500</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>90800</v>
+        <v>114500</v>
       </c>
       <c r="E21" s="3">
+        <v>60300</v>
+      </c>
+      <c r="F21" s="3">
+        <v>102300</v>
+      </c>
+      <c r="G21" s="3">
         <v>145500</v>
       </c>
-      <c r="F21" s="3">
-        <v>64000</v>
-      </c>
-      <c r="G21" s="3">
-        <v>137500</v>
-      </c>
       <c r="H21" s="3">
-        <v>291000</v>
+        <v>83300</v>
       </c>
       <c r="I21" s="3">
+        <v>188900</v>
+      </c>
+      <c r="J21" s="3">
+        <v>313600</v>
+      </c>
+      <c r="K21" s="3">
         <v>127900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>390100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>162800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>892000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>522900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>36500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>17200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>26200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>9900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>61800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>51800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>78000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>24200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>46500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>54400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>118400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>67300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>14400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>107800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>249700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>111500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>61800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>59700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>47300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>40100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>36100</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2016,11 +2095,11 @@
       <c r="M22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="N22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -2079,204 +2158,222 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>75400</v>
+        <v>86000</v>
       </c>
       <c r="E23" s="3">
+        <v>44800</v>
+      </c>
+      <c r="F23" s="3">
+        <v>86900</v>
+      </c>
+      <c r="G23" s="3">
         <v>130200</v>
       </c>
-      <c r="F23" s="3">
-        <v>42100</v>
-      </c>
-      <c r="G23" s="3">
-        <v>127700</v>
-      </c>
       <c r="H23" s="3">
-        <v>272700</v>
+        <v>54600</v>
       </c>
       <c r="I23" s="3">
+        <v>168300</v>
+      </c>
+      <c r="J23" s="3">
+        <v>295200</v>
+      </c>
+      <c r="K23" s="3">
         <v>111900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>365900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>134600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>834000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>481900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>31900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>14100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>21900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>8000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>50700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>38600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>61200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>17500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>33700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>45000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>102400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>55600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-11500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>95300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>228600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>98000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>58400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>56700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>44200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>36800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>35900</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>25400</v>
+        <v>34700</v>
       </c>
       <c r="E24" s="3">
+        <v>17000</v>
+      </c>
+      <c r="F24" s="3">
+        <v>29600</v>
+      </c>
+      <c r="G24" s="3">
         <v>49600</v>
       </c>
-      <c r="F24" s="3">
-        <v>-41800</v>
-      </c>
-      <c r="G24" s="3">
-        <v>25400</v>
-      </c>
       <c r="H24" s="3">
-        <v>100100</v>
+        <v>-55200</v>
       </c>
       <c r="I24" s="3">
+        <v>33500</v>
+      </c>
+      <c r="J24" s="3">
+        <v>108600</v>
+      </c>
+      <c r="K24" s="3">
         <v>46100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>211700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>47400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>308500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>151400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>7800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>3300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>-7800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>2400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>11100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>11900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>-29400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>-3000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>21700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>11100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>44400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>34000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>21500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>11100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>72200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>42000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>18500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>15400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>12700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>11000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>12400</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2373,204 +2470,222 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>50000</v>
+        <v>51300</v>
       </c>
       <c r="E26" s="3">
+        <v>27800</v>
+      </c>
+      <c r="F26" s="3">
+        <v>57300</v>
+      </c>
+      <c r="G26" s="3">
         <v>80600</v>
       </c>
-      <c r="F26" s="3">
-        <v>83900</v>
-      </c>
-      <c r="G26" s="3">
-        <v>102300</v>
-      </c>
       <c r="H26" s="3">
-        <v>172600</v>
+        <v>109800</v>
       </c>
       <c r="I26" s="3">
+        <v>134800</v>
+      </c>
+      <c r="J26" s="3">
+        <v>186600</v>
+      </c>
+      <c r="K26" s="3">
         <v>65800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>154200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>87300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>525500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>330500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>24000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>10700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>29700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>5600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>39600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>26700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>90600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>20500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>12100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>33900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>58000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>21700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-33000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>84100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>156400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>56000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>39900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>41400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>31500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>25900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>46500</v>
+        <v>46900</v>
       </c>
       <c r="E27" s="3">
+        <v>25600</v>
+      </c>
+      <c r="F27" s="3">
+        <v>53400</v>
+      </c>
+      <c r="G27" s="3">
         <v>77500</v>
       </c>
-      <c r="F27" s="3">
-        <v>80400</v>
-      </c>
-      <c r="G27" s="3">
-        <v>102800</v>
-      </c>
       <c r="H27" s="3">
-        <v>169700</v>
+        <v>105200</v>
       </c>
       <c r="I27" s="3">
+        <v>135400</v>
+      </c>
+      <c r="J27" s="3">
+        <v>183600</v>
+      </c>
+      <c r="K27" s="3">
         <v>67000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>155600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>85000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>520500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>330700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>24400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>10900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>30100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>5800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>39500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>26700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>91000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>20800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>13000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>33900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>57200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>21200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-28600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>79700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>156400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>56000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>39900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>40800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>31100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>25500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2667,8 +2782,14 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2765,8 +2886,14 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2863,8 +2990,14 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2961,204 +3094,222 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>3400</v>
+        <v>2500</v>
       </c>
       <c r="E32" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F32" s="3">
+        <v>3600</v>
+      </c>
+      <c r="G32" s="3">
         <v>700</v>
       </c>
-      <c r="F32" s="3">
-        <v>700</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I32" s="3">
+        <v>500</v>
+      </c>
+      <c r="J32" s="3">
+        <v>3700</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="L32" s="3">
         <v>400</v>
       </c>
-      <c r="H32" s="3">
-        <v>3800</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-5600</v>
-      </c>
-      <c r="J32" s="3">
-        <v>400</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>9500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-1300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>104700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>66400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>115200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>43200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>199000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>172400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>317800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>118400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>161000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>104600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>193000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>177000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>255800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>63500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>122200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>56500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>41500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>18300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>32100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>38800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>33500</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>46500</v>
+        <v>46900</v>
       </c>
       <c r="E33" s="3">
+        <v>25600</v>
+      </c>
+      <c r="F33" s="3">
+        <v>53400</v>
+      </c>
+      <c r="G33" s="3">
         <v>77500</v>
       </c>
-      <c r="F33" s="3">
-        <v>80400</v>
-      </c>
-      <c r="G33" s="3">
-        <v>102800</v>
-      </c>
       <c r="H33" s="3">
-        <v>169700</v>
+        <v>105200</v>
       </c>
       <c r="I33" s="3">
+        <v>135400</v>
+      </c>
+      <c r="J33" s="3">
+        <v>183600</v>
+      </c>
+      <c r="K33" s="3">
         <v>67000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>155600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>85000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>520500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>330700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>24400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>10900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>30100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>5800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>39500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>26700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>91000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>20800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>13000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>33900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>57200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>21200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-28600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>79700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>156400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>56000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>39900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>40800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>31100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>25500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3255,209 +3406,227 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>46500</v>
+        <v>46900</v>
       </c>
       <c r="E35" s="3">
+        <v>25600</v>
+      </c>
+      <c r="F35" s="3">
+        <v>53400</v>
+      </c>
+      <c r="G35" s="3">
         <v>77500</v>
       </c>
-      <c r="F35" s="3">
-        <v>80400</v>
-      </c>
-      <c r="G35" s="3">
-        <v>102800</v>
-      </c>
       <c r="H35" s="3">
-        <v>169700</v>
+        <v>105200</v>
       </c>
       <c r="I35" s="3">
+        <v>135400</v>
+      </c>
+      <c r="J35" s="3">
+        <v>183600</v>
+      </c>
+      <c r="K35" s="3">
         <v>67000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>155600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>85000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>520500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>330700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>24400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>10900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>30100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>5800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>39500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>26700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>91000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>20800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>13000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>33900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>57200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>21200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-28600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>79700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>156400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>56000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>39900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>40800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>31100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>25500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3492,8 +3661,10 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
+      <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3528,243 +3699,257 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
+      <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1767300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1463200</v>
+      </c>
+      <c r="F41" s="3">
         <v>1461200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1475800</v>
       </c>
-      <c r="F41" s="3">
-        <v>2003000</v>
-      </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
+        <v>2634900</v>
+      </c>
+      <c r="I41" s="3">
         <v>2192100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>868600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>941600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>2109300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>773300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>776600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>620200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>290000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>212500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>204300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>224900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>1192000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>836700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>837900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>1195800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>1398000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>804800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>676300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>1410000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>2158700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>898700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>947900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>1060300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>1235900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>1103600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>735900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>535600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>596800</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>247600</v>
+      </c>
+      <c r="E42" s="3">
+        <v>269200</v>
+      </c>
+      <c r="F42" s="3">
         <v>543600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>658000</v>
       </c>
-      <c r="F42" s="3">
-        <v>171400</v>
-      </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
+        <v>225500</v>
+      </c>
+      <c r="I42" s="3">
         <v>135600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>627100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>2659000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>3881400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>1234500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>1224200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>864700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>45600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>36800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>38900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>22800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>31500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>51000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>45500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>70200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>67700</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>74900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>98000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>151400</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>115000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>141800</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>107400</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>118300</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AF42" s="3">
         <v>212600</v>
-      </c>
-      <c r="AE42" s="3">
-        <v>96300</v>
-      </c>
-      <c r="AF42" s="3">
-        <v>104300</v>
       </c>
       <c r="AG42" s="3">
         <v>96300</v>
       </c>
       <c r="AH42" s="3">
+        <v>104300</v>
+      </c>
+      <c r="AI42" s="3">
+        <v>96300</v>
+      </c>
+      <c r="AJ42" s="3">
         <v>279000</v>
       </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>100400</v>
+      </c>
+      <c r="E43" s="3">
+        <v>160600</v>
+      </c>
+      <c r="F43" s="3">
         <v>157700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>201100</v>
       </c>
-      <c r="F43" s="3">
-        <v>172100</v>
-      </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
+        <v>226300</v>
+      </c>
+      <c r="I43" s="3">
         <v>184300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>132600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>112100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>238200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>226900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>138900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>137400</v>
       </c>
-      <c r="N43" s="3">
-        <v>0</v>
-      </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
       <c r="P43" s="3">
         <v>0</v>
       </c>
@@ -3822,19 +4007,25 @@
       <c r="AH43" s="3">
         <v>0</v>
       </c>
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E44" s="3">
-        <v>200</v>
+        <v>18100</v>
       </c>
       <c r="F44" s="3">
-        <v>200</v>
+        <v>18400</v>
       </c>
       <c r="G44" s="3">
         <v>200</v>
@@ -3843,7 +4034,7 @@
         <v>200</v>
       </c>
       <c r="I44" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J44" s="3">
         <v>200</v>
@@ -3855,13 +4046,13 @@
         <v>200</v>
       </c>
       <c r="M44" s="3">
+        <v>100</v>
+      </c>
+      <c r="N44" s="3">
         <v>200</v>
       </c>
-      <c r="N44" s="3">
-        <v>0</v>
-      </c>
       <c r="O44" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -3920,47 +4111,53 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>198500</v>
+      </c>
+      <c r="E45" s="3">
+        <v>403500</v>
+      </c>
+      <c r="F45" s="3">
         <v>153600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>188100</v>
       </c>
-      <c r="F45" s="3">
-        <v>198200</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
+        <v>241400</v>
+      </c>
+      <c r="I45" s="3">
         <v>150500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>328300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>56400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>123500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>63500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>55700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>71200</v>
       </c>
-      <c r="N45" s="3">
-        <v>0</v>
-      </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
       <c r="P45" s="3">
         <v>0</v>
       </c>
@@ -4018,47 +4215,53 @@
       <c r="AH45" s="3">
         <v>0</v>
       </c>
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>3636000</v>
+        <v>3863100</v>
       </c>
       <c r="E46" s="3">
-        <v>3331200</v>
+        <v>3698500</v>
       </c>
       <c r="F46" s="3">
-        <v>3280800</v>
+        <v>3654200</v>
       </c>
       <c r="G46" s="3">
+        <v>3363000</v>
+      </c>
+      <c r="H46" s="3">
+        <v>4351700</v>
+      </c>
+      <c r="I46" s="3">
         <v>3617700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>2700300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>4328800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>7321900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>2912800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>3095200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>2884000</v>
       </c>
-      <c r="N46" s="3">
-        <v>0</v>
-      </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
         <v>0</v>
       </c>
@@ -4116,204 +4319,222 @@
       <c r="AH46" s="3">
         <v>0</v>
       </c>
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2477500</v>
+      </c>
+      <c r="E47" s="3">
+        <v>2090000</v>
+      </c>
+      <c r="F47" s="3">
         <v>2069500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>2243600</v>
       </c>
-      <c r="F47" s="3">
-        <v>2457500</v>
-      </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
+        <v>3232800</v>
+      </c>
+      <c r="I47" s="3">
         <v>2669800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>2502600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>1049000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>2088700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>3184700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>3991400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>3368600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>3600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>3400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>3100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>2700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>11300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>8400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>8800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>9900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>13600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>8300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>7700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>11200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>14500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>2800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>22000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>20300</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>23800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>24200</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>15900</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AI47" s="3">
         <v>15200</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AJ47" s="3">
         <v>10900</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>617800</v>
+      </c>
+      <c r="E48" s="3">
+        <v>594100</v>
+      </c>
+      <c r="F48" s="3">
         <v>628000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>650500</v>
       </c>
-      <c r="F48" s="3">
-        <v>627100</v>
-      </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
+        <v>824900</v>
+      </c>
+      <c r="I48" s="3">
         <v>604600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>608400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>543100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>803200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>549600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>556100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>555800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>99900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>89900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>81100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>68800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>280700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>192100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>177700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>234900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>318100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>188100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>176400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>271100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>364900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>121500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>125900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>126800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>133200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>124500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>133800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>149200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>70200</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4339,79 +4560,85 @@
         <v>0</v>
       </c>
       <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
         <v>59000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>57400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>55700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>10000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>8300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>6900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>5400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>20300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>12300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>10200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>11900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>14600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>8100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>6700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>9100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>10900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>6600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>6300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>5900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>6900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>8100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>7900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>7400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4508,8 +4735,14 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4606,106 +4839,118 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>375000</v>
+        <v>485000</v>
       </c>
       <c r="E52" s="3">
-        <v>379600</v>
+        <v>478000</v>
       </c>
       <c r="F52" s="3">
-        <v>515900</v>
+        <v>356800</v>
       </c>
       <c r="G52" s="3">
+        <v>347800</v>
+      </c>
+      <c r="H52" s="3">
+        <v>642800</v>
+      </c>
+      <c r="I52" s="3">
         <v>355300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>378500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>392200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>866700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>515200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>403000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>335400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>1800</v>
-      </c>
-      <c r="O52" s="3">
-        <v>1600</v>
-      </c>
-      <c r="P52" s="3">
-        <v>1700</v>
       </c>
       <c r="Q52" s="3">
         <v>1600</v>
       </c>
       <c r="R52" s="3">
+        <v>1700</v>
+      </c>
+      <c r="S52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="T52" s="3">
         <v>6500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>4200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>4000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>27700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>52100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>37000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>34100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>75300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>40000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>35600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>6200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>3600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>9300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>4800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>7800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>13200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4802,106 +5047,118 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>17506500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>16174100</v>
+      </c>
+      <c r="F54" s="3">
         <v>16165500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>15178900</v>
       </c>
-      <c r="F54" s="3">
-        <v>14282200</v>
-      </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
+        <v>18788000</v>
+      </c>
+      <c r="I54" s="3">
         <v>12943400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>10462000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>9452000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>16496200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>11090500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>12207700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>11291800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>2037200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>1777500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>1658300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>1379500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>5679100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>3940200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>3725500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>4629800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>6479800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>3680600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>3382600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>5085500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>6320300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>4256700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>4168600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>4234100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>4812100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>4532100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>3926900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>3707300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>3729900</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4936,8 +5193,10 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
+      <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4972,145 +5231,153 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
+      <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11854100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>11205200</v>
+      </c>
+      <c r="F57" s="3">
         <v>10931100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>10227100</v>
       </c>
-      <c r="F57" s="3">
-        <v>9631100</v>
-      </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
+        <v>12669500</v>
+      </c>
+      <c r="I57" s="3">
         <v>8795300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>6371200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>5569500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>9802400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>7410500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>7830100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>7521300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>167400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>134500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>124000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>104100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>426700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>286900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>249200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>354700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>443700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>274100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>200400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>455500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>435500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>346300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>251100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>320900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>398200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>316500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>284300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>301300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>275600</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>377300</v>
+        <v>391600</v>
       </c>
       <c r="E58" s="3">
+        <v>378900</v>
+      </c>
+      <c r="F58" s="3">
+        <v>361100</v>
+      </c>
+      <c r="G58" s="3">
         <v>253200</v>
       </c>
-      <c r="F58" s="3">
-        <v>117200</v>
-      </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
+        <v>150900</v>
+      </c>
+      <c r="I58" s="3">
         <v>7400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>197200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>5500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>43600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>8000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>3800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>4200</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -5168,145 +5435,157 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>599000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>333900</v>
+      </c>
+      <c r="F59" s="3">
         <v>235700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>164200</v>
       </c>
-      <c r="F59" s="3">
-        <v>251700</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
+        <v>331200</v>
+      </c>
+      <c r="I59" s="3">
         <v>264300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>271800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>281700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>940500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>207500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>376300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>239300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>50400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>44900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>52600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>48200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>222400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>140900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>131000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>146300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>232300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>74200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>69900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>165500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>193200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>105900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>91000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>97800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>97400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>80000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>57500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>49900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>54200</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>11702900</v>
+        <v>13010300</v>
       </c>
       <c r="E60" s="3">
+        <v>12091000</v>
+      </c>
+      <c r="F60" s="3">
+        <v>11686700</v>
+      </c>
+      <c r="G60" s="3">
         <v>10783500</v>
       </c>
-      <c r="F60" s="3">
-        <v>10149400</v>
-      </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
+        <v>13348000</v>
+      </c>
+      <c r="I60" s="3">
         <v>9201200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>6962000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>5968400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>11042700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>7805000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>8365400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>7907800</v>
       </c>
-      <c r="N60" s="3">
-        <v>0</v>
-      </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
       <c r="P60" s="3">
         <v>0</v>
       </c>
@@ -5364,204 +5643,222 @@
       <c r="AH60" s="3">
         <v>0</v>
       </c>
+      <c r="AI60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1277200</v>
+        <v>1534800</v>
       </c>
       <c r="E61" s="3">
+        <v>1237800</v>
+      </c>
+      <c r="F61" s="3">
+        <v>1293500</v>
+      </c>
+      <c r="G61" s="3">
         <v>1205800</v>
       </c>
-      <c r="F61" s="3">
-        <v>1105400</v>
-      </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
+        <v>1457400</v>
+      </c>
+      <c r="I61" s="3">
         <v>947900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>750300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>494900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>893400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>533900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>663000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>575600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>4300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>4200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>3900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>3500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>16100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>12600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>12200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>18600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>27800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>17400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>16600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>25300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>35200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>26400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>21300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>23100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>200</v>
       </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
         <v>13700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>9600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>78300</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>508300</v>
+      </c>
+      <c r="E62" s="3">
+        <v>661300</v>
+      </c>
+      <c r="F62" s="3">
         <v>713200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>554700</v>
       </c>
-      <c r="F62" s="3">
-        <v>474400</v>
-      </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
+        <v>618600</v>
+      </c>
+      <c r="I62" s="3">
         <v>317500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>426800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>503700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>648000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>481400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>905400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>574600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>16000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>15800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>8100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>20500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>76200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>44000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>42100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>65800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>108400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>65500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>68700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>111800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>150400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>79000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>75500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>42900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>49900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>47400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>54400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>62500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>46300</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5658,8 +5955,14 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5756,8 +6059,14 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5854,106 +6163,118 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>15064800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>13997700</v>
+      </c>
+      <c r="F66" s="3">
         <v>13702600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>12553500</v>
       </c>
-      <c r="F66" s="3">
-        <v>11740100</v>
-      </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
+        <v>15443900</v>
+      </c>
+      <c r="I66" s="3">
         <v>10478600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>8150000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>6973900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>12660300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>8906100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>9998600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>9091700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1662300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1447700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1387000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1154700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>4800300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>3313100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>3164100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>3896400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>5522700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>3027400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>2801800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>4222000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>5280700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>3680100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>3651100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>3749600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>4289000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>4047700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>3445800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>3184200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>3299200</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5988,8 +6309,10 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
+      <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6086,8 +6409,14 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6184,8 +6513,14 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6282,8 +6617,14 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6380,106 +6721,118 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1559400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>1494700</v>
+      </c>
+      <c r="F72" s="3">
         <v>1594300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>1711900</v>
       </c>
-      <c r="F72" s="3">
-        <v>1571100</v>
-      </c>
-      <c r="G72" s="3">
-        <v>278800</v>
-      </c>
       <c r="H72" s="3">
+        <v>2066800</v>
+      </c>
+      <c r="I72" s="3">
+        <v>901700</v>
+      </c>
+      <c r="J72" s="3">
         <v>1313500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>1481200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>2194400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>1426700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>1415300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>1433700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>235300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>202900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>160600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>130500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>499000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>357800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>314900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>411700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>527200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>397400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>343200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>505000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>570400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>497900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>436200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>400900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>419200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>380500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>368900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>396500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>304100</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6576,8 +6929,14 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6674,8 +7033,14 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6772,106 +7137,118 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2365100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>2130800</v>
+      </c>
+      <c r="F76" s="3">
         <v>2415900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>2579800</v>
       </c>
-      <c r="F76" s="3">
-        <v>2501300</v>
-      </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
+        <v>3290400</v>
+      </c>
+      <c r="I76" s="3">
         <v>2427300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>2275900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>2447300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>3787500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>2151300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>2176300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>2168600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>374900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>329800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>271200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>224900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>878700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>627200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>561400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>733400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>957100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>653200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>580800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>863500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>1039600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>576700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>517500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>484600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>523100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>484400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>481100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>523100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>430700</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6968,209 +7345,227 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>46500</v>
+        <v>46900</v>
       </c>
       <c r="E81" s="3">
+        <v>25600</v>
+      </c>
+      <c r="F81" s="3">
+        <v>53400</v>
+      </c>
+      <c r="G81" s="3">
         <v>77500</v>
       </c>
-      <c r="F81" s="3">
-        <v>80400</v>
-      </c>
-      <c r="G81" s="3">
-        <v>102800</v>
-      </c>
       <c r="H81" s="3">
-        <v>169700</v>
+        <v>105200</v>
       </c>
       <c r="I81" s="3">
+        <v>135400</v>
+      </c>
+      <c r="J81" s="3">
+        <v>183600</v>
+      </c>
+      <c r="K81" s="3">
         <v>67000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>155600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>85000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>520500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>330700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>24400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>10900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>30100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>5800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>39500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>26700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>91000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>20800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>13000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>33900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>57200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>21200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-28600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>79700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>156400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>56000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>39900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>40800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>31100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>25500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7205,106 +7600,114 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
+      <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>25300</v>
+      </c>
+      <c r="E83" s="3">
+        <v>22100</v>
+      </c>
+      <c r="F83" s="3">
         <v>19700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>16700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>18700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>33000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>51600</v>
-      </c>
-      <c r="I83" s="3">
-        <v>46200</v>
-      </c>
-      <c r="J83" s="3">
-        <v>86300</v>
       </c>
       <c r="K83" s="3">
         <v>46200</v>
       </c>
       <c r="L83" s="3">
+        <v>86300</v>
+      </c>
+      <c r="M83" s="3">
+        <v>46200</v>
+      </c>
+      <c r="N83" s="3">
         <v>34200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>28700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>4700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>3200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>4300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>1900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>11100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>13100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>16800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>6700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>12800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>9500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>16000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>11600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>25900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>12500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>21100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>13400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>3400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>3000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>3000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>3300</v>
       </c>
-      <c r="AH83" s="3" t="s">
+      <c r="AJ83" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7401,8 +7804,14 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7499,8 +7908,14 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7597,8 +8012,14 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7695,8 +8116,14 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7793,106 +8220,118 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1104300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-1705700</v>
+      </c>
+      <c r="F89" s="3">
         <v>-1336200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-1507700</v>
       </c>
-      <c r="F89" s="3">
-        <v>-1798600</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-1541300</v>
-      </c>
       <c r="H89" s="3">
+        <v>-2359300</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-1886700</v>
+      </c>
+      <c r="J89" s="3">
         <v>-1105600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-1789400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-2431600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-6472600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-6616800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-3450000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>38700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-38200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-117900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-61000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>82500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-7600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>88800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>157000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-19300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>50100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-415200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-247300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>611600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-180800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-156000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-62700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>260600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>198900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>38000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>-38900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>154700</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7927,106 +8366,114 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
+      <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-76900</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="F91" s="3">
         <v>-28300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-16900</v>
       </c>
-      <c r="F91" s="3">
-        <v>-126800</v>
-      </c>
-      <c r="G91" s="3">
-        <v>12700</v>
-      </c>
       <c r="H91" s="3">
+        <v>-166700</v>
+      </c>
+      <c r="I91" s="3">
+        <v>20400</v>
+      </c>
+      <c r="J91" s="3">
         <v>-29200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-44000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-69500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-49600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-42900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-34500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-12277100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-312900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-2694300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-1125700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-10201100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-2576100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-1792900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-4400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-7800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-4800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-3700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-14400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-9200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-4500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-22400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>7300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-4800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-5200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8123,8 +8570,14 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8221,106 +8674,118 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-94600</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-37500</v>
+      </c>
+      <c r="F94" s="3">
         <v>-28300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-16800</v>
       </c>
-      <c r="F94" s="3">
-        <v>-127300</v>
-      </c>
-      <c r="G94" s="3">
-        <v>12400</v>
-      </c>
       <c r="H94" s="3">
+        <v>-167400</v>
+      </c>
+      <c r="I94" s="3">
+        <v>19700</v>
+      </c>
+      <c r="J94" s="3">
         <v>-24600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-44000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-71600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-49600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-37100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-42400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-26100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-1500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-14500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-4200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-6000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-2700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-8300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-4500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-15100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>17800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>16100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-22300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>14500</v>
       </c>
-      <c r="AF94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI94" s="3">
         <v>-5100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8355,46 +8820,48 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
+      <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E96" s="3">
+        <v>4800</v>
+      </c>
+      <c r="F96" s="3">
         <v>2800</v>
       </c>
-      <c r="E96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F96" s="3">
-        <v>6500</v>
-      </c>
-      <c r="G96" s="3">
-        <v>36100</v>
+      <c r="G96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H96" s="3">
+        <v>8400</v>
+      </c>
+      <c r="I96" s="3">
+        <v>43700</v>
+      </c>
+      <c r="J96" s="3">
         <v>74700</v>
       </c>
-      <c r="I96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J96" s="3">
-        <v>300</v>
-      </c>
-      <c r="K96" s="3">
-        <v>700</v>
+      <c r="K96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L96" s="3">
         <v>300</v>
       </c>
-      <c r="M96" s="3" t="s">
-        <v>5</v>
+      <c r="M96" s="3">
+        <v>700</v>
       </c>
       <c r="N96" s="3">
-        <v>0</v>
-      </c>
-      <c r="O96" s="3">
-        <v>0</v>
+        <v>300</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -8433,14 +8900,14 @@
         <v>0</v>
       </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-25500</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
         <v>0</v>
       </c>
@@ -8451,10 +8918,16 @@
         <v>0</v>
       </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8551,8 +9024,14 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8649,8 +9128,14 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8747,298 +9232,322 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1877400</v>
+      </c>
+      <c r="E100" s="3">
+        <v>1975200</v>
+      </c>
+      <c r="F100" s="3">
         <v>1986000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>1203800</v>
       </c>
-      <c r="F100" s="3">
-        <v>1937100</v>
-      </c>
-      <c r="G100" s="3">
-        <v>3326400</v>
-      </c>
       <c r="H100" s="3">
+        <v>2536300</v>
+      </c>
+      <c r="I100" s="3">
+        <v>4172300</v>
+      </c>
+      <c r="J100" s="3">
         <v>1713900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>2508500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>3133100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>6830200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>7590600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>4933100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-11200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>4100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-2200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-3400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-18400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-9800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-5300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-16500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-22500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-12900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>11500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-30600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-18300</v>
-      </c>
-      <c r="AC100" s="3">
-        <v>21900</v>
-      </c>
-      <c r="AD100" s="3">
-        <v>-8000</v>
       </c>
       <c r="AE100" s="3">
         <v>21900</v>
       </c>
       <c r="AF100" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="AG100" s="3">
+        <v>21900</v>
+      </c>
+      <c r="AH100" s="3">
         <v>55900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>2100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-63300</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-92700</v>
+      </c>
+      <c r="F101" s="3">
         <v>-271500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-361600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>1230900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>530900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>120000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>171000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>218900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-69800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-204200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>7700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>16500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-3600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-13500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-25700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-65700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>5500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>4800</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>23400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>23700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>51500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>63500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>30300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>245700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>69900</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>87800</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>-81800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>221100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>161900</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AI101" s="3">
         <v>22700</v>
       </c>
-      <c r="AH101" s="3" t="s">
+      <c r="AJ101" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>717700</v>
+      </c>
+      <c r="E102" s="3">
+        <v>392700</v>
+      </c>
+      <c r="F102" s="3">
         <v>715700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-365300</v>
       </c>
-      <c r="F102" s="3">
-        <v>-37700</v>
-      </c>
-      <c r="G102" s="3">
-        <v>1703100</v>
-      </c>
       <c r="H102" s="3">
+        <v>-53700</v>
+      </c>
+      <c r="I102" s="3">
+        <v>2212600</v>
+      </c>
+      <c r="J102" s="3">
         <v>312200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>313400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>1860800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>838800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>1056700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>1611600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>31500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-52700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-132000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-64300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-102100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>54400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>149300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-16900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>44100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-405400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-217500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>638300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>33000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-86500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>53300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>152200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>452700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>257800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-21800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>188600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BBAR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BBAR_QTR_FIN.xlsx
@@ -5352,7 +5352,7 @@
         <v>361100</v>
       </c>
       <c r="G58" s="3">
-        <v>253200</v>
+        <v>242100</v>
       </c>
       <c r="H58" s="3">
         <v>150900</v>
@@ -5560,7 +5560,7 @@
         <v>11686700</v>
       </c>
       <c r="G60" s="3">
-        <v>10783500</v>
+        <v>10772400</v>
       </c>
       <c r="H60" s="3">
         <v>13348000</v>
@@ -5664,7 +5664,7 @@
         <v>1293500</v>
       </c>
       <c r="G61" s="3">
-        <v>1205800</v>
+        <v>1217000</v>
       </c>
       <c r="H61" s="3">
         <v>1457400</v>
